--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3227,22 +3227,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>9.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,22 +3704,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>9.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3386,22 +3386,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,22 +3545,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3227,22 +3227,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,22 +3386,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3704,22 +3704,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.27</v>
+        <v>2.27</v>
       </c>
       <c r="O22" t="n">
-        <v>5.4</v>
+        <v>3.2</v>
       </c>
       <c r="P22" t="n">
-        <v>9.949999999999999</v>
+        <v>3.12</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,22 +3386,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,22 +3704,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>9.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>9.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,22 +3227,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,22 +3545,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,22 +3704,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G22" t="n">

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU23"/>
+  <dimension ref="A1:AU20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,22 +3386,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3540,27 +3540,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3690,483 +3690,6 @@
         <v>0</v>
       </c>
       <c r="AU20" s="3" t="n">
-        <v>46224.875</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Europe UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Fenerbahçe</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Górnik Zabrze</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N21" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="O21" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="P21" t="n">
-        <v>9.949999999999999</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU21" s="3" t="n">
-        <v>46224.875</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Lokomotiv</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Andijan</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU22" s="3" t="n">
-        <v>46224.875</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>21:35</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Vila Nova</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Fortaleza</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU23" s="3" t="n">
         <v>46224.89930555555</v>
       </c>
     </row>

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>9.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,22 +3386,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU20"/>
+  <dimension ref="A1:AU26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>9.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,22 +3227,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,22 +3386,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3540,156 +3540,1110 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Larne</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Red Star Belgrade</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" s="3" t="n">
+        <v>46224.875</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>FC Avan Academy</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Shamrock Rovers</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" s="3" t="n">
+        <v>46224.875</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sabah</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>KuPS</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" s="3" t="n">
+        <v>46224.875</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Mjällby</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lincoln Red Imps</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" s="3" t="n">
+        <v>46224.875</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AGF</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Lech Poznań</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="O24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P24" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" s="3" t="n">
+        <v>46224.875</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Saburtalo</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Slovan Bratislava</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" s="3" t="n">
+        <v>46224.875</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>21:35</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Vila Nova</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Fortaleza</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="inlineStr">
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" s="3" t="n">
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" s="3" t="n">
         <v>46224.89930555555</v>
       </c>
     </row>

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>9.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,22 +3227,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.27</v>
+        <v>1.27</v>
       </c>
       <c r="O24" t="n">
-        <v>3.2</v>
+        <v>5.4</v>
       </c>
       <c r="P24" t="n">
-        <v>3.12</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G25" t="n">

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,22 +3227,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.27</v>
+        <v>2.27</v>
       </c>
       <c r="O24" t="n">
-        <v>5.4</v>
+        <v>3.2</v>
       </c>
       <c r="P24" t="n">
-        <v>9.949999999999999</v>
+        <v>3.12</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G25" t="n">

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>9.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,22 +3227,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>9.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.27</v>
+        <v>1.27</v>
       </c>
       <c r="O25" t="n">
-        <v>3.2</v>
+        <v>5.4</v>
       </c>
       <c r="P25" t="n">
-        <v>3.12</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.27</v>
+        <v>2.27</v>
       </c>
       <c r="O25" t="n">
-        <v>5.4</v>
+        <v>3.2</v>
       </c>
       <c r="P25" t="n">
-        <v>9.949999999999999</v>
+        <v>3.12</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU26"/>
+  <dimension ref="A1:AU30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>9.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Egnatia Rrogozhinë</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4494,156 +4494,792 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>FC Avan Academy</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Shamrock Rovers</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" s="3" t="n">
+        <v>46224.875</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Fenerbahçe</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Górnik Zabrze</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="O27" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="P27" t="n">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" s="3" t="n">
+        <v>46224.875</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Sabah</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>KuPS</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" s="3" t="n">
+        <v>46224.875</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Levski Sofia</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>CS U Craiova</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" s="3" t="n">
+        <v>46224.875</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>21:35</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Vila Nova</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>Fortaleza</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="inlineStr">
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU26" s="3" t="n">
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" s="3" t="n">
         <v>46224.89930555555</v>
       </c>
     </row>

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Egnatia Rrogozhinë</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Egnatia Rrogozhinë</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>9.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,22 +3227,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Egnatia Rrogozhinë</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Egnatia Rrogozhinë</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>9.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Egnatia Rrogozhinë</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Egnatia Rrogozhinë</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,22 +3227,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Egnatia Rrogozhinë</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>9.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Egnatia Rrogozhinë</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G29" t="n">

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Egnatia Rrogozhinë</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Egnatia Rrogozhinë</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>9.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.27</v>
+        <v>1.27</v>
       </c>
       <c r="O25" t="n">
-        <v>3.2</v>
+        <v>5.4</v>
       </c>
       <c r="P25" t="n">
-        <v>3.12</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,22 +4817,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G29" t="n">

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.93</v>
+        <v>3.25</v>
       </c>
       <c r="O2" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="P2" t="n">
-        <v>3.45</v>
+        <v>2.15</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G29" t="n">

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>3.25</v>
+        <v>1.93</v>
       </c>
       <c r="O2" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="P2" t="n">
-        <v>2.15</v>
+        <v>3.45</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.93</v>
+        <v>3.25</v>
       </c>
       <c r="O3" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="P3" t="n">
-        <v>3.45</v>
+        <v>2.15</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1688,55 +1688,55 @@
         <v>3.52</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2006,55 +2006,55 @@
         <v>3.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>5.93</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2483,34 +2483,34 @@
         <v>3.46</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA13" t="n">
         <v>1.88</v>
@@ -2519,19 +2519,19 @@
         <v>1.85</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Egnatia Rrogozhinë</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Egnatia Rrogozhinë</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.27</v>
+        <v>2.32</v>
       </c>
       <c r="O25" t="n">
-        <v>5.4</v>
+        <v>3.2</v>
       </c>
       <c r="P25" t="n">
-        <v>9.949999999999999</v>
+        <v>2.95</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,22 +4817,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU30"/>
+  <dimension ref="A1:AU27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1473,27 +1473,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1623,7 +1623,7 @@
         <v>0</v>
       </c>
       <c r="AU7" s="3" t="n">
-        <v>46224.58333333334</v>
+        <v>46224.54166666666</v>
       </c>
     </row>
     <row r="8">
@@ -1632,27 +1632,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1782,7 +1782,7 @@
         <v>0</v>
       </c>
       <c r="AU8" s="3" t="n">
-        <v>46224.625</v>
+        <v>46224.54166666666</v>
       </c>
     </row>
     <row r="9">
@@ -1791,27 +1791,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1941,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="AU9" s="3" t="n">
-        <v>46224.77083333334</v>
+        <v>46224.54166666666</v>
       </c>
     </row>
     <row r="10">
@@ -1950,27 +1950,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.93</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2100,7 +2100,7 @@
         <v>0</v>
       </c>
       <c r="AU10" s="3" t="n">
-        <v>46224.79166666666</v>
+        <v>46224.54166666666</v>
       </c>
     </row>
     <row r="11">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2259,7 +2259,7 @@
         <v>0</v>
       </c>
       <c r="AU11" s="3" t="n">
-        <v>46224.8125</v>
+        <v>46224.58333333334</v>
       </c>
     </row>
     <row r="12">
@@ -2268,27 +2268,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2418,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="AU12" s="3" t="n">
-        <v>46224.8125</v>
+        <v>46224.58333333334</v>
       </c>
     </row>
     <row r="13">
@@ -2427,27 +2427,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2577,7 +2577,7 @@
         <v>0</v>
       </c>
       <c r="AU13" s="3" t="n">
-        <v>46224.8125</v>
+        <v>46224.625</v>
       </c>
     </row>
     <row r="14">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.51</v>
+        <v>2.32</v>
       </c>
       <c r="O14" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="P14" t="n">
-        <v>4.7</v>
+        <v>3.52</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>3.38</v>
       </c>
       <c r="R14" t="n">
-        <v>2.4</v>
+        <v>1.66</v>
       </c>
       <c r="S14" t="n">
-        <v>1.27</v>
+        <v>1.74</v>
       </c>
       <c r="T14" t="n">
-        <v>3.4</v>
+        <v>2.08</v>
       </c>
       <c r="U14" t="n">
-        <v>2.15</v>
+        <v>4.25</v>
       </c>
       <c r="V14" t="n">
-        <v>1.52</v>
+        <v>1.15</v>
       </c>
       <c r="W14" t="n">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AE14" t="n">
         <v>1.02</v>
       </c>
-      <c r="Y14" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AF14" t="n">
-        <v>1.59</v>
+        <v>2.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.3</v>
+        <v>1.45</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2736,7 +2736,7 @@
         <v>0</v>
       </c>
       <c r="AU14" s="3" t="n">
-        <v>46224.83333333334</v>
+        <v>46224.625</v>
       </c>
     </row>
     <row r="15">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2895,7 +2895,7 @@
         <v>0</v>
       </c>
       <c r="AU15" s="3" t="n">
-        <v>46224.875</v>
+        <v>46224.625</v>
       </c>
     </row>
     <row r="16">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3054,7 +3054,7 @@
         <v>0</v>
       </c>
       <c r="AU16" s="3" t="n">
-        <v>46224.875</v>
+        <v>46224.64583333334</v>
       </c>
     </row>
     <row r="17">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="AU17" s="3" t="n">
-        <v>46224.875</v>
+        <v>46224.65625</v>
       </c>
     </row>
     <row r="18">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Egnatia Rrogozhinë</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3372,7 +3372,7 @@
         <v>0</v>
       </c>
       <c r="AU18" s="3" t="n">
-        <v>46224.875</v>
+        <v>46224.66666666666</v>
       </c>
     </row>
     <row r="19">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>5.36</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3531,7 +3531,7 @@
         <v>0</v>
       </c>
       <c r="AU19" s="3" t="n">
-        <v>46224.875</v>
+        <v>46224.66666666666</v>
       </c>
     </row>
     <row r="20">
@@ -3540,27 +3540,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3690,7 +3690,7 @@
         <v>0</v>
       </c>
       <c r="AU20" s="3" t="n">
-        <v>46224.875</v>
+        <v>46224.77083333334</v>
       </c>
     </row>
     <row r="21">
@@ -3699,27 +3699,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>5.93</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3849,7 +3849,7 @@
         <v>0</v>
       </c>
       <c r="AU21" s="3" t="n">
-        <v>46224.875</v>
+        <v>46224.79166666666</v>
       </c>
     </row>
     <row r="22">
@@ -3858,27 +3858,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="O22" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P22" t="n">
-        <v>3.12</v>
+        <v>3.46</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4008,7 +4008,7 @@
         <v>0</v>
       </c>
       <c r="AU22" s="3" t="n">
-        <v>46224.875</v>
+        <v>46224.8125</v>
       </c>
     </row>
     <row r="23">
@@ -4017,27 +4017,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4167,7 +4167,7 @@
         <v>0</v>
       </c>
       <c r="AU23" s="3" t="n">
-        <v>46224.875</v>
+        <v>46224.8125</v>
       </c>
     </row>
     <row r="24">
@@ -4176,27 +4176,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4326,7 +4326,7 @@
         <v>0</v>
       </c>
       <c r="AU24" s="3" t="n">
-        <v>46224.875</v>
+        <v>46224.8125</v>
       </c>
     </row>
     <row r="25">
@@ -4335,12 +4335,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.32</v>
+        <v>1.51</v>
       </c>
       <c r="O25" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="P25" t="n">
-        <v>2.95</v>
+        <v>4.7</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4485,7 +4485,7 @@
         <v>0</v>
       </c>
       <c r="AU25" s="3" t="n">
-        <v>46224.875</v>
+        <v>46224.83333333334</v>
       </c>
     </row>
     <row r="26">
@@ -4499,22 +4499,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4653,27 +4653,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4803,483 +4803,6 @@
         <v>0</v>
       </c>
       <c r="AU27" s="3" t="n">
-        <v>46224.875</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Europe UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Fenerbahçe</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Górnik Zabrze</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N28" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="O28" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="P28" t="n">
-        <v>9.949999999999999</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU28" s="3" t="n">
-        <v>46224.875</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Europe UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Larne</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Red Star Belgrade</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU29" s="3" t="n">
-        <v>46224.875</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>21:35</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Vila Nova</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Fortaleza</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N30" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O30" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU30" s="3" t="n">
         <v>46224.89930555555</v>
       </c>
     </row>

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.32</v>
+        <v>1.27</v>
       </c>
       <c r="O14" t="n">
-        <v>2.8</v>
+        <v>5.4</v>
       </c>
       <c r="P14" t="n">
-        <v>3.52</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>9.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G24" t="n">

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G24" t="n">

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.92</v>
+        <v>2.27</v>
       </c>
       <c r="O11" t="n">
-        <v>3.72</v>
+        <v>3.2</v>
       </c>
       <c r="P11" t="n">
-        <v>3.52</v>
+        <v>3.12</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA11" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AK11" t="n">
         <v>1.61</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.27</v>
+        <v>1.92</v>
       </c>
       <c r="O12" t="n">
-        <v>3.2</v>
+        <v>3.72</v>
       </c>
       <c r="P12" t="n">
-        <v>3.12</v>
+        <v>3.52</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.27</v>
+        <v>3.6</v>
       </c>
       <c r="O14" t="n">
-        <v>5.4</v>
+        <v>3.6</v>
       </c>
       <c r="P14" t="n">
-        <v>9.949999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -4550,22 +4550,22 @@
         <v>2.95</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -4574,31 +4574,31 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>4.2</v>
+        <v>1.11</v>
       </c>
       <c r="O7" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="P7" t="n">
-        <v>1.72</v>
+        <v>14</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.39</v>
+        <v>1.55</v>
       </c>
       <c r="R7" t="n">
-        <v>2.43</v>
+        <v>2.9</v>
       </c>
       <c r="S7" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T7" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="U7" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="V7" t="n">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="W7" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.62</v>
+        <v>5.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.3</v>
+        <v>2.65</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.43</v>
+        <v>2.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.28</v>
+        <v>1.74</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.24</v>
+        <v>1.06</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.19</v>
+        <v>4.7</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.34</v>
+        <v>2.02</v>
       </c>
       <c r="O8" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>2.72</v>
+        <v>3.27</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.87</v>
+        <v>2.52</v>
       </c>
       <c r="R8" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="S8" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T8" t="n">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="V8" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="W8" t="n">
         <v>1.07</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.94</v>
+        <v>3.7</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.72</v>
+        <v>2.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.26</v>
+        <v>2.02</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.56</v>
+        <v>1.76</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.11</v>
+        <v>2.34</v>
       </c>
       <c r="O9" t="n">
-        <v>7</v>
+        <v>3.6</v>
       </c>
       <c r="P9" t="n">
-        <v>14</v>
+        <v>2.72</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.55</v>
+        <v>2.87</v>
       </c>
       <c r="R9" t="n">
-        <v>2.9</v>
+        <v>2.24</v>
       </c>
       <c r="S9" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="T9" t="n">
-        <v>4</v>
+        <v>3.28</v>
       </c>
       <c r="U9" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="V9" t="n">
-        <v>1.67</v>
+        <v>1.47</v>
       </c>
       <c r="W9" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.8</v>
+        <v>3.94</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.42</v>
+        <v>1.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.65</v>
+        <v>1.95</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.1</v>
+        <v>2.72</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.66</v>
+        <v>1.36</v>
       </c>
       <c r="AE9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
         <v>1.26</v>
       </c>
-      <c r="AF9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AK9" t="n">
-        <v>4.7</v>
+        <v>1.56</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.02</v>
+        <v>4.2</v>
       </c>
       <c r="O10" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P10" t="n">
-        <v>3.27</v>
+        <v>1.72</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.52</v>
+        <v>4.39</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2</v>
+        <v>2.43</v>
       </c>
       <c r="S10" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="U10" t="n">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="V10" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="W10" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AF10" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.76</v>
+        <v>1.19</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.32</v>
+        <v>2.37</v>
       </c>
       <c r="O13" t="n">
-        <v>2.8</v>
+        <v>2.61</v>
       </c>
       <c r="P13" t="n">
-        <v>3.52</v>
+        <v>3.25</v>
       </c>
       <c r="Q13" t="n">
         <v>3.38</v>
@@ -2498,25 +2498,25 @@
         <v>4.25</v>
       </c>
       <c r="V13" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AA13" t="n">
         <v>3.04</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AC13" t="n">
         <v>7</v>
@@ -2528,7 +2528,7 @@
         <v>1.02</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AG13" t="n">
         <v>1.5</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>3.6</v>
+        <v>1.27</v>
       </c>
       <c r="O14" t="n">
-        <v>3.6</v>
+        <v>5.4</v>
       </c>
       <c r="P14" t="n">
-        <v>1.8</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>5</v>
+        <v>1.67</v>
       </c>
       <c r="R14" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="S14" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="T14" t="n">
-        <v>3.15</v>
+        <v>3.34</v>
       </c>
       <c r="U14" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V14" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="W14" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.57</v>
+        <v>2.01</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.25</v>
+        <v>1.72</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.17</v>
+        <v>3.78</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.27</v>
+        <v>3.6</v>
       </c>
       <c r="O15" t="n">
-        <v>5.4</v>
+        <v>3.6</v>
       </c>
       <c r="P15" t="n">
-        <v>9.949999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.67</v>
+        <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="S15" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="T15" t="n">
-        <v>3.34</v>
+        <v>3.15</v>
       </c>
       <c r="U15" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="V15" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="W15" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="AD15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF15" t="n">
         <v>1.57</v>
       </c>
-      <c r="AE15" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.01</v>
-      </c>
       <c r="AG15" t="n">
-        <v>1.72</v>
+        <v>2.25</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AK15" t="n">
-        <v>3.78</v>
+        <v>1.17</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>6.2</v>
+        <v>2.4</v>
       </c>
       <c r="O18" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="P18" t="n">
-        <v>1.52</v>
+        <v>2.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.4</v>
+        <v>6.2</v>
       </c>
       <c r="O19" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="P19" t="n">
-        <v>2.8</v>
+        <v>1.52</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.93</v>
+        <v>3.25</v>
       </c>
       <c r="O2" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="P2" t="n">
-        <v>3.45</v>
+        <v>2.15</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.11</v>
+        <v>1.62</v>
       </c>
       <c r="O7" t="n">
-        <v>7</v>
+        <v>3.57</v>
       </c>
       <c r="P7" t="n">
-        <v>14</v>
+        <v>4.21</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.55</v>
+        <v>2.26</v>
       </c>
       <c r="R7" t="n">
-        <v>2.9</v>
+        <v>2.35</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="T7" t="n">
-        <v>4</v>
+        <v>3.34</v>
       </c>
       <c r="U7" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="V7" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="W7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y7" t="n">
         <v>1.17</v>
       </c>
-      <c r="X7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.09</v>
-      </c>
       <c r="Z7" t="n">
-        <v>5.8</v>
+        <v>4.05</v>
       </c>
       <c r="AA7" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AD7" t="n">
         <v>1.42</v>
       </c>
-      <c r="AB7" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AE7" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="AF7" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.74</v>
+        <v>2.17</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.06</v>
+        <v>1.23</v>
       </c>
       <c r="AK7" t="n">
-        <v>4.7</v>
+        <v>2.02</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.02</v>
+        <v>4.2</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>3.27</v>
+        <v>1.72</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.52</v>
+        <v>4.21</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="S8" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T8" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="U8" t="n">
-        <v>2.65</v>
+        <v>2.41</v>
       </c>
       <c r="V8" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.7</v>
+        <v>4.05</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>2.13</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.9</v>
+        <v>2.57</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.02</v>
+        <v>2.23</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.76</v>
+        <v>1.26</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="O9" t="n">
-        <v>3.6</v>
+        <v>3.08</v>
       </c>
       <c r="P9" t="n">
-        <v>2.72</v>
+        <v>2.67</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.87</v>
+        <v>3.01</v>
       </c>
       <c r="R9" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="S9" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T9" t="n">
-        <v>3.28</v>
+        <v>2.89</v>
       </c>
       <c r="U9" t="n">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="V9" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="W9" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.94</v>
+        <v>3.44</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.72</v>
+        <v>3.05</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>4.2</v>
+        <v>1.11</v>
       </c>
       <c r="O10" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="P10" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="V10" t="n">
         <v>1.72</v>
       </c>
-      <c r="Q10" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.54</v>
-      </c>
       <c r="W10" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.62</v>
+        <v>5.85</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.3</v>
+        <v>2.72</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.43</v>
+        <v>2.04</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.57</v>
+        <v>2.03</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.28</v>
+        <v>1.7</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.19</v>
+        <v>5.05</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="O11" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="P11" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="S11" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="T11" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="U11" t="n">
-        <v>2.89</v>
+        <v>3.22</v>
       </c>
       <c r="V11" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.05</v>
+        <v>2.68</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.04</v>
+        <v>2.29</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.38</v>
+        <v>4.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.93</v>
+        <v>1.77</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2636,13 +2636,13 @@
         <v>1.27</v>
       </c>
       <c r="O14" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="P14" t="n">
-        <v>9.949999999999999</v>
+        <v>11</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="R14" t="n">
         <v>2.62</v>
@@ -2654,10 +2654,10 @@
         <v>3.34</v>
       </c>
       <c r="U14" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="V14" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W14" t="n">
         <v>1.13</v>
@@ -2669,28 +2669,28 @@
         <v>1.13</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.51</v>
+        <v>1.66</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2792,31 +2792,31 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="O15" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P15" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>4.45</v>
       </c>
       <c r="R15" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S15" t="n">
         <v>1.31</v>
       </c>
       <c r="T15" t="n">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="U15" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V15" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W15" t="n">
         <v>1.11</v>
@@ -2828,7 +2828,7 @@
         <v>1.16</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.25</v>
+        <v>4.15</v>
       </c>
       <c r="AA15" t="n">
         <v>1.61</v>
@@ -2837,19 +2837,19 @@
         <v>2.25</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.34</v>
+        <v>2.45</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>1.25</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="O16" t="n">
-        <v>3.47</v>
+        <v>3.7</v>
       </c>
       <c r="P16" t="n">
-        <v>3.42</v>
+        <v>3.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="R16" t="n">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="S16" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T16" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="U16" t="n">
-        <v>2.31</v>
+        <v>2.48</v>
       </c>
       <c r="V16" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.34</v>
+        <v>2.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.37</v>
+        <v>2.18</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.42</v>
+        <v>2.51</v>
       </c>
       <c r="O17" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="P17" t="n">
-        <v>2.7</v>
+        <v>2.51</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.4</v>
+        <v>10.5</v>
       </c>
       <c r="O18" t="n">
-        <v>3.5</v>
+        <v>6.1</v>
       </c>
       <c r="P18" t="n">
-        <v>2.8</v>
+        <v>1.13</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.9</v>
+        <v>14.5</v>
       </c>
       <c r="R18" t="n">
-        <v>2.15</v>
+        <v>2.78</v>
       </c>
       <c r="S18" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="T18" t="n">
-        <v>2.99</v>
+        <v>3.34</v>
       </c>
       <c r="U18" t="n">
-        <v>2.57</v>
+        <v>2.13</v>
       </c>
       <c r="V18" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="W18" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE18" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z18" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AF18" t="n">
-        <v>1.62</v>
+        <v>2.58</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.2</v>
+        <v>1.44</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.3</v>
+        <v>1.07</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>6.2</v>
+        <v>2.31</v>
       </c>
       <c r="O19" t="n">
-        <v>4.5</v>
+        <v>3.14</v>
       </c>
       <c r="P19" t="n">
-        <v>1.52</v>
+        <v>2.56</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>4.2</v>
+        <v>1.11</v>
       </c>
       <c r="O8" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="P8" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="V8" t="n">
         <v>1.72</v>
       </c>
-      <c r="Q8" t="n">
-        <v>4.21</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.5</v>
-      </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.05</v>
+        <v>5.85</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.69</v>
+        <v>1.36</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.13</v>
+        <v>2.72</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.57</v>
+        <v>2.04</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.58</v>
+        <v>2.03</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.23</v>
+        <v>1.7</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.26</v>
+        <v>5.05</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,80 +1997,80 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.11</v>
+        <v>4.2</v>
       </c>
       <c r="O10" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="P10" t="n">
-        <v>14</v>
+        <v>1.72</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.49</v>
+        <v>4.21</v>
       </c>
       <c r="R10" t="n">
-        <v>2.99</v>
+        <v>2.21</v>
       </c>
       <c r="S10" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="T10" t="n">
-        <v>4.1</v>
+        <v>3.15</v>
       </c>
       <c r="U10" t="n">
-        <v>2.05</v>
+        <v>2.41</v>
       </c>
       <c r="V10" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.85</v>
+        <v>4.05</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.36</v>
+        <v>1.69</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.72</v>
+        <v>2.13</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.04</v>
+        <v>2.57</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AE10" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.26</v>
       </c>
-      <c r="AF10" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AK10" t="n">
-        <v>5.05</v>
+        <v>1.26</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.37</v>
+        <v>3.8</v>
       </c>
       <c r="O13" t="n">
-        <v>2.61</v>
+        <v>3.75</v>
       </c>
       <c r="P13" t="n">
-        <v>3.25</v>
+        <v>1.85</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.38</v>
+        <v>4.45</v>
       </c>
       <c r="R13" t="n">
-        <v>1.66</v>
+        <v>2.38</v>
       </c>
       <c r="S13" t="n">
-        <v>1.74</v>
+        <v>1.31</v>
       </c>
       <c r="T13" t="n">
-        <v>2.08</v>
+        <v>3.22</v>
       </c>
       <c r="U13" t="n">
-        <v>4.25</v>
+        <v>2.34</v>
       </c>
       <c r="V13" t="n">
-        <v>1.17</v>
+        <v>1.53</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X13" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.71</v>
+        <v>1.16</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.1</v>
+        <v>4.15</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.04</v>
+        <v>1.61</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.29</v>
+        <v>2.25</v>
       </c>
       <c r="AC13" t="n">
-        <v>7</v>
+        <v>2.45</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.07</v>
+        <v>1.44</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.4</v>
+        <v>1.53</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>3.8</v>
+        <v>2.37</v>
       </c>
       <c r="O15" t="n">
-        <v>3.75</v>
+        <v>2.61</v>
       </c>
       <c r="P15" t="n">
-        <v>1.85</v>
+        <v>3.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.45</v>
+        <v>3.38</v>
       </c>
       <c r="R15" t="n">
-        <v>2.38</v>
+        <v>1.66</v>
       </c>
       <c r="S15" t="n">
-        <v>1.31</v>
+        <v>1.74</v>
       </c>
       <c r="T15" t="n">
-        <v>3.22</v>
+        <v>2.08</v>
       </c>
       <c r="U15" t="n">
-        <v>2.34</v>
+        <v>4.25</v>
       </c>
       <c r="V15" t="n">
-        <v>1.53</v>
+        <v>1.15</v>
       </c>
       <c r="W15" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.16</v>
+        <v>1.71</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.15</v>
+        <v>2.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.61</v>
+        <v>3.04</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.25</v>
+        <v>1.29</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.45</v>
+        <v>7</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.44</v>
+        <v>1.07</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.53</v>
+        <v>2.4</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="O21" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="P21" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q21" t="n">
         <v>3.1</v>
@@ -3779,22 +3779,22 @@
         <v>1.09</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AC21" t="n">
-        <v>5.93</v>
+        <v>5.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AE21" t="n">
         <v>1.03</v>
@@ -3905,25 +3905,25 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="O22" t="n">
         <v>3.4</v>
       </c>
       <c r="P22" t="n">
-        <v>3.46</v>
+        <v>3.56</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="R22" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="S22" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="T22" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="U22" t="n">
         <v>2.59</v>
@@ -3935,34 +3935,34 @@
         <v>1.05</v>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC22" t="n">
         <v>3.25</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE22" t="n">
         <v>1.11</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G24" t="n">

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>3.25</v>
+        <v>1.93</v>
       </c>
       <c r="O2" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="P2" t="n">
-        <v>2.15</v>
+        <v>3.45</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.93</v>
+        <v>3.25</v>
       </c>
       <c r="O3" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="P3" t="n">
-        <v>3.45</v>
+        <v>2.15</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="O7" t="n">
+        <v>7</v>
+      </c>
+      <c r="P7" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AD7" t="n">
         <v>1.62</v>
       </c>
-      <c r="O7" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="P7" t="n">
-        <v>4.21</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AE7" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.62</v>
+        <v>2.15</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.17</v>
+        <v>1.63</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.23</v>
+        <v>1.03</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.02</v>
+        <v>4.5</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.11</v>
+        <v>2.35</v>
       </c>
       <c r="O8" t="n">
-        <v>7</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>14</v>
+        <v>2.65</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.49</v>
+        <v>2.72</v>
       </c>
       <c r="R8" t="n">
-        <v>2.99</v>
+        <v>2.09</v>
       </c>
       <c r="S8" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="T8" t="n">
-        <v>4.1</v>
+        <v>2.89</v>
       </c>
       <c r="U8" t="n">
-        <v>2.05</v>
+        <v>2.73</v>
       </c>
       <c r="V8" t="n">
-        <v>1.72</v>
+        <v>1.4</v>
       </c>
       <c r="W8" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.07</v>
       </c>
-      <c r="Z8" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AF8" t="n">
-        <v>2.03</v>
+        <v>1.67</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.7</v>
+        <v>2.08</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.07</v>
+        <v>1.4</v>
       </c>
       <c r="AK8" t="n">
-        <v>5.05</v>
+        <v>1.52</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.26</v>
+        <v>4.2</v>
       </c>
       <c r="O9" t="n">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="P9" t="n">
-        <v>2.67</v>
+        <v>1.72</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.01</v>
+        <v>4.1</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="S9" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="T9" t="n">
-        <v>2.89</v>
+        <v>3.15</v>
       </c>
       <c r="U9" t="n">
-        <v>2.69</v>
+        <v>2.41</v>
       </c>
       <c r="V9" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.44</v>
+        <v>4.05</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.05</v>
+        <v>2.57</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.52</v>
+        <v>1.26</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>4.2</v>
+        <v>1.64</v>
       </c>
       <c r="O10" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="P10" t="n">
-        <v>1.72</v>
+        <v>4.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.21</v>
+        <v>2.1</v>
       </c>
       <c r="R10" t="n">
-        <v>2.21</v>
+        <v>2.47</v>
       </c>
       <c r="S10" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="T10" t="n">
-        <v>3.15</v>
+        <v>3.07</v>
       </c>
       <c r="U10" t="n">
-        <v>2.41</v>
+        <v>2.29</v>
       </c>
       <c r="V10" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
         <v>1.17</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.05</v>
+        <v>4.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.26</v>
+        <v>2.1</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="O11" t="n">
-        <v>3.12</v>
+        <v>3.24</v>
       </c>
       <c r="P11" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.29</v>
+        <v>1.61</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.61</v>
+        <v>2.25</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="O12" t="n">
-        <v>3.72</v>
+        <v>3.25</v>
       </c>
       <c r="P12" t="n">
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AA12" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AB12" t="n">
         <v>1.61</v>
       </c>
-      <c r="AB12" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3.8</v>
+        <v>2.37</v>
       </c>
       <c r="O13" t="n">
-        <v>3.75</v>
+        <v>2.61</v>
       </c>
       <c r="P13" t="n">
-        <v>1.85</v>
+        <v>3.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.45</v>
+        <v>3.3</v>
       </c>
       <c r="R13" t="n">
-        <v>2.38</v>
+        <v>1.66</v>
       </c>
       <c r="S13" t="n">
-        <v>1.31</v>
+        <v>1.74</v>
       </c>
       <c r="T13" t="n">
-        <v>3.22</v>
+        <v>2.08</v>
       </c>
       <c r="U13" t="n">
-        <v>2.34</v>
+        <v>4.25</v>
       </c>
       <c r="V13" t="n">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
       <c r="W13" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.16</v>
+        <v>1.71</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.15</v>
+        <v>2.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.61</v>
+        <v>3.04</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.25</v>
+        <v>1.29</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.45</v>
+        <v>7</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.44</v>
+        <v>1.06</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.53</v>
+        <v>2.4</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.27</v>
+        <v>3.25</v>
       </c>
       <c r="O14" t="n">
-        <v>5.2</v>
+        <v>3.55</v>
       </c>
       <c r="P14" t="n">
-        <v>11</v>
+        <v>1.94</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.62</v>
+        <v>3.74</v>
       </c>
       <c r="R14" t="n">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="S14" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="T14" t="n">
-        <v>3.34</v>
+        <v>3.15</v>
       </c>
       <c r="U14" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="V14" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="W14" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.55</v>
+        <v>4.05</v>
       </c>
       <c r="AA14" t="n">
         <v>1.66</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.29</v>
+        <v>2.48</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.02</v>
+        <v>1.57</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.71</v>
+        <v>2.3</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.78</v>
+        <v>1.28</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.37</v>
+        <v>1.27</v>
       </c>
       <c r="O15" t="n">
-        <v>2.61</v>
+        <v>6</v>
       </c>
       <c r="P15" t="n">
-        <v>3.25</v>
+        <v>11</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.38</v>
+        <v>1.65</v>
       </c>
       <c r="R15" t="n">
-        <v>1.66</v>
+        <v>2.78</v>
       </c>
       <c r="S15" t="n">
-        <v>1.74</v>
+        <v>1.26</v>
       </c>
       <c r="T15" t="n">
-        <v>2.08</v>
+        <v>3.34</v>
       </c>
       <c r="U15" t="n">
-        <v>4.25</v>
+        <v>2.21</v>
       </c>
       <c r="V15" t="n">
-        <v>1.15</v>
+        <v>1.57</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="X15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
         <v>1.12</v>
       </c>
-      <c r="Y15" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AK15" t="n">
-        <v>1.45</v>
+        <v>3.78</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2954,61 +2954,61 @@
         <v>1.91</v>
       </c>
       <c r="O16" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P16" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="R16" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="S16" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T16" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="U16" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W16" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.7</v>
+        <v>2.34</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3110,61 +3110,61 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.51</v>
+        <v>2.18</v>
       </c>
       <c r="O17" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>2.51</v>
+        <v>3.13</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.26</v>
+        <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S17" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="T17" t="n">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="U17" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="V17" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AC17" t="n">
         <v>4.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AE17" t="n">
         <v>1.02</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AG17" t="n">
         <v>1.8</v>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,80 +3269,80 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>10.5</v>
+        <v>2.4</v>
       </c>
       <c r="O18" t="n">
-        <v>6.1</v>
+        <v>3.5</v>
       </c>
       <c r="P18" t="n">
-        <v>1.13</v>
+        <v>2.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>14.5</v>
+        <v>2.8</v>
       </c>
       <c r="R18" t="n">
-        <v>2.78</v>
+        <v>2.13</v>
       </c>
       <c r="S18" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="T18" t="n">
-        <v>3.34</v>
+        <v>2.87</v>
       </c>
       <c r="U18" t="n">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="V18" t="n">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.75</v>
+        <v>3.62</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.47</v>
+        <v>1.71</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.38</v>
+        <v>2.03</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.26</v>
+        <v>2.71</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AE18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18" t="n">
         <v>1.22</v>
       </c>
-      <c r="AF18" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AK18" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.31</v>
+        <v>12</v>
       </c>
       <c r="O19" t="n">
-        <v>3.14</v>
+        <v>7.6</v>
       </c>
       <c r="P19" t="n">
-        <v>2.56</v>
+        <v>1.11</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.99</v>
+        <v>11.12</v>
       </c>
       <c r="R19" t="n">
-        <v>2.12</v>
+        <v>3.03</v>
       </c>
       <c r="S19" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="T19" t="n">
-        <v>2.94</v>
+        <v>3.45</v>
       </c>
       <c r="U19" t="n">
-        <v>2.58</v>
+        <v>2.2</v>
       </c>
       <c r="V19" t="n">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AE19" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z19" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AF19" t="n">
-        <v>1.59</v>
+        <v>2.62</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.18</v>
+        <v>1.36</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.3</v>
+        <v>5.5</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3749,16 +3749,16 @@
         <v>2.3</v>
       </c>
       <c r="O21" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="P21" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q21" t="n">
         <v>3.1</v>
       </c>
       <c r="R21" t="n">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="S21" t="n">
         <v>1.62</v>
@@ -3767,10 +3767,10 @@
         <v>2.25</v>
       </c>
       <c r="U21" t="n">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="V21" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="W21" t="n">
         <v>1.01</v>
@@ -3785,7 +3785,7 @@
         <v>2.23</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="AB21" t="n">
         <v>1.36</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4394,19 +4394,19 @@
         <v>2</v>
       </c>
       <c r="R25" t="n">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="S25" t="n">
         <v>1.27</v>
       </c>
       <c r="T25" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U25" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="V25" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="W25" t="n">
         <v>1.15</v>
@@ -4418,13 +4418,13 @@
         <v>1.12</v>
       </c>
       <c r="Z25" t="n">
-        <v>5</v>
+        <v>4.65</v>
       </c>
       <c r="AA25" t="n">
         <v>1.55</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="AC25" t="n">
         <v>2.3</v>
@@ -4433,7 +4433,7 @@
         <v>1.48</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AF25" t="n">
         <v>1.59</v>

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.35</v>
+        <v>1.64</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="P8" t="n">
-        <v>2.65</v>
+        <v>4.05</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.72</v>
+        <v>2.1</v>
       </c>
       <c r="R8" t="n">
-        <v>2.09</v>
+        <v>2.47</v>
       </c>
       <c r="S8" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="T8" t="n">
-        <v>2.89</v>
+        <v>3.07</v>
       </c>
       <c r="U8" t="n">
-        <v>2.73</v>
+        <v>2.29</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.44</v>
+        <v>4.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.12</v>
+        <v>2.38</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.52</v>
+        <v>2.1</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.64</v>
+        <v>2.35</v>
       </c>
       <c r="O10" t="n">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="P10" t="n">
-        <v>4.05</v>
+        <v>2.65</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.1</v>
+        <v>2.72</v>
       </c>
       <c r="R10" t="n">
-        <v>2.47</v>
+        <v>2.09</v>
       </c>
       <c r="S10" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="T10" t="n">
-        <v>3.07</v>
+        <v>2.89</v>
       </c>
       <c r="U10" t="n">
-        <v>2.29</v>
+        <v>2.73</v>
       </c>
       <c r="V10" t="n">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="W10" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.6</v>
+        <v>3.44</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.38</v>
+        <v>3.12</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.1</v>
+        <v>1.52</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.11</v>
+        <v>1.64</v>
       </c>
       <c r="O7" t="n">
-        <v>7</v>
+        <v>3.85</v>
       </c>
       <c r="P7" t="n">
-        <v>14</v>
+        <v>4.05</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.47</v>
+        <v>2.1</v>
       </c>
       <c r="R7" t="n">
-        <v>2.82</v>
+        <v>2.47</v>
       </c>
       <c r="S7" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T7" t="n">
-        <v>3.45</v>
+        <v>3.07</v>
       </c>
       <c r="U7" t="n">
-        <v>2.06</v>
+        <v>2.29</v>
       </c>
       <c r="V7" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="W7" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X7" t="n">
         <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.25</v>
+        <v>4.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.15</v>
+        <v>1.59</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.63</v>
+        <v>2.25</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="AK7" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.64</v>
+        <v>1.11</v>
       </c>
       <c r="O8" t="n">
-        <v>3.85</v>
+        <v>7</v>
       </c>
       <c r="P8" t="n">
-        <v>4.05</v>
+        <v>14</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.1</v>
+        <v>1.47</v>
       </c>
       <c r="R8" t="n">
-        <v>2.47</v>
+        <v>2.82</v>
       </c>
       <c r="S8" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T8" t="n">
-        <v>3.07</v>
+        <v>3.45</v>
       </c>
       <c r="U8" t="n">
-        <v>2.29</v>
+        <v>2.06</v>
       </c>
       <c r="V8" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="W8" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X8" t="n">
         <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.6</v>
+        <v>5.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.38</v>
+        <v>2.12</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.59</v>
+        <v>2.15</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.25</v>
+        <v>1.63</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.1</v>
+        <v>4.5</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>4.2</v>
+        <v>2.35</v>
       </c>
       <c r="O9" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>1.72</v>
+        <v>2.65</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.1</v>
+        <v>2.72</v>
       </c>
       <c r="R9" t="n">
-        <v>2.21</v>
+        <v>2.09</v>
       </c>
       <c r="S9" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="T9" t="n">
-        <v>3.15</v>
+        <v>2.89</v>
       </c>
       <c r="U9" t="n">
-        <v>2.41</v>
+        <v>2.73</v>
       </c>
       <c r="V9" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W9" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.05</v>
+        <v>3.44</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.69</v>
+        <v>1.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.57</v>
+        <v>3.12</v>
       </c>
       <c r="AD9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
         <v>1.4</v>
       </c>
-      <c r="AE9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AK9" t="n">
-        <v>1.26</v>
+        <v>1.52</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.35</v>
+        <v>4.2</v>
       </c>
       <c r="O10" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P10" t="n">
-        <v>2.65</v>
+        <v>1.72</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.72</v>
+        <v>4.1</v>
       </c>
       <c r="R10" t="n">
-        <v>2.09</v>
+        <v>2.21</v>
       </c>
       <c r="S10" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="T10" t="n">
-        <v>2.89</v>
+        <v>3.15</v>
       </c>
       <c r="U10" t="n">
-        <v>2.73</v>
+        <v>2.41</v>
       </c>
       <c r="V10" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.44</v>
+        <v>4.05</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.9</v>
+        <v>1.69</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.9</v>
+        <v>2.11</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.12</v>
+        <v>2.57</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.52</v>
+        <v>1.26</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,65 +3269,65 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.4</v>
+        <v>12</v>
       </c>
       <c r="O18" t="n">
-        <v>3.5</v>
+        <v>7.6</v>
       </c>
       <c r="P18" t="n">
-        <v>2.8</v>
+        <v>1.11</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.8</v>
+        <v>11.12</v>
       </c>
       <c r="R18" t="n">
-        <v>2.13</v>
+        <v>3.03</v>
       </c>
       <c r="S18" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="T18" t="n">
-        <v>2.87</v>
+        <v>3.45</v>
       </c>
       <c r="U18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB18" t="n">
         <v>2.5</v>
       </c>
-      <c r="V18" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.03</v>
-      </c>
       <c r="AC18" t="n">
-        <v>2.71</v>
+        <v>2.16</v>
       </c>
       <c r="AD18" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.36</v>
       </c>
-      <c r="AE18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.21</v>
-      </c>
       <c r="AH18" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.22</v>
+        <v>5.5</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,80 +3428,80 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>12</v>
+        <v>2.4</v>
       </c>
       <c r="O19" t="n">
-        <v>7.6</v>
+        <v>3.5</v>
       </c>
       <c r="P19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE19" t="n">
         <v>1.11</v>
       </c>
-      <c r="Q19" t="n">
-        <v>11.12</v>
-      </c>
-      <c r="R19" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AE19" t="n">
+      <c r="AF19" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19" t="n">
         <v>1.22</v>
       </c>
-      <c r="AF19" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AK19" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G24" t="n">

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.25</v>
+        <v>2.03</v>
       </c>
       <c r="O4" t="n">
-        <v>2.95</v>
+        <v>3.55</v>
       </c>
       <c r="P4" t="n">
-        <v>2.15</v>
+        <v>3.8</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.64</v>
+        <v>4.2</v>
       </c>
       <c r="O7" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>4.05</v>
+        <v>1.72</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.1</v>
+        <v>4.1</v>
       </c>
       <c r="R7" t="n">
-        <v>2.47</v>
+        <v>2.21</v>
       </c>
       <c r="S7" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="T7" t="n">
-        <v>3.07</v>
+        <v>3.15</v>
       </c>
       <c r="U7" t="n">
-        <v>2.29</v>
+        <v>2.41</v>
       </c>
       <c r="V7" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
         <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.6</v>
+        <v>4.05</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.38</v>
+        <v>2.57</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.1</v>
+        <v>1.26</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.11</v>
+        <v>2.35</v>
       </c>
       <c r="O8" t="n">
-        <v>7</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>14</v>
+        <v>2.65</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.47</v>
+        <v>2.72</v>
       </c>
       <c r="R8" t="n">
-        <v>2.82</v>
+        <v>2.09</v>
       </c>
       <c r="S8" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="T8" t="n">
-        <v>3.45</v>
+        <v>2.89</v>
       </c>
       <c r="U8" t="n">
-        <v>2.06</v>
+        <v>2.73</v>
       </c>
       <c r="V8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF8" t="n">
         <v>1.67</v>
       </c>
-      <c r="W8" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AG8" t="n">
-        <v>1.63</v>
+        <v>2.08</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.03</v>
+        <v>1.4</v>
       </c>
       <c r="AK8" t="n">
-        <v>4.5</v>
+        <v>1.52</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.35</v>
+        <v>1.64</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="P9" t="n">
-        <v>2.65</v>
+        <v>4.05</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.72</v>
+        <v>2.1</v>
       </c>
       <c r="R9" t="n">
-        <v>2.09</v>
+        <v>2.47</v>
       </c>
       <c r="S9" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="T9" t="n">
-        <v>2.89</v>
+        <v>3.07</v>
       </c>
       <c r="U9" t="n">
-        <v>2.73</v>
+        <v>2.29</v>
       </c>
       <c r="V9" t="n">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.44</v>
+        <v>4.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.12</v>
+        <v>2.38</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.52</v>
+        <v>2.1</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>4.2</v>
+        <v>1.11</v>
       </c>
       <c r="O10" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="P10" t="n">
-        <v>1.72</v>
+        <v>14</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.1</v>
+        <v>1.47</v>
       </c>
       <c r="R10" t="n">
-        <v>2.21</v>
+        <v>2.82</v>
       </c>
       <c r="S10" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T10" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="U10" t="n">
-        <v>2.41</v>
+        <v>2.06</v>
       </c>
       <c r="V10" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.05</v>
+        <v>5.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.69</v>
+        <v>1.48</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.11</v>
+        <v>2.55</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.57</v>
+        <v>2.12</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.58</v>
+        <v>2.15</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.23</v>
+        <v>1.63</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.26</v>
+        <v>1.03</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.26</v>
+        <v>4.5</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2159,7 +2159,7 @@
         <v>2.02</v>
       </c>
       <c r="O11" t="n">
-        <v>3.24</v>
+        <v>3.5</v>
       </c>
       <c r="P11" t="n">
         <v>3.45</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>3.25</v>
+        <v>1.27</v>
       </c>
       <c r="O14" t="n">
-        <v>3.55</v>
+        <v>6</v>
       </c>
       <c r="P14" t="n">
-        <v>1.94</v>
+        <v>11</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.74</v>
+        <v>1.65</v>
       </c>
       <c r="R14" t="n">
-        <v>2.35</v>
+        <v>2.78</v>
       </c>
       <c r="S14" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="T14" t="n">
-        <v>3.15</v>
+        <v>3.34</v>
       </c>
       <c r="U14" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="V14" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.05</v>
+        <v>4.45</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.12</v>
+        <v>2.43</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.48</v>
+        <v>2.31</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.57</v>
+        <v>2.03</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.28</v>
+        <v>3.78</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.27</v>
+        <v>3.25</v>
       </c>
       <c r="O15" t="n">
-        <v>6</v>
+        <v>3.55</v>
       </c>
       <c r="P15" t="n">
-        <v>11</v>
+        <v>1.94</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.65</v>
+        <v>3.74</v>
       </c>
       <c r="R15" t="n">
-        <v>2.78</v>
+        <v>2.35</v>
       </c>
       <c r="S15" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="T15" t="n">
-        <v>3.34</v>
+        <v>3.15</v>
       </c>
       <c r="U15" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="V15" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="W15" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE15" t="n">
         <v>1.14</v>
       </c>
-      <c r="Z15" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AF15" t="n">
-        <v>2.03</v>
+        <v>1.57</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="AK15" t="n">
-        <v>3.78</v>
+        <v>1.28</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>4.2</v>
+        <v>1.62</v>
       </c>
       <c r="O7" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="P7" t="n">
-        <v>1.72</v>
+        <v>4.44</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="R7" t="n">
-        <v>2.21</v>
+        <v>2.46</v>
       </c>
       <c r="S7" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T7" t="n">
-        <v>3.15</v>
+        <v>3.07</v>
       </c>
       <c r="U7" t="n">
-        <v>2.41</v>
+        <v>2.26</v>
       </c>
       <c r="V7" t="n">
         <v>1.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
         <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.05</v>
+        <v>4.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.57</v>
+        <v>2.39</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.26</v>
+        <v>2.1</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.35</v>
+        <v>4.2</v>
       </c>
       <c r="O8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T8" t="n">
         <v>3.3</v>
       </c>
-      <c r="P8" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.89</v>
-      </c>
       <c r="U8" t="n">
-        <v>2.73</v>
+        <v>2.41</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W8" t="n">
         <v>1.1</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.44</v>
+        <v>4.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.9</v>
+        <v>1.69</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>2.13</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.12</v>
+        <v>2.55</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.4</v>
+        <v>1.81</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.52</v>
+        <v>1.19</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.64</v>
+        <v>1.11</v>
       </c>
       <c r="O9" t="n">
-        <v>3.85</v>
+        <v>7</v>
       </c>
       <c r="P9" t="n">
-        <v>4.05</v>
+        <v>14</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="R9" t="n">
-        <v>2.47</v>
+        <v>2.89</v>
       </c>
       <c r="S9" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T9" t="n">
-        <v>3.07</v>
+        <v>4</v>
       </c>
       <c r="U9" t="n">
-        <v>2.29</v>
+        <v>2.18</v>
       </c>
       <c r="V9" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="W9" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X9" t="n">
         <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.6</v>
+        <v>5.15</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.59</v>
+        <v>2.15</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.25</v>
+        <v>1.63</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.1</v>
+        <v>4.85</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.11</v>
+        <v>2.33</v>
       </c>
       <c r="O10" t="n">
-        <v>7</v>
+        <v>3.34</v>
       </c>
       <c r="P10" t="n">
-        <v>14</v>
+        <v>2.95</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.47</v>
+        <v>2.9</v>
       </c>
       <c r="R10" t="n">
-        <v>2.82</v>
+        <v>2.09</v>
       </c>
       <c r="S10" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="T10" t="n">
-        <v>3.45</v>
+        <v>2.73</v>
       </c>
       <c r="U10" t="n">
-        <v>2.06</v>
+        <v>2.73</v>
       </c>
       <c r="V10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF10" t="n">
         <v>1.67</v>
       </c>
-      <c r="W10" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AG10" t="n">
-        <v>1.63</v>
+        <v>2.05</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.03</v>
+        <v>1.4</v>
       </c>
       <c r="AK10" t="n">
-        <v>4.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="O11" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="P11" t="n">
         <v>3.5</v>
       </c>
-      <c r="P11" t="n">
-        <v>3.45</v>
-      </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.61</v>
+        <v>2.24</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.25</v>
+        <v>1.56</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="O12" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P12" t="n">
         <v>3.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.33</v>
+        <v>1.61</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.61</v>
+        <v>2.25</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.37</v>
+        <v>3.05</v>
       </c>
       <c r="O13" t="n">
-        <v>2.61</v>
+        <v>3.7</v>
       </c>
       <c r="P13" t="n">
-        <v>3.25</v>
+        <v>1.96</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="R13" t="n">
-        <v>1.66</v>
+        <v>2.28</v>
       </c>
       <c r="S13" t="n">
-        <v>1.74</v>
+        <v>1.29</v>
       </c>
       <c r="T13" t="n">
-        <v>2.08</v>
+        <v>3.4</v>
       </c>
       <c r="U13" t="n">
-        <v>4.25</v>
+        <v>2.34</v>
       </c>
       <c r="V13" t="n">
-        <v>1.2</v>
+        <v>1.53</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X13" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.71</v>
+        <v>1.16</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.1</v>
+        <v>4.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.04</v>
+        <v>1.65</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.29</v>
+        <v>2.19</v>
       </c>
       <c r="AC13" t="n">
-        <v>7</v>
+        <v>2.48</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.06</v>
+        <v>1.43</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.4</v>
+        <v>1.55</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2633,10 +2633,10 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="O14" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="P14" t="n">
         <v>11</v>
@@ -2648,10 +2648,10 @@
         <v>2.78</v>
       </c>
       <c r="S14" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="T14" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="U14" t="n">
         <v>2.21</v>
@@ -2672,25 +2672,25 @@
         <v>4.45</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="AD14" t="n">
         <v>1.56</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="P15" t="n">
         <v>3.25</v>
       </c>
-      <c r="O15" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.94</v>
-      </c>
       <c r="Q15" t="n">
-        <v>3.74</v>
+        <v>3.3</v>
       </c>
       <c r="R15" t="n">
-        <v>2.35</v>
+        <v>1.66</v>
       </c>
       <c r="S15" t="n">
-        <v>1.31</v>
+        <v>1.74</v>
       </c>
       <c r="T15" t="n">
-        <v>3.15</v>
+        <v>2.08</v>
       </c>
       <c r="U15" t="n">
-        <v>2.3</v>
+        <v>4.25</v>
       </c>
       <c r="V15" t="n">
-        <v>1.52</v>
+        <v>1.2</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.18</v>
+        <v>1.71</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.05</v>
+        <v>2.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.66</v>
+        <v>3.04</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.12</v>
+        <v>1.29</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.48</v>
+        <v>7</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.43</v>
+        <v>1.06</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.57</v>
+        <v>2.4</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2957,7 +2957,7 @@
         <v>3.6</v>
       </c>
       <c r="P16" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q16" t="n">
         <v>2.41</v>
@@ -2966,13 +2966,13 @@
         <v>2.16</v>
       </c>
       <c r="S16" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T16" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="U16" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="V16" t="n">
         <v>1.45</v>
@@ -2987,28 +2987,28 @@
         <v>1.22</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.8</v>
+        <v>3.54</v>
       </c>
       <c r="AA16" t="n">
         <v>1.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.34</v>
+        <v>2.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AF16" t="n">
         <v>1.67</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="O17" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="P17" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Q17" t="n">
         <v>3.1</v>
       </c>
-      <c r="P17" t="n">
+      <c r="R17" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U17" t="n">
         <v>3.13</v>
       </c>
-      <c r="Q17" t="n">
-        <v>3</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U17" t="n">
-        <v>3.05</v>
-      </c>
       <c r="V17" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="W17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X17" t="n">
         <v>1.05</v>
       </c>
-      <c r="X17" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y17" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.68</v>
+        <v>2.48</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.33</v>
+        <v>2.46</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,65 +3269,65 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>12</v>
+        <v>2.3</v>
       </c>
       <c r="O18" t="n">
-        <v>7.6</v>
+        <v>3.5</v>
       </c>
       <c r="P18" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W18" t="n">
         <v>1.11</v>
       </c>
-      <c r="Q18" t="n">
-        <v>11.12</v>
-      </c>
-      <c r="R18" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="U18" t="n">
+      <c r="X18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG18" t="n">
         <v>2.2</v>
       </c>
-      <c r="V18" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH18" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>5.5</v>
+        <v>1.28</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.4</v>
+        <v>16</v>
       </c>
       <c r="O19" t="n">
-        <v>3.5</v>
+        <v>7.45</v>
       </c>
       <c r="P19" t="n">
-        <v>2.8</v>
+        <v>1.11</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.8</v>
+        <v>13</v>
       </c>
       <c r="R19" t="n">
-        <v>2.13</v>
+        <v>3</v>
       </c>
       <c r="S19" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="T19" t="n">
-        <v>2.87</v>
+        <v>3.7</v>
       </c>
       <c r="U19" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="V19" t="n">
-        <v>1.47</v>
+        <v>1.64</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.62</v>
+        <v>4.95</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.71</v>
+        <v>1.44</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.03</v>
+        <v>2.53</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.71</v>
+        <v>2.17</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.59</v>
+        <v>2.51</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.21</v>
+        <v>1.46</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.22</v>
+        <v>5.7</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.55</v>
+        <v>1.02</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O2" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>4.2</v>
+        <v>2.33</v>
       </c>
       <c r="O8" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="P8" t="n">
-        <v>1.72</v>
+        <v>2.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="S8" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="T8" t="n">
-        <v>3.3</v>
+        <v>2.73</v>
       </c>
       <c r="U8" t="n">
-        <v>2.41</v>
+        <v>2.73</v>
       </c>
       <c r="V8" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W8" t="n">
         <v>1.1</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.2</v>
+        <v>3.44</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.69</v>
+        <v>1.89</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.55</v>
+        <v>3.12</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.81</v>
+        <v>1.4</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.19</v>
+        <v>1.57</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,65 +1838,65 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.11</v>
+        <v>4.2</v>
       </c>
       <c r="O9" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="P9" t="n">
-        <v>14</v>
+        <v>1.72</v>
       </c>
       <c r="Q9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="V9" t="n">
         <v>1.5</v>
       </c>
-      <c r="R9" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T9" t="n">
-        <v>4</v>
-      </c>
-      <c r="U9" t="n">
+      <c r="W9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AG9" t="n">
         <v>2.18</v>
       </c>
-      <c r="V9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.08</v>
+        <v>1.81</v>
       </c>
       <c r="AK9" t="n">
-        <v>4.85</v>
+        <v>1.19</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.33</v>
+        <v>1.11</v>
       </c>
       <c r="O10" t="n">
-        <v>3.34</v>
+        <v>7</v>
       </c>
       <c r="P10" t="n">
-        <v>2.95</v>
+        <v>14</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="R10" t="n">
-        <v>2.09</v>
+        <v>2.89</v>
       </c>
       <c r="S10" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T10" t="n">
-        <v>2.73</v>
+        <v>4</v>
       </c>
       <c r="U10" t="n">
-        <v>2.73</v>
+        <v>2.18</v>
       </c>
       <c r="V10" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.44</v>
+        <v>5.15</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.89</v>
+        <v>1.47</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.89</v>
+        <v>2.44</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.12</v>
+        <v>2.08</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.28</v>
+        <v>1.68</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.05</v>
+        <v>1.63</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.4</v>
+        <v>1.08</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.57</v>
+        <v>4.85</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3.05</v>
+        <v>2.33</v>
       </c>
       <c r="O13" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="P13" t="n">
-        <v>1.96</v>
+        <v>3.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.9</v>
+        <v>3.38</v>
       </c>
       <c r="R13" t="n">
-        <v>2.28</v>
+        <v>1.66</v>
       </c>
       <c r="S13" t="n">
-        <v>1.29</v>
+        <v>1.74</v>
       </c>
       <c r="T13" t="n">
-        <v>3.4</v>
+        <v>2.08</v>
       </c>
       <c r="U13" t="n">
-        <v>2.34</v>
+        <v>4.25</v>
       </c>
       <c r="V13" t="n">
-        <v>1.53</v>
+        <v>1.15</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.16</v>
+        <v>1.71</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.65</v>
+        <v>3.04</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.19</v>
+        <v>1.33</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.48</v>
+        <v>7</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.43</v>
+        <v>1.06</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.55</v>
+        <v>2.4</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.37</v>
+        <v>3.05</v>
       </c>
       <c r="O15" t="n">
-        <v>2.61</v>
+        <v>3.7</v>
       </c>
       <c r="P15" t="n">
-        <v>3.25</v>
+        <v>1.96</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="R15" t="n">
-        <v>1.66</v>
+        <v>2.28</v>
       </c>
       <c r="S15" t="n">
-        <v>1.74</v>
+        <v>1.29</v>
       </c>
       <c r="T15" t="n">
-        <v>2.08</v>
+        <v>3.4</v>
       </c>
       <c r="U15" t="n">
-        <v>4.25</v>
+        <v>2.34</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2</v>
+        <v>1.53</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X15" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.71</v>
+        <v>1.16</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.1</v>
+        <v>4.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.04</v>
+        <v>1.65</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.29</v>
+        <v>2.19</v>
       </c>
       <c r="AC15" t="n">
-        <v>7</v>
+        <v>2.48</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.06</v>
+        <v>1.43</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.4</v>
+        <v>1.55</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3749,25 +3749,25 @@
         <v>2.3</v>
       </c>
       <c r="O21" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="P21" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q21" t="n">
         <v>3.1</v>
       </c>
       <c r="R21" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="S21" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="T21" t="n">
         <v>2.25</v>
       </c>
       <c r="U21" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="V21" t="n">
         <v>1.19</v>
@@ -3782,28 +3782,28 @@
         <v>1.58</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AC21" t="n">
-        <v>5.3</v>
+        <v>5.75</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AE21" t="n">
         <v>1.03</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3914,55 +3914,55 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK26" t="n">
         <v>1.52</v>

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>3.2</v>
+        <v>1.91</v>
       </c>
       <c r="O2" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R2" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2.03</v>
-      </c>
       <c r="S2" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="T2" t="n">
-        <v>2.41</v>
+        <v>2.73</v>
       </c>
       <c r="U2" t="n">
-        <v>3.48</v>
+        <v>2.95</v>
       </c>
       <c r="V2" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE2" t="n">
         <v>1.06</v>
       </c>
-      <c r="Y2" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AF2" t="n">
-        <v>2.02</v>
+        <v>1.79</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.71</v>
+        <v>1.92</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.29</v>
+        <v>1.82</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>2.55</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="T3" t="n">
-        <v>2.73</v>
+        <v>2.53</v>
       </c>
       <c r="U3" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="V3" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="W3" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.41</v>
+        <v>3.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.4</v>
+        <v>3.91</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.82</v>
+        <v>1.62</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.55</v>
+        <v>4.4</v>
       </c>
       <c r="R4" t="n">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="S4" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="T4" t="n">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="U4" t="n">
-        <v>3.1</v>
+        <v>3.48</v>
       </c>
       <c r="V4" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="W4" t="n">
         <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.1</v>
+        <v>2.72</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.06</v>
+        <v>2.46</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.72</v>
+        <v>1.56</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.91</v>
+        <v>4.73</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>4.2</v>
+        <v>1.11</v>
       </c>
       <c r="O9" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="P9" t="n">
-        <v>1.72</v>
+        <v>14</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3</v>
+        <v>2.89</v>
       </c>
       <c r="S9" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T9" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="U9" t="n">
-        <v>2.41</v>
+        <v>2.18</v>
       </c>
       <c r="V9" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1.2</v>
       </c>
-      <c r="Z9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AF9" t="n">
-        <v>1.59</v>
+        <v>2.15</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.18</v>
+        <v>1.63</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.81</v>
+        <v>1.08</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.19</v>
+        <v>4.85</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,65 +1997,65 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.11</v>
+        <v>4.2</v>
       </c>
       <c r="O10" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="P10" t="n">
-        <v>14</v>
+        <v>1.72</v>
       </c>
       <c r="Q10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="V10" t="n">
         <v>1.5</v>
       </c>
-      <c r="R10" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T10" t="n">
-        <v>4</v>
-      </c>
-      <c r="U10" t="n">
+      <c r="W10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AG10" t="n">
         <v>2.18</v>
       </c>
-      <c r="V10" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AH10" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.08</v>
+        <v>1.81</v>
       </c>
       <c r="AK10" t="n">
-        <v>4.85</v>
+        <v>1.19</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.33</v>
+        <v>3.05</v>
       </c>
       <c r="O13" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="P13" t="n">
-        <v>3.2</v>
+        <v>1.96</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.38</v>
+        <v>3.9</v>
       </c>
       <c r="R13" t="n">
-        <v>1.66</v>
+        <v>2.28</v>
       </c>
       <c r="S13" t="n">
-        <v>1.74</v>
+        <v>1.29</v>
       </c>
       <c r="T13" t="n">
-        <v>2.08</v>
+        <v>3.4</v>
       </c>
       <c r="U13" t="n">
-        <v>4.25</v>
+        <v>2.34</v>
       </c>
       <c r="V13" t="n">
-        <v>1.15</v>
+        <v>1.53</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X13" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.71</v>
+        <v>1.16</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.1</v>
+        <v>4.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.04</v>
+        <v>1.65</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.33</v>
+        <v>2.19</v>
       </c>
       <c r="AC13" t="n">
-        <v>7</v>
+        <v>2.48</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.06</v>
+        <v>1.43</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.4</v>
+        <v>1.55</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.25</v>
+        <v>2.13</v>
       </c>
       <c r="O14" t="n">
-        <v>5.7</v>
+        <v>2.5</v>
       </c>
       <c r="P14" t="n">
-        <v>11</v>
+        <v>4.04</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.65</v>
+        <v>3.38</v>
       </c>
       <c r="R14" t="n">
-        <v>2.78</v>
+        <v>1.66</v>
       </c>
       <c r="S14" t="n">
-        <v>1.29</v>
+        <v>1.75</v>
       </c>
       <c r="T14" t="n">
-        <v>3.2</v>
+        <v>2.08</v>
       </c>
       <c r="U14" t="n">
-        <v>2.21</v>
+        <v>4.25</v>
       </c>
       <c r="V14" t="n">
-        <v>1.57</v>
+        <v>1.15</v>
       </c>
       <c r="W14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X14" t="n">
         <v>1.13</v>
       </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y14" t="n">
-        <v>1.14</v>
+        <v>1.71</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.45</v>
+        <v>2.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.66</v>
+        <v>3.05</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.27</v>
+        <v>1.36</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.34</v>
+        <v>6.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.56</v>
+        <v>1.06</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.8</v>
+        <v>1.45</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>3.05</v>
+        <v>1.25</v>
       </c>
       <c r="O15" t="n">
-        <v>3.7</v>
+        <v>5.7</v>
       </c>
       <c r="P15" t="n">
-        <v>1.96</v>
+        <v>11</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.9</v>
+        <v>1.65</v>
       </c>
       <c r="R15" t="n">
-        <v>2.28</v>
+        <v>2.78</v>
       </c>
       <c r="S15" t="n">
         <v>1.29</v>
       </c>
       <c r="T15" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="U15" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AC15" t="n">
         <v>2.34</v>
       </c>
-      <c r="V15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.48</v>
-      </c>
       <c r="AD15" t="n">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="AE15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
         <v>1.14</v>
       </c>
-      <c r="AF15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AK15" t="n">
-        <v>1.25</v>
+        <v>3.8</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.3</v>
+        <v>16</v>
       </c>
       <c r="O18" t="n">
-        <v>3.5</v>
+        <v>7.45</v>
       </c>
       <c r="P18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>13</v>
+      </c>
+      <c r="R18" t="n">
         <v>3</v>
       </c>
-      <c r="Q18" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.2</v>
-      </c>
       <c r="S18" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T18" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="U18" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="V18" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AA18" t="n">
         <v>1.44</v>
       </c>
-      <c r="W18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y18" t="n">
+      <c r="AB18" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AE18" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z18" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AF18" t="n">
-        <v>1.57</v>
+        <v>2.51</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.2</v>
+        <v>1.46</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.28</v>
+        <v>5.7</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.57</v>
+        <v>1.02</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>16</v>
+        <v>2.3</v>
       </c>
       <c r="O19" t="n">
-        <v>7.45</v>
+        <v>3.5</v>
       </c>
       <c r="P19" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W19" t="n">
         <v>1.11</v>
       </c>
-      <c r="Q19" t="n">
-        <v>13</v>
-      </c>
-      <c r="R19" t="n">
-        <v>3</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.17</v>
-      </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE19" t="n">
         <v>1.11</v>
       </c>
-      <c r="Z19" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AF19" t="n">
-        <v>2.51</v>
+        <v>1.57</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.46</v>
+        <v>2.2</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>5.7</v>
+        <v>1.28</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.02</v>
+        <v>1.57</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3752,7 +3752,7 @@
         <v>2.75</v>
       </c>
       <c r="P21" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q21" t="n">
         <v>3.1</v>
@@ -3767,7 +3767,7 @@
         <v>2.25</v>
       </c>
       <c r="U21" t="n">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="V21" t="n">
         <v>1.19</v>
@@ -3800,7 +3800,7 @@
         <v>1.03</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AG21" t="n">
         <v>1.62</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="R22" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="S22" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="T22" t="n">
-        <v>2.44</v>
+        <v>3.07</v>
       </c>
       <c r="U22" t="n">
-        <v>3.1</v>
+        <v>2.59</v>
       </c>
       <c r="V22" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="W22" t="n">
         <v>1.04</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.78</v>
+        <v>3.38</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.26</v>
+        <v>1.94</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4073,55 +4073,55 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK26" t="n">
         <v>1.52</v>

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,80 +725,80 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.91</v>
+        <v>3.2</v>
       </c>
       <c r="O2" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.55</v>
+        <v>4.4</v>
       </c>
       <c r="R2" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="T2" t="n">
-        <v>2.73</v>
+        <v>2.41</v>
       </c>
       <c r="U2" t="n">
-        <v>2.95</v>
+        <v>3.48</v>
       </c>
       <c r="V2" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="W2" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.41</v>
+        <v>2.72</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.95</v>
+        <v>2.46</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.82</v>
+        <v>1.56</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.4</v>
+        <v>4.73</v>
       </c>
       <c r="AD2" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK2" t="n">
         <v>1.29</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1.82</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q3" t="n">
         <v>2.55</v>
       </c>
       <c r="R3" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S3" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T3" t="n">
-        <v>2.53</v>
+        <v>2.73</v>
       </c>
       <c r="U3" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="V3" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.1</v>
+        <v>3.41</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.91</v>
+        <v>3.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.4</v>
+        <v>2.55</v>
       </c>
       <c r="R4" t="n">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="T4" t="n">
-        <v>2.41</v>
+        <v>2.53</v>
       </c>
       <c r="U4" t="n">
-        <v>3.48</v>
+        <v>3.1</v>
       </c>
       <c r="V4" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="W4" t="n">
         <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.72</v>
+        <v>3.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.46</v>
+        <v>2.06</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.56</v>
+        <v>1.72</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.73</v>
+        <v>3.91</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.33</v>
+        <v>4.2</v>
       </c>
       <c r="O8" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>2.95</v>
+        <v>1.72</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="R8" t="n">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="S8" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="T8" t="n">
-        <v>2.73</v>
+        <v>3.3</v>
       </c>
       <c r="U8" t="n">
-        <v>2.73</v>
+        <v>2.41</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W8" t="n">
         <v>1.1</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.44</v>
+        <v>4.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.89</v>
+        <v>1.69</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.89</v>
+        <v>2.13</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.12</v>
+        <v>2.55</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.4</v>
+        <v>1.81</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.57</v>
+        <v>1.19</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.11</v>
+        <v>2.33</v>
       </c>
       <c r="O9" t="n">
-        <v>7</v>
+        <v>3.34</v>
       </c>
       <c r="P9" t="n">
-        <v>14</v>
+        <v>2.95</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="R9" t="n">
-        <v>2.89</v>
+        <v>2.09</v>
       </c>
       <c r="S9" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="T9" t="n">
-        <v>4</v>
+        <v>2.73</v>
       </c>
       <c r="U9" t="n">
-        <v>2.18</v>
+        <v>2.73</v>
       </c>
       <c r="V9" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="W9" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.15</v>
+        <v>3.44</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.47</v>
+        <v>1.89</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.44</v>
+        <v>1.89</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.08</v>
+        <v>3.12</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.68</v>
+        <v>1.28</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.63</v>
+        <v>2.05</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.08</v>
+        <v>1.4</v>
       </c>
       <c r="AK9" t="n">
-        <v>4.85</v>
+        <v>1.57</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>4.2</v>
+        <v>1.11</v>
       </c>
       <c r="O10" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="P10" t="n">
-        <v>1.72</v>
+        <v>14</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3</v>
+        <v>2.89</v>
       </c>
       <c r="S10" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T10" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="U10" t="n">
-        <v>2.41</v>
+        <v>2.18</v>
       </c>
       <c r="V10" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.2</v>
       </c>
-      <c r="Z10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AF10" t="n">
-        <v>1.59</v>
+        <v>2.15</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.18</v>
+        <v>1.63</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.81</v>
+        <v>1.08</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.19</v>
+        <v>4.85</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="O11" t="n">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="P11" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.24</v>
+        <v>1.61</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.56</v>
+        <v>2.25</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="O12" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="P12" t="n">
         <v>3.5</v>
       </c>
-      <c r="P12" t="n">
-        <v>3.6</v>
-      </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.61</v>
+        <v>2.24</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.25</v>
+        <v>1.56</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,80 +2474,80 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3.05</v>
+        <v>1.25</v>
       </c>
       <c r="O13" t="n">
-        <v>3.7</v>
+        <v>5.7</v>
       </c>
       <c r="P13" t="n">
-        <v>1.96</v>
+        <v>11</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.9</v>
+        <v>1.65</v>
       </c>
       <c r="R13" t="n">
-        <v>2.28</v>
+        <v>2.78</v>
       </c>
       <c r="S13" t="n">
         <v>1.29</v>
       </c>
       <c r="T13" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="U13" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AC13" t="n">
         <v>2.34</v>
       </c>
-      <c r="V13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.48</v>
-      </c>
       <c r="AD13" t="n">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="AE13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
         <v>1.14</v>
       </c>
-      <c r="AF13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AK13" t="n">
-        <v>1.25</v>
+        <v>3.8</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.25</v>
+        <v>3.05</v>
       </c>
       <c r="O15" t="n">
-        <v>5.7</v>
+        <v>3.7</v>
       </c>
       <c r="P15" t="n">
-        <v>11</v>
+        <v>1.96</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.65</v>
+        <v>3.9</v>
       </c>
       <c r="R15" t="n">
-        <v>2.78</v>
+        <v>2.28</v>
       </c>
       <c r="S15" t="n">
         <v>1.29</v>
       </c>
       <c r="T15" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="U15" t="n">
-        <v>2.21</v>
+        <v>2.34</v>
       </c>
       <c r="V15" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W15" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE15" t="n">
         <v>1.14</v>
       </c>
-      <c r="Z15" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AF15" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.14</v>
+        <v>1.73</v>
       </c>
       <c r="AK15" t="n">
-        <v>3.8</v>
+        <v>1.25</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="O22" t="n">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="P22" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
         <v>2.2</v>
       </c>
-      <c r="S22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.94</v>
-      </c>
       <c r="AB22" t="n">
-        <v>1.9</v>
+        <v>1.58</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="O27" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P27" t="n">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>3.2</v>
+        <v>1.93</v>
       </c>
       <c r="O2" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="P2" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.4</v>
+        <v>2.48</v>
       </c>
       <c r="R2" t="n">
-        <v>2.03</v>
+        <v>2.11</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="T2" t="n">
-        <v>2.41</v>
+        <v>2.8</v>
       </c>
       <c r="U2" t="n">
-        <v>3.48</v>
+        <v>2.92</v>
       </c>
       <c r="V2" t="n">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.72</v>
+        <v>3.45</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.46</v>
+        <v>1.94</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.56</v>
+        <v>1.83</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.73</v>
+        <v>3.18</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.02</v>
+        <v>1.77</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.71</v>
+        <v>1.94</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.29</v>
+        <v>1.83</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="R3" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA3" t="n">
         <v>2.1</v>
       </c>
-      <c r="S3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W3" t="n">
+      <c r="AB3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE3" t="n">
         <v>1.05</v>
       </c>
-      <c r="X3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AF3" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,80 +1043,80 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.55</v>
+        <v>4.5</v>
       </c>
       <c r="R4" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="S4" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="T4" t="n">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="U4" t="n">
-        <v>3.1</v>
+        <v>3.48</v>
       </c>
       <c r="V4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
         <v>1.32</v>
       </c>
-      <c r="W4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AK4" t="n">
-        <v>1.62</v>
+        <v>1.28</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,65 +1520,65 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.62</v>
+        <v>1.2</v>
       </c>
       <c r="O7" t="n">
-        <v>3.85</v>
+        <v>7</v>
       </c>
       <c r="P7" t="n">
-        <v>4.44</v>
+        <v>13</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.2</v>
+        <v>1.55</v>
       </c>
       <c r="R7" t="n">
-        <v>2.46</v>
+        <v>2.84</v>
       </c>
       <c r="S7" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T7" t="n">
-        <v>3.07</v>
+        <v>3.66</v>
       </c>
       <c r="U7" t="n">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="W7" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X7" t="n">
         <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.39</v>
+        <v>2.08</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AE7" t="n">
         <v>1.17</v>
       </c>
       <c r="AF7" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AG7" t="n">
         <v>1.61</v>
       </c>
-      <c r="AG7" t="n">
-        <v>2.18</v>
-      </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1697,25 +1697,25 @@
         <v>1.31</v>
       </c>
       <c r="T8" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="U8" t="n">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
       <c r="V8" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W8" t="n">
         <v>1.1</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="AA8" t="n">
         <v>1.69</v>
@@ -1724,19 +1724,19 @@
         <v>2.13</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="AD8" t="n">
         <v>1.45</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>1.81</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1838,61 +1838,61 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="O9" t="n">
-        <v>3.34</v>
+        <v>3.15</v>
       </c>
       <c r="P9" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="S9" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T9" t="n">
         <v>2.73</v>
       </c>
       <c r="U9" t="n">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="V9" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="Z9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC9" t="n">
         <v>3.44</v>
       </c>
-      <c r="AA9" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.12</v>
-      </c>
       <c r="AD9" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AG9" t="n">
         <v>2.05</v>
@@ -1911,7 +1911,7 @@
         <v>1.4</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,80 +1997,80 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.11</v>
+        <v>1.54</v>
       </c>
       <c r="O10" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="P10" t="n">
-        <v>14</v>
+        <v>4.91</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="R10" t="n">
-        <v>2.89</v>
+        <v>2.45</v>
       </c>
       <c r="S10" t="n">
         <v>1.25</v>
       </c>
       <c r="T10" t="n">
-        <v>4</v>
+        <v>3.07</v>
       </c>
       <c r="U10" t="n">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="V10" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="W10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.15</v>
       </c>
-      <c r="X10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AK10" t="n">
-        <v>4.85</v>
+        <v>2.38</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="O11" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P11" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O12" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="P12" t="n">
         <v>3.5</v>
@@ -2336,7 +2336,7 @@
         <v>2.63</v>
       </c>
       <c r="U12" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="V12" t="n">
         <v>1.33</v>
@@ -2345,34 +2345,34 @@
         <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y12" t="n">
         <v>1.41</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF12" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK12" t="n">
         <v>1.65</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.25</v>
+        <v>2.35</v>
       </c>
       <c r="O13" t="n">
-        <v>5.7</v>
+        <v>2.53</v>
       </c>
       <c r="P13" t="n">
-        <v>11</v>
+        <v>2.91</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.65</v>
+        <v>3.38</v>
       </c>
       <c r="R13" t="n">
-        <v>2.78</v>
+        <v>1.66</v>
       </c>
       <c r="S13" t="n">
-        <v>1.29</v>
+        <v>1.74</v>
       </c>
       <c r="T13" t="n">
-        <v>3.2</v>
+        <v>2.08</v>
       </c>
       <c r="U13" t="n">
-        <v>2.21</v>
+        <v>4.25</v>
       </c>
       <c r="V13" t="n">
-        <v>1.57</v>
+        <v>1.17</v>
       </c>
       <c r="W13" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.14</v>
+        <v>1.71</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.45</v>
+        <v>2.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.66</v>
+        <v>3.04</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.27</v>
+        <v>1.33</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.34</v>
+        <v>6.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.56</v>
+        <v>1.06</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="AK13" t="n">
-        <v>3.8</v>
+        <v>1.45</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.13</v>
+        <v>3.25</v>
       </c>
       <c r="O14" t="n">
-        <v>2.5</v>
+        <v>3.65</v>
       </c>
       <c r="P14" t="n">
-        <v>4.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.38</v>
+        <v>3.71</v>
       </c>
       <c r="R14" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA14" t="n">
         <v>1.66</v>
       </c>
-      <c r="S14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U14" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>3.05</v>
-      </c>
       <c r="AB14" t="n">
-        <v>1.36</v>
+        <v>2.18</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.5</v>
+        <v>2.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.06</v>
+        <v>1.46</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.4</v>
+        <v>1.54</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.5</v>
+        <v>2.32</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>3.05</v>
+        <v>1.25</v>
       </c>
       <c r="O15" t="n">
-        <v>3.7</v>
+        <v>6.25</v>
       </c>
       <c r="P15" t="n">
-        <v>1.96</v>
+        <v>11.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.9</v>
+        <v>1.62</v>
       </c>
       <c r="R15" t="n">
-        <v>2.28</v>
+        <v>2.78</v>
       </c>
       <c r="S15" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T15" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U15" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AC15" t="n">
         <v>2.34</v>
       </c>
-      <c r="V15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.48</v>
-      </c>
       <c r="AD15" t="n">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.55</v>
+        <v>1.97</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.73</v>
+        <v>1.08</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.25</v>
+        <v>3.8</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2951,7 +2951,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="O16" t="n">
         <v>3.6</v>
@@ -2960,49 +2960,49 @@
         <v>3.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="R16" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="S16" t="n">
         <v>1.35</v>
       </c>
       <c r="T16" t="n">
-        <v>2.94</v>
+        <v>3.11</v>
       </c>
       <c r="U16" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="V16" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W16" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
         <v>1.22</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF16" t="n">
         <v>1.67</v>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3110,31 +3110,31 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.17</v>
+        <v>2.33</v>
       </c>
       <c r="O17" t="n">
-        <v>3.05</v>
+        <v>3.12</v>
       </c>
       <c r="P17" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="S17" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="T17" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="U17" t="n">
-        <v>3.13</v>
+        <v>3.4</v>
       </c>
       <c r="V17" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="W17" t="n">
         <v>1.03</v>
@@ -3143,28 +3143,28 @@
         <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AB17" t="n">
         <v>1.57</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.8</v>
+        <v>5.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AG17" t="n">
         <v>1.69</v>
@@ -3183,7 +3183,7 @@
         <v>1.27</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>16</v>
+        <v>2.3</v>
       </c>
       <c r="O18" t="n">
-        <v>7.45</v>
+        <v>3.4</v>
       </c>
       <c r="P18" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W18" t="n">
         <v>1.11</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>13</v>
-      </c>
-      <c r="R18" t="n">
-        <v>3</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.17</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.95</v>
+        <v>4</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.53</v>
+        <v>2.07</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.17</v>
+        <v>2.66</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.61</v>
+        <v>1.41</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.51</v>
+        <v>1.57</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.46</v>
+        <v>2.23</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>5.7</v>
+        <v>1.28</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.02</v>
+        <v>1.57</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.3</v>
+        <v>16</v>
       </c>
       <c r="O19" t="n">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="P19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="R19" t="n">
         <v>3</v>
       </c>
-      <c r="Q19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R19" t="n">
-        <v>2.2</v>
-      </c>
       <c r="S19" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T19" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="U19" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="V19" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="W19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y19" t="n">
         <v>1.11</v>
       </c>
-      <c r="X19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.22</v>
-      </c>
       <c r="Z19" t="n">
-        <v>4</v>
+        <v>5.75</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.74</v>
+        <v>1.46</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.06</v>
+        <v>2.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.66</v>
+        <v>2.19</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.41</v>
+        <v>1.65</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.57</v>
+        <v>2.55</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.2</v>
+        <v>1.45</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.28</v>
+        <v>1.06</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.57</v>
+        <v>1.02</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.55</v>
+        <v>2.39</v>
       </c>
       <c r="O20" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="P20" t="n">
         <v>2.8</v>
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O21" t="n">
         <v>2.75</v>
@@ -3767,10 +3767,10 @@
         <v>2.25</v>
       </c>
       <c r="U21" t="n">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="V21" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W21" t="n">
         <v>1.01</v>
@@ -3782,7 +3782,7 @@
         <v>1.58</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AA21" t="n">
         <v>2.87</v>
@@ -3800,7 +3800,7 @@
         <v>1.03</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AG21" t="n">
         <v>1.62</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="O22" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="P22" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.58</v>
+        <v>1.9</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="O24" t="n">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="P24" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="R24" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S24" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T24" t="n">
-        <v>3.07</v>
+        <v>2.75</v>
       </c>
       <c r="U24" t="n">
-        <v>2.59</v>
+        <v>2.96</v>
       </c>
       <c r="V24" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="W24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X24" t="n">
         <v>1.04</v>
       </c>
-      <c r="X24" t="n">
+      <c r="Y24" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE24" t="n">
         <v>1.02</v>
       </c>
-      <c r="Y24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AF24" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.04</v>
+        <v>1.78</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4541,25 +4541,25 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.32</v>
+        <v>2.05</v>
       </c>
       <c r="O26" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P26" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.95</v>
+        <v>2.66</v>
       </c>
       <c r="R26" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="S26" t="n">
         <v>1.41</v>
       </c>
       <c r="T26" t="n">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="U26" t="n">
         <v>2.9</v>
@@ -4568,34 +4568,34 @@
         <v>1.34</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC26" t="n">
         <v>3.65</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AG26" t="n">
         <v>1.85</v>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.43</v>
+        <v>2.39</v>
       </c>
       <c r="O27" t="n">
         <v>3</v>
       </c>
       <c r="P27" t="n">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU27"/>
+  <dimension ref="A1:AU28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC2" t="n">
         <v>3.8</v>
       </c>
-      <c r="Q2" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W2" t="n">
+      <c r="AD2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE2" t="n">
         <v>1.05</v>
       </c>
-      <c r="X2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AB2" t="n">
+      <c r="AF2" t="n">
         <v>1.83</v>
       </c>
-      <c r="AC2" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AG2" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="R3" t="n">
-        <v>2.14</v>
+        <v>1.94</v>
       </c>
       <c r="S3" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="T3" t="n">
-        <v>2.56</v>
+        <v>2.51</v>
       </c>
       <c r="U3" t="n">
-        <v>3.04</v>
+        <v>3.48</v>
       </c>
       <c r="V3" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="Z3" t="n">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.8</v>
+        <v>4.55</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.2</v>
+        <v>1.93</v>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="P4" t="n">
-        <v>2.18</v>
+        <v>3.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.5</v>
+        <v>2.48</v>
       </c>
       <c r="R4" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AA4" t="n">
         <v>1.94</v>
       </c>
-      <c r="S4" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="U4" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.32</v>
-      </c>
       <c r="AB4" t="n">
-        <v>1.56</v>
+        <v>1.83</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.55</v>
+        <v>3.18</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AF4" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.7</v>
+        <v>1.94</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.28</v>
+        <v>1.83</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1473,27 +1473,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1623,7 +1623,7 @@
         <v>0</v>
       </c>
       <c r="AU7" s="3" t="n">
-        <v>46224.54166666666</v>
+        <v>46224.5</v>
       </c>
     </row>
     <row r="8">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.25</v>
+        <v>1.2</v>
       </c>
       <c r="O9" t="n">
-        <v>3.15</v>
+        <v>7</v>
       </c>
       <c r="P9" t="n">
-        <v>2.9</v>
+        <v>13</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>1.55</v>
       </c>
       <c r="R9" t="n">
-        <v>2.03</v>
+        <v>2.84</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="T9" t="n">
-        <v>2.73</v>
+        <v>3.66</v>
       </c>
       <c r="U9" t="n">
-        <v>2.88</v>
+        <v>2.23</v>
       </c>
       <c r="V9" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.05</v>
+        <v>4.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.05</v>
+        <v>1.48</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.74</v>
+        <v>2.34</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.44</v>
+        <v>2.08</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.76</v>
+        <v>2.18</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.05</v>
+        <v>1.61</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.4</v>
+        <v>1.03</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.53</v>
+        <v>3.8</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2109,27 +2109,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="O11" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="P11" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.61</v>
+        <v>2.05</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.25</v>
+        <v>1.74</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2259,7 +2259,7 @@
         <v>0</v>
       </c>
       <c r="AU11" s="3" t="n">
-        <v>46224.58333333334</v>
+        <v>46224.54166666666</v>
       </c>
     </row>
     <row r="12">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O12" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P12" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.4</v>
+        <v>1.61</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.55</v>
+        <v>2.25</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2427,27 +2427,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="O13" t="n">
-        <v>2.53</v>
+        <v>3.25</v>
       </c>
       <c r="P13" t="n">
-        <v>2.91</v>
+        <v>3.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.38</v>
+        <v>2.7</v>
       </c>
       <c r="R13" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>1.74</v>
+        <v>1.44</v>
       </c>
       <c r="T13" t="n">
-        <v>2.08</v>
+        <v>2.63</v>
       </c>
       <c r="U13" t="n">
-        <v>4.25</v>
+        <v>3.1</v>
       </c>
       <c r="V13" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.71</v>
+        <v>1.41</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.1</v>
+        <v>2.56</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.04</v>
+        <v>2.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.5</v>
+        <v>4.33</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2577,7 +2577,7 @@
         <v>0</v>
       </c>
       <c r="AU13" s="3" t="n">
-        <v>46224.625</v>
+        <v>46224.58333333334</v>
       </c>
     </row>
     <row r="14">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>3.25</v>
+        <v>2.35</v>
       </c>
       <c r="O14" t="n">
-        <v>3.65</v>
+        <v>2.53</v>
       </c>
       <c r="P14" t="n">
-        <v>2.02</v>
+        <v>2.91</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.71</v>
+        <v>3.38</v>
       </c>
       <c r="R14" t="n">
-        <v>2.22</v>
+        <v>1.66</v>
       </c>
       <c r="S14" t="n">
-        <v>1.28</v>
+        <v>1.74</v>
       </c>
       <c r="T14" t="n">
-        <v>3.4</v>
+        <v>2.08</v>
       </c>
       <c r="U14" t="n">
-        <v>2.36</v>
+        <v>4.25</v>
       </c>
       <c r="V14" t="n">
-        <v>1.53</v>
+        <v>1.17</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.19</v>
+        <v>1.71</v>
       </c>
       <c r="Z14" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.66</v>
+        <v>3.04</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.18</v>
+        <v>1.33</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.6</v>
+        <v>6.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.46</v>
+        <v>1.06</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.54</v>
+        <v>2.4</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.32</v>
+        <v>1.5</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.25</v>
+        <v>3.25</v>
       </c>
       <c r="O15" t="n">
-        <v>6.25</v>
+        <v>3.65</v>
       </c>
       <c r="P15" t="n">
-        <v>11.2</v>
+        <v>2.02</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.62</v>
+        <v>3.71</v>
       </c>
       <c r="R15" t="n">
-        <v>2.78</v>
+        <v>2.22</v>
       </c>
       <c r="S15" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T15" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U15" t="n">
-        <v>2.23</v>
+        <v>2.36</v>
       </c>
       <c r="V15" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W15" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.48</v>
+        <v>2.18</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.97</v>
+        <v>1.54</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.8</v>
+        <v>2.32</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.08</v>
+        <v>1.67</v>
       </c>
       <c r="AK15" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.9</v>
+        <v>1.25</v>
       </c>
       <c r="O16" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="P16" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T16" t="n">
         <v>3.6</v>
       </c>
-      <c r="P16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.11</v>
-      </c>
       <c r="U16" t="n">
-        <v>2.59</v>
+        <v>2.23</v>
       </c>
       <c r="V16" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="W16" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X16" t="n">
         <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.62</v>
+        <v>4.9</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="AB16" t="n">
-        <v>2</v>
+        <v>2.48</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.87</v>
+        <v>2.34</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.67</v>
+        <v>1.97</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.88</v>
+        <v>3.8</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
         <v>0</v>
       </c>
       <c r="AU16" s="3" t="n">
-        <v>46224.64583333334</v>
+        <v>46224.625</v>
       </c>
     </row>
     <row r="17">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,80 +3110,80 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.33</v>
+        <v>1.9</v>
       </c>
       <c r="O17" t="n">
-        <v>3.12</v>
+        <v>3.6</v>
       </c>
       <c r="P17" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.94</v>
+        <v>2.17</v>
       </c>
       <c r="S17" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="T17" t="n">
-        <v>2.31</v>
+        <v>3.11</v>
       </c>
       <c r="U17" t="n">
-        <v>3.4</v>
+        <v>2.59</v>
       </c>
       <c r="V17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17" t="n">
         <v>1.29</v>
       </c>
-      <c r="W17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AK17" t="n">
-        <v>1.53</v>
+        <v>1.88</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="AU17" s="3" t="n">
-        <v>46224.65625</v>
+        <v>46224.64583333334</v>
       </c>
     </row>
     <row r="18">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="O18" t="n">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="P18" t="n">
         <v>3</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="R18" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="S18" t="n">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="T18" t="n">
-        <v>3.19</v>
+        <v>2.31</v>
       </c>
       <c r="U18" t="n">
-        <v>2.45</v>
+        <v>3.4</v>
       </c>
       <c r="V18" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="W18" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="Z18" t="n">
-        <v>4</v>
+        <v>2.42</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.73</v>
+        <v>2.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.07</v>
+        <v>1.57</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.66</v>
+        <v>5.25</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.41</v>
+        <v>1.13</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.23</v>
+        <v>1.69</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3372,7 +3372,7 @@
         <v>0</v>
       </c>
       <c r="AU18" s="3" t="n">
-        <v>46224.66666666666</v>
+        <v>46224.65625</v>
       </c>
     </row>
     <row r="19">
@@ -3540,27 +3540,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="O20" t="n">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="P20" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q20" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3690,7 +3690,7 @@
         <v>0</v>
       </c>
       <c r="AU20" s="3" t="n">
-        <v>46224.77083333334</v>
+        <v>46224.66666666666</v>
       </c>
     </row>
     <row r="21">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="O21" t="n">
-        <v>2.75</v>
+        <v>3.08</v>
       </c>
       <c r="P21" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3849,7 +3849,7 @@
         <v>0</v>
       </c>
       <c r="AU21" s="3" t="n">
-        <v>46224.79166666666</v>
+        <v>46224.77083333334</v>
       </c>
     </row>
     <row r="22">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,80 +3905,80 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.11</v>
+        <v>2.35</v>
       </c>
       <c r="O22" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="P22" t="n">
         <v>3.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="R22" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="S22" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22" t="n">
         <v>1.35</v>
       </c>
-      <c r="T22" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AK22" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4008,7 +4008,7 @@
         <v>0</v>
       </c>
       <c r="AU22" s="3" t="n">
-        <v>46224.8125</v>
+        <v>46224.79166666666</v>
       </c>
     </row>
     <row r="23">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="O23" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P23" t="n">
-        <v>3.74</v>
+        <v>3.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.35</v>
+        <v>1.94</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.52</v>
+        <v>1.9</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4335,12 +4335,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.51</v>
+        <v>2.07</v>
       </c>
       <c r="O25" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="P25" t="n">
-        <v>4.7</v>
+        <v>3.74</v>
       </c>
       <c r="Q25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.55</v>
+        <v>2.35</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.29</v>
+        <v>1.52</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4485,7 +4485,7 @@
         <v>0</v>
       </c>
       <c r="AU25" s="3" t="n">
-        <v>46224.83333333334</v>
+        <v>46224.8125</v>
       </c>
     </row>
     <row r="26">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.05</v>
+        <v>1.51</v>
       </c>
       <c r="O26" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="P26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="T26" t="n">
         <v>3.25</v>
       </c>
-      <c r="Q26" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="S26" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.59</v>
-      </c>
       <c r="U26" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="V26" t="n">
-        <v>1.34</v>
+        <v>1.57</v>
       </c>
       <c r="W26" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.04</v>
+        <v>4.65</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.03</v>
+        <v>1.55</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.7</v>
+        <v>2.29</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.65</v>
+        <v>2.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.22</v>
+        <v>1.48</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.81</v>
+        <v>1.59</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.66</v>
+        <v>2.3</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4644,7 +4644,7 @@
         <v>0</v>
       </c>
       <c r="AU26" s="3" t="n">
-        <v>46224.875</v>
+        <v>46224.83333333334</v>
       </c>
     </row>
     <row r="27">
@@ -4653,156 +4653,315 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>CD Universidad Católica</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="O27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P27" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" s="3" t="n">
+        <v>46224.875</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>21:35</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Vila Nova</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>Fortaleza</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="inlineStr">
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N27" t="n">
+      <c r="N28" t="n">
         <v>2.39</v>
       </c>
-      <c r="O27" t="n">
+      <c r="O28" t="n">
         <v>3</v>
       </c>
-      <c r="P27" t="n">
+      <c r="P28" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU27" s="3" t="n">
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" s="3" t="n">
         <v>46224.89930555555</v>
       </c>
     </row>

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="R2" t="n">
-        <v>2.14</v>
+        <v>1.94</v>
       </c>
       <c r="S2" t="n">
         <v>1.45</v>
       </c>
       <c r="T2" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="U2" t="n">
-        <v>3.04</v>
+        <v>3.48</v>
       </c>
       <c r="V2" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>3</v>
+        <v>2.57</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.8</v>
+        <v>4.55</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AE2" t="n">
         <v>1.05</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="R3" t="n">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
       <c r="S3" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="T3" t="n">
-        <v>2.51</v>
+        <v>2.56</v>
       </c>
       <c r="U3" t="n">
-        <v>3.48</v>
+        <v>3.04</v>
       </c>
       <c r="V3" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.72</v>
+        <v>2.89</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.55</v>
+        <v>3.62</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>1.32</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="O4" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P4" t="n">
-        <v>3.8</v>
+        <v>3.94</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="R4" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="S4" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T4" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="U4" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="V4" t="n">
         <v>1.39</v>
       </c>
       <c r="W4" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X4" t="n">
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.2</v>
+        <v>2.25</v>
       </c>
       <c r="O9" t="n">
-        <v>7</v>
+        <v>3.15</v>
       </c>
       <c r="P9" t="n">
-        <v>13</v>
+        <v>2.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.55</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>2.84</v>
+        <v>2.03</v>
       </c>
       <c r="S9" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="T9" t="n">
-        <v>3.66</v>
+        <v>2.73</v>
       </c>
       <c r="U9" t="n">
-        <v>2.23</v>
+        <v>2.88</v>
       </c>
       <c r="V9" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="W9" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.9</v>
+        <v>3.05</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.48</v>
+        <v>2.05</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.34</v>
+        <v>1.74</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.08</v>
+        <v>3.44</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.18</v>
+        <v>1.76</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.61</v>
+        <v>2.05</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.03</v>
+        <v>1.4</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.8</v>
+        <v>1.53</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,80 +1997,80 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.54</v>
+        <v>1.2</v>
       </c>
       <c r="O10" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="P10" t="n">
-        <v>4.91</v>
+        <v>13</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="R10" t="n">
-        <v>2.45</v>
+        <v>2.84</v>
       </c>
       <c r="S10" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T10" t="n">
-        <v>3.07</v>
+        <v>3.66</v>
       </c>
       <c r="U10" t="n">
         <v>2.23</v>
       </c>
       <c r="V10" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W10" t="n">
         <v>1.13</v>
       </c>
       <c r="X10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y10" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AK10" t="n">
-        <v>2.38</v>
+        <v>3.8</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.25</v>
+        <v>1.54</v>
       </c>
       <c r="O11" t="n">
-        <v>3.15</v>
+        <v>4.5</v>
       </c>
       <c r="P11" t="n">
-        <v>2.9</v>
+        <v>4.91</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="R11" t="n">
-        <v>2.03</v>
+        <v>2.45</v>
       </c>
       <c r="S11" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="T11" t="n">
-        <v>2.73</v>
+        <v>3.07</v>
       </c>
       <c r="U11" t="n">
-        <v>2.88</v>
+        <v>2.23</v>
       </c>
       <c r="V11" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.05</v>
+        <v>4.65</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.05</v>
+        <v>1.54</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.74</v>
+        <v>2.27</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.44</v>
+        <v>2.35</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.37</v>
+        <v>1.57</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.4</v>
+        <v>1.15</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.53</v>
+        <v>2.38</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="O12" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="P12" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="O24" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="P24" t="n">
-        <v>3.5</v>
+        <v>3.74</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="O25" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="P25" t="n">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.35</v>
+        <v>2.26</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>3.45</v>
+        <v>2.1</v>
       </c>
       <c r="O2" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P2" t="n">
-        <v>2.03</v>
+        <v>3.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.8</v>
+        <v>2.86</v>
       </c>
       <c r="R2" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="S2" t="n">
         <v>1.45</v>
       </c>
       <c r="T2" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="U2" t="n">
-        <v>3.48</v>
+        <v>3.04</v>
       </c>
       <c r="V2" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W2" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.57</v>
+        <v>2.89</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.55</v>
+        <v>3.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,80 +884,80 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.8</v>
+        <v>2.42</v>
       </c>
       <c r="R3" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="S3" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="T3" t="n">
-        <v>2.56</v>
+        <v>2.77</v>
       </c>
       <c r="U3" t="n">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="V3" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.89</v>
+        <v>3.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.62</v>
+        <v>3.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AG3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AK3" t="n">
         <v>1.87</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.6</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,80 +1043,80 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.85</v>
+        <v>3.45</v>
       </c>
       <c r="O4" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="P4" t="n">
-        <v>3.94</v>
+        <v>2.03</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="R4" t="n">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="S4" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="T4" t="n">
-        <v>2.77</v>
+        <v>2.55</v>
       </c>
       <c r="U4" t="n">
-        <v>2.91</v>
+        <v>3.48</v>
       </c>
       <c r="V4" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="W4" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.29</v>
+        <v>1.47</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.4</v>
+        <v>2.57</v>
       </c>
       <c r="AA4" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.84</v>
+        <v>1.56</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.12</v>
+        <v>4.2</v>
       </c>
       <c r="AD4" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AK4" t="n">
         <v>1.28</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.85</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.25</v>
+        <v>1.54</v>
       </c>
       <c r="O9" t="n">
-        <v>3.15</v>
+        <v>4.5</v>
       </c>
       <c r="P9" t="n">
-        <v>2.9</v>
+        <v>4.91</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="R9" t="n">
-        <v>2.03</v>
+        <v>2.45</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="T9" t="n">
-        <v>2.73</v>
+        <v>3.07</v>
       </c>
       <c r="U9" t="n">
-        <v>2.88</v>
+        <v>2.23</v>
       </c>
       <c r="V9" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.05</v>
+        <v>4.65</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.05</v>
+        <v>1.54</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.74</v>
+        <v>2.27</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.44</v>
+        <v>2.35</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.37</v>
+        <v>1.57</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.4</v>
+        <v>1.15</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.53</v>
+        <v>2.38</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.54</v>
+        <v>2.25</v>
       </c>
       <c r="O11" t="n">
-        <v>4.5</v>
+        <v>3.15</v>
       </c>
       <c r="P11" t="n">
-        <v>4.91</v>
+        <v>2.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>2.45</v>
+        <v>2.03</v>
       </c>
       <c r="S11" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="T11" t="n">
-        <v>3.07</v>
+        <v>2.73</v>
       </c>
       <c r="U11" t="n">
-        <v>2.23</v>
+        <v>2.88</v>
       </c>
       <c r="V11" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.65</v>
+        <v>3.05</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.54</v>
+        <v>2.05</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.27</v>
+        <v>1.74</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.35</v>
+        <v>3.44</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.19</v>
+        <v>1.04</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.15</v>
+        <v>1.4</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.38</v>
+        <v>1.53</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2315,43 +2315,43 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="O12" t="n">
-        <v>3.24</v>
+        <v>3.5</v>
       </c>
       <c r="P12" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA12" t="n">
         <v>1.61</v>
@@ -2360,19 +2360,19 @@
         <v>2.25</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.35</v>
+        <v>3.25</v>
       </c>
       <c r="O14" t="n">
-        <v>2.53</v>
+        <v>3.65</v>
       </c>
       <c r="P14" t="n">
-        <v>2.91</v>
+        <v>2.02</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.38</v>
+        <v>3.71</v>
       </c>
       <c r="R14" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA14" t="n">
         <v>1.66</v>
       </c>
-      <c r="S14" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U14" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>3.04</v>
-      </c>
       <c r="AB14" t="n">
-        <v>1.33</v>
+        <v>2.18</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.5</v>
+        <v>2.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.06</v>
+        <v>1.46</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.4</v>
+        <v>1.54</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.5</v>
+        <v>2.32</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>3.25</v>
+        <v>2.37</v>
       </c>
       <c r="O15" t="n">
-        <v>3.65</v>
+        <v>2.6</v>
       </c>
       <c r="P15" t="n">
-        <v>2.02</v>
+        <v>3.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.71</v>
+        <v>3.38</v>
       </c>
       <c r="R15" t="n">
-        <v>2.22</v>
+        <v>1.66</v>
       </c>
       <c r="S15" t="n">
-        <v>1.28</v>
+        <v>1.74</v>
       </c>
       <c r="T15" t="n">
-        <v>3.4</v>
+        <v>2.08</v>
       </c>
       <c r="U15" t="n">
-        <v>2.36</v>
+        <v>4.25</v>
       </c>
       <c r="V15" t="n">
-        <v>1.53</v>
+        <v>1.17</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.19</v>
+        <v>1.71</v>
       </c>
       <c r="Z15" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.66</v>
+        <v>3.04</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.18</v>
+        <v>1.31</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.6</v>
+        <v>6.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.46</v>
+        <v>1.06</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.54</v>
+        <v>2.25</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.32</v>
+        <v>1.57</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>16</v>
+        <v>2.3</v>
       </c>
       <c r="O19" t="n">
-        <v>7.5</v>
+        <v>3.4</v>
       </c>
       <c r="P19" t="n">
-        <v>1.15</v>
+        <v>3</v>
       </c>
       <c r="Q19" t="n">
-        <v>14.5</v>
+        <v>2.8</v>
       </c>
       <c r="R19" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="T19" t="n">
-        <v>3.7</v>
+        <v>3.19</v>
       </c>
       <c r="U19" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="V19" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="W19" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
         <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.75</v>
+        <v>4</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.46</v>
+        <v>1.73</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.5</v>
+        <v>2.07</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.19</v>
+        <v>2.66</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.65</v>
+        <v>1.41</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.45</v>
+        <v>2.23</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.06</v>
+        <v>1.28</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.02</v>
+        <v>1.57</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.3</v>
+        <v>16</v>
       </c>
       <c r="O20" t="n">
-        <v>3.4</v>
+        <v>7.5</v>
       </c>
       <c r="P20" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="R20" t="n">
         <v>3</v>
       </c>
-      <c r="Q20" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R20" t="n">
-        <v>2.2</v>
-      </c>
       <c r="S20" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="T20" t="n">
-        <v>3.19</v>
+        <v>3.7</v>
       </c>
       <c r="U20" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="V20" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="W20" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X20" t="n">
         <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="Z20" t="n">
-        <v>4</v>
+        <v>5.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.73</v>
+        <v>1.46</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.07</v>
+        <v>2.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.66</v>
+        <v>2.19</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.41</v>
+        <v>1.65</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.57</v>
+        <v>2.55</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.23</v>
+        <v>1.45</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.28</v>
+        <v>1.06</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.57</v>
+        <v>1.02</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="O22" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="P22" t="n">
         <v>3.2</v>
@@ -3932,7 +3932,7 @@
         <v>1.2</v>
       </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
         <v>1.09</v>
@@ -3947,13 +3947,13 @@
         <v>2.87</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AC22" t="n">
-        <v>5.75</v>
+        <v>5.15</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AE22" t="n">
         <v>1.03</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="O24" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="P24" t="n">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.35</v>
+        <v>2.26</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="O25" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="P25" t="n">
-        <v>3.5</v>
+        <v>3.74</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="O2" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P2" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.86</v>
+        <v>2.37</v>
       </c>
       <c r="R2" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="S2" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="T2" t="n">
-        <v>2.56</v>
+        <v>2.81</v>
       </c>
       <c r="U2" t="n">
-        <v>3.04</v>
+        <v>2.75</v>
       </c>
       <c r="V2" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.89</v>
+        <v>3.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.93</v>
+        <v>3.44</v>
       </c>
       <c r="O3" t="n">
-        <v>3.6</v>
+        <v>3.14</v>
       </c>
       <c r="P3" t="n">
-        <v>3.6</v>
+        <v>2.18</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.42</v>
+        <v>3.93</v>
       </c>
       <c r="R3" t="n">
-        <v>2.12</v>
+        <v>1.9</v>
       </c>
       <c r="S3" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="T3" t="n">
-        <v>2.77</v>
+        <v>2.4</v>
       </c>
       <c r="U3" t="n">
-        <v>2.9</v>
+        <v>3.48</v>
       </c>
       <c r="V3" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="W3" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE3" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AF3" t="n">
-        <v>1.78</v>
+        <v>2.02</v>
       </c>
       <c r="AG3" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.87</v>
+        <v>1.26</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.45</v>
+        <v>2.21</v>
       </c>
       <c r="O4" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P4" t="n">
-        <v>2.03</v>
+        <v>3.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.8</v>
+        <v>2.86</v>
       </c>
       <c r="R4" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="S4" t="n">
         <v>1.45</v>
       </c>
       <c r="T4" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="U4" t="n">
-        <v>3.48</v>
+        <v>2.86</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.57</v>
+        <v>2.89</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.28</v>
+        <v>1.55</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>4.2</v>
+        <v>1.57</v>
       </c>
       <c r="O8" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="P8" t="n">
-        <v>1.72</v>
+        <v>4.81</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="S8" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="T8" t="n">
-        <v>3.15</v>
+        <v>3.07</v>
       </c>
       <c r="U8" t="n">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="V8" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.05</v>
+        <v>4.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.69</v>
+        <v>1.54</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.13</v>
+        <v>2.27</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.53</v>
+        <v>2.18</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.81</v>
+        <v>1.18</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.25</v>
+        <v>2.35</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,65 +1838,65 @@
         </is>
       </c>
       <c r="N9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O9" t="n">
+        <v>7</v>
+      </c>
+      <c r="P9" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q9" t="n">
         <v>1.54</v>
       </c>
-      <c r="O9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P9" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.1</v>
-      </c>
       <c r="R9" t="n">
-        <v>2.45</v>
+        <v>2.84</v>
       </c>
       <c r="S9" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T9" t="n">
-        <v>3.07</v>
+        <v>3.66</v>
       </c>
       <c r="U9" t="n">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="V9" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W9" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.65</v>
+        <v>5</v>
       </c>
       <c r="AA9" t="n">
         <v>1.54</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.27</v>
+        <v>2.45</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AD9" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG9" t="n">
         <v>1.57</v>
       </c>
-      <c r="AE9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.21</v>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.38</v>
+        <v>4.75</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.2</v>
+        <v>2.25</v>
       </c>
       <c r="O10" t="n">
-        <v>7</v>
+        <v>3.15</v>
       </c>
       <c r="P10" t="n">
-        <v>13</v>
+        <v>2.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.55</v>
+        <v>2.9</v>
       </c>
       <c r="R10" t="n">
-        <v>2.84</v>
+        <v>2.14</v>
       </c>
       <c r="S10" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="T10" t="n">
-        <v>3.66</v>
+        <v>2.64</v>
       </c>
       <c r="U10" t="n">
-        <v>2.23</v>
+        <v>2.89</v>
       </c>
       <c r="V10" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="W10" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.11</v>
+        <v>1.31</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.9</v>
+        <v>3.24</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.48</v>
+        <v>2.05</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.34</v>
+        <v>1.74</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.08</v>
+        <v>3.44</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.18</v>
+        <v>1.73</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.61</v>
+        <v>2.05</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.03</v>
+        <v>1.36</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.8</v>
+        <v>1.56</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.25</v>
+        <v>3.7</v>
       </c>
       <c r="O11" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="P11" t="n">
-        <v>2.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>3.46</v>
       </c>
       <c r="R11" t="n">
-        <v>2.03</v>
+        <v>2.21</v>
       </c>
       <c r="S11" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="T11" t="n">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="U11" t="n">
-        <v>2.88</v>
+        <v>2.46</v>
       </c>
       <c r="V11" t="n">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.05</v>
+        <v>4.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.74</v>
+        <v>2.11</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.44</v>
+        <v>2.65</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.53</v>
+        <v>1.19</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="O12" t="n">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="P12" t="n">
-        <v>3.25</v>
+        <v>3.61</v>
       </c>
       <c r="Q12" t="n">
         <v>2.3</v>
@@ -2333,7 +2333,7 @@
         <v>1.35</v>
       </c>
       <c r="T12" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="U12" t="n">
         <v>2.39</v>
@@ -2345,7 +2345,7 @@
         <v>1.08</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
         <v>1.18</v>
@@ -2360,13 +2360,13 @@
         <v>2.25</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AF12" t="n">
         <v>1.53</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK12" t="n">
         <v>1.75</v>
@@ -2474,61 +2474,61 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="O13" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="P13" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="S13" t="n">
         <v>1.44</v>
       </c>
       <c r="T13" t="n">
-        <v>2.63</v>
+        <v>2.41</v>
       </c>
       <c r="U13" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="V13" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W13" t="n">
         <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AE13" t="n">
         <v>1.01</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG13" t="n">
         <v>1.78</v>
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK13" t="n">
         <v>1.65</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>3.25</v>
+        <v>1.15</v>
       </c>
       <c r="O14" t="n">
-        <v>3.65</v>
+        <v>6.4</v>
       </c>
       <c r="P14" t="n">
-        <v>2.02</v>
+        <v>14.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.71</v>
+        <v>1.45</v>
       </c>
       <c r="R14" t="n">
-        <v>2.22</v>
+        <v>2.93</v>
       </c>
       <c r="S14" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T14" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U14" t="n">
-        <v>2.36</v>
+        <v>2.14</v>
       </c>
       <c r="V14" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="Z14" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.18</v>
+        <v>2.62</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.6</v>
+        <v>2.19</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.46</v>
+        <v>1.65</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.54</v>
+        <v>2.04</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.32</v>
+        <v>1.62</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.67</v>
+        <v>1.05</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.3</v>
+        <v>3.8</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.37</v>
+        <v>3.85</v>
       </c>
       <c r="O15" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="P15" t="n">
-        <v>3.3</v>
+        <v>1.95</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.38</v>
+        <v>4</v>
       </c>
       <c r="R15" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA15" t="n">
         <v>1.66</v>
       </c>
-      <c r="S15" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U15" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>3.04</v>
-      </c>
       <c r="AB15" t="n">
-        <v>1.31</v>
+        <v>2.15</v>
       </c>
       <c r="AC15" t="n">
-        <v>6.5</v>
+        <v>2.58</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.06</v>
+        <v>1.47</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.25</v>
+        <v>1.56</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.57</v>
+        <v>2.28</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,65 +2951,65 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.25</v>
+        <v>2.37</v>
       </c>
       <c r="O16" t="n">
-        <v>6.25</v>
+        <v>2.6</v>
       </c>
       <c r="P16" t="n">
-        <v>11.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.62</v>
+        <v>3.38</v>
       </c>
       <c r="R16" t="n">
-        <v>2.78</v>
+        <v>1.66</v>
       </c>
       <c r="S16" t="n">
-        <v>1.25</v>
+        <v>1.74</v>
       </c>
       <c r="T16" t="n">
-        <v>3.6</v>
+        <v>2.08</v>
       </c>
       <c r="U16" t="n">
-        <v>2.23</v>
+        <v>4.25</v>
       </c>
       <c r="V16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.57</v>
       </c>
-      <c r="W16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AH16" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.08</v>
+        <v>1.4</v>
       </c>
       <c r="AK16" t="n">
-        <v>3.8</v>
+        <v>1.45</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="O17" t="n">
         <v>3.6</v>
       </c>
       <c r="P17" t="n">
-        <v>3.8</v>
+        <v>3.33</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="R17" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="S17" t="n">
         <v>1.35</v>
       </c>
       <c r="T17" t="n">
-        <v>3.11</v>
+        <v>2.94</v>
       </c>
       <c r="U17" t="n">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="V17" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="W17" t="n">
         <v>1.07</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
         <v>1.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.62</v>
+        <v>3.55</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AB17" t="n">
         <v>2</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AE17" t="n">
         <v>1.11</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AA18" t="n">
         <v>2.33</v>
       </c>
-      <c r="O18" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="P18" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="U18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AB18" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC18" t="n">
-        <v>5.25</v>
+        <v>4.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AE18" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>1.27</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3428,10 +3428,10 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O19" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P19" t="n">
         <v>3</v>
@@ -3440,13 +3440,13 @@
         <v>2.8</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S19" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T19" t="n">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="U19" t="n">
         <v>2.45</v>
@@ -3458,28 +3458,28 @@
         <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
         <v>1.22</v>
       </c>
       <c r="Z19" t="n">
-        <v>4</v>
+        <v>3.74</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AB19" t="n">
         <v>2.07</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF19" t="n">
         <v>1.57</v>
@@ -3501,7 +3501,7 @@
         <v>1.28</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3587,28 +3587,28 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="O20" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="P20" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Q20" t="n">
         <v>14.5</v>
       </c>
       <c r="R20" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="T20" t="n">
         <v>3.7</v>
       </c>
       <c r="U20" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="V20" t="n">
         <v>1.65</v>
@@ -3620,13 +3620,13 @@
         <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z20" t="n">
         <v>5.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AB20" t="n">
         <v>2.5</v>
@@ -3638,7 +3638,7 @@
         <v>1.65</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AF20" t="n">
         <v>2.55</v>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.39</v>
+        <v>2.2</v>
       </c>
       <c r="O21" t="n">
-        <v>3.08</v>
+        <v>2.95</v>
       </c>
       <c r="P21" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="O23" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="P23" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="R23" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="S23" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="T23" t="n">
-        <v>3.07</v>
+        <v>2.63</v>
       </c>
       <c r="U23" t="n">
-        <v>2.59</v>
+        <v>3.16</v>
       </c>
       <c r="V23" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="W23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X23" t="n">
         <v>1.04</v>
       </c>
-      <c r="X23" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y23" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.4</v>
+        <v>2.78</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.94</v>
+        <v>2.26</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.04</v>
+        <v>1.83</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="O24" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="P24" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="R24" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="S24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="V24" t="n">
         <v>1.4</v>
       </c>
-      <c r="T24" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="V24" t="n">
+      <c r="W24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AD24" t="n">
         <v>1.3</v>
       </c>
-      <c r="W24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AE24" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.78</v>
+        <v>2.04</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.07</v>
+        <v>2.21</v>
       </c>
       <c r="O25" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P25" t="n">
-        <v>3.74</v>
+        <v>3.42</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="O27" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="P27" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.66</v>
+        <v>2.39</v>
       </c>
       <c r="R27" t="n">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="S27" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T27" t="n">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="U27" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="V27" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W27" t="n">
         <v>1.07</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.65</v>
+        <v>3.42</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.39</v>
+        <v>2.46</v>
       </c>
       <c r="O28" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P28" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.85</v>
+        <v>2.21</v>
       </c>
       <c r="O2" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P2" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.37</v>
+        <v>2.86</v>
       </c>
       <c r="R2" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="S2" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="T2" t="n">
-        <v>2.81</v>
+        <v>2.56</v>
       </c>
       <c r="U2" t="n">
-        <v>2.75</v>
+        <v>2.86</v>
       </c>
       <c r="V2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W2" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.4</v>
+        <v>2.89</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AB2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF2" t="n">
         <v>1.83</v>
       </c>
-      <c r="AC2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AG2" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.21</v>
+        <v>1.85</v>
       </c>
       <c r="O4" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P4" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.86</v>
+        <v>2.37</v>
       </c>
       <c r="R4" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="S4" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="T4" t="n">
-        <v>2.56</v>
+        <v>2.81</v>
       </c>
       <c r="U4" t="n">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="V4" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W4" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.89</v>
+        <v>3.4</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AC4" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF8" t="n">
         <v>1.57</v>
       </c>
-      <c r="O8" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="P8" t="n">
-        <v>4.81</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AG8" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>1.18</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.35</v>
+        <v>1.19</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.25</v>
+        <v>1.57</v>
       </c>
       <c r="O10" t="n">
-        <v>3.15</v>
+        <v>4.33</v>
       </c>
       <c r="P10" t="n">
-        <v>2.9</v>
+        <v>4.81</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="R10" t="n">
-        <v>2.14</v>
+        <v>2.45</v>
       </c>
       <c r="S10" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="T10" t="n">
-        <v>2.64</v>
+        <v>3.07</v>
       </c>
       <c r="U10" t="n">
-        <v>2.89</v>
+        <v>2.24</v>
       </c>
       <c r="V10" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="W10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X10" t="n">
         <v>1.03</v>
       </c>
-      <c r="X10" t="n">
-        <v>1</v>
-      </c>
       <c r="Y10" t="n">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.24</v>
+        <v>4.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.05</v>
+        <v>1.54</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.74</v>
+        <v>2.27</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.44</v>
+        <v>2.18</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.37</v>
+        <v>1.56</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.56</v>
+        <v>2.35</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>3.7</v>
+        <v>2.25</v>
       </c>
       <c r="O11" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="P11" t="n">
-        <v>1.91</v>
+        <v>2.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.46</v>
+        <v>2.9</v>
       </c>
       <c r="R11" t="n">
-        <v>2.21</v>
+        <v>2.14</v>
       </c>
       <c r="S11" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="T11" t="n">
-        <v>3.1</v>
+        <v>2.64</v>
       </c>
       <c r="U11" t="n">
-        <v>2.46</v>
+        <v>2.89</v>
       </c>
       <c r="V11" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.1</v>
+        <v>3.24</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.11</v>
+        <v>1.74</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.65</v>
+        <v>3.44</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.19</v>
+        <v>1.56</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,80 +2633,80 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.15</v>
+        <v>3.85</v>
       </c>
       <c r="O14" t="n">
-        <v>6.4</v>
+        <v>3.7</v>
       </c>
       <c r="P14" t="n">
-        <v>14.6</v>
+        <v>1.95</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.45</v>
+        <v>4</v>
       </c>
       <c r="R14" t="n">
-        <v>2.93</v>
+        <v>2.36</v>
       </c>
       <c r="S14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
         <v>1.25</v>
       </c>
-      <c r="T14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AK14" t="n">
-        <v>3.8</v>
+        <v>1.29</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>3.85</v>
+        <v>1.15</v>
       </c>
       <c r="O15" t="n">
-        <v>3.7</v>
+        <v>6.4</v>
       </c>
       <c r="P15" t="n">
-        <v>1.95</v>
+        <v>14.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>1.45</v>
       </c>
       <c r="R15" t="n">
-        <v>2.36</v>
+        <v>2.93</v>
       </c>
       <c r="S15" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T15" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U15" t="n">
-        <v>2.36</v>
+        <v>2.14</v>
       </c>
       <c r="V15" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="Z15" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.15</v>
+        <v>2.62</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.58</v>
+        <v>2.19</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.56</v>
+        <v>2.04</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.28</v>
+        <v>1.62</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.29</v>
+        <v>3.8</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2957,7 +2957,7 @@
         <v>2.6</v>
       </c>
       <c r="P16" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Q16" t="n">
         <v>3.38</v>
@@ -2975,7 +2975,7 @@
         <v>4.25</v>
       </c>
       <c r="V16" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="W16" t="n">
         <v>1.03</v>
@@ -2993,7 +2993,7 @@
         <v>3.04</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AC16" t="n">
         <v>6.5</v>
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O21" t="n">
-        <v>2.95</v>
+        <v>3.13</v>
       </c>
       <c r="P21" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="Q21" t="n">
         <v>2.97</v>
@@ -3761,37 +3761,37 @@
         <v>1.9</v>
       </c>
       <c r="S21" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="T21" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="U21" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="V21" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W21" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X21" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="AA21" t="n">
         <v>2.46</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.2</v>
+        <v>4.65</v>
       </c>
       <c r="AD21" t="n">
         <v>1.17</v>
@@ -3800,10 +3800,10 @@
         <v>1.01</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="O22" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="P22" t="n">
         <v>3.2</v>
@@ -3947,7 +3947,7 @@
         <v>2.87</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AC22" t="n">
         <v>5.15</v>
@@ -3962,7 +3962,7 @@
         <v>2.17</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4064,22 +4064,22 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="O23" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="P23" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q23" t="n">
         <v>2.75</v>
       </c>
       <c r="R23" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="S23" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="T23" t="n">
         <v>2.63</v>
@@ -4097,7 +4097,7 @@
         <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="Z23" t="n">
         <v>2.78</v>
@@ -4109,19 +4109,19 @@
         <v>1.61</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.33</v>
+        <v>3.95</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.11</v>
+        <v>2.03</v>
       </c>
       <c r="O24" t="n">
         <v>3.4</v>
       </c>
       <c r="P24" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="Q24" t="n">
         <v>2.5</v>
@@ -4268,10 +4268,10 @@
         <v>1.9</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AE24" t="n">
         <v>1.11</v>
@@ -4382,28 +4382,28 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.21</v>
+        <v>2.09</v>
       </c>
       <c r="O25" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P25" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="R25" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="S25" t="n">
         <v>1.51</v>
       </c>
       <c r="T25" t="n">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="U25" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="V25" t="n">
         <v>1.3</v>
@@ -4412,25 +4412,25 @@
         <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.66</v>
+        <v>2.85</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.43</v>
+        <v>2.29</v>
       </c>
       <c r="AB25" t="n">
         <v>1.56</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AE25" t="n">
         <v>1.01</v>
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AK25" t="n">
         <v>1.57</v>
@@ -4700,31 +4700,31 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="O27" t="n">
-        <v>3.45</v>
+        <v>3.48</v>
       </c>
       <c r="P27" t="n">
-        <v>3.9</v>
+        <v>4.36</v>
       </c>
       <c r="Q27" t="n">
         <v>2.39</v>
       </c>
       <c r="R27" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="S27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V27" t="n">
         <v>1.36</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.33</v>
       </c>
       <c r="W27" t="n">
         <v>1.07</v>
@@ -4733,25 +4733,25 @@
         <v>1.06</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF27" t="n">
         <v>1.84</v>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.46</v>
+        <v>2.22</v>
       </c>
       <c r="O28" t="n">
         <v>3.1</v>
       </c>
       <c r="P28" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.21</v>
+        <v>1.85</v>
       </c>
       <c r="O2" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P2" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.86</v>
+        <v>2.37</v>
       </c>
       <c r="R2" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="S2" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="T2" t="n">
-        <v>2.56</v>
+        <v>2.81</v>
       </c>
       <c r="U2" t="n">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="V2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W2" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.89</v>
+        <v>3.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AC2" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,80 +884,80 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3.44</v>
+        <v>2.21</v>
       </c>
       <c r="O3" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="P3" t="n">
-        <v>2.18</v>
+        <v>3.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.93</v>
+        <v>2.86</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="S3" t="n">
         <v>1.45</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="U3" t="n">
-        <v>3.48</v>
+        <v>2.86</v>
       </c>
       <c r="V3" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.57</v>
+        <v>2.89</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="AB3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AK3" t="n">
         <v>1.55</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.26</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,80 +1043,80 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.85</v>
+        <v>3.44</v>
       </c>
       <c r="O4" t="n">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="P4" t="n">
-        <v>3.75</v>
+        <v>2.18</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.37</v>
+        <v>3.93</v>
       </c>
       <c r="R4" t="n">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="S4" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="T4" t="n">
-        <v>2.81</v>
+        <v>2.4</v>
       </c>
       <c r="U4" t="n">
-        <v>2.75</v>
+        <v>3.48</v>
       </c>
       <c r="V4" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="W4" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="X4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE4" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AF4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK4" t="n">
         <v>1.26</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.85</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="O8" t="n">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="P8" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.46</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>2.21</v>
+        <v>2.33</v>
       </c>
       <c r="S8" t="n">
         <v>1.32</v>
@@ -1709,13 +1709,13 @@
         <v>1.1</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
         <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.1</v>
+        <v>3.96</v>
       </c>
       <c r="AA8" t="n">
         <v>1.7</v>
@@ -1733,10 +1733,10 @@
         <v>1.12</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1841,55 +1841,55 @@
         <v>1.2</v>
       </c>
       <c r="O9" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="P9" t="n">
         <v>13</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="R9" t="n">
-        <v>2.84</v>
+        <v>2.98</v>
       </c>
       <c r="S9" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="T9" t="n">
-        <v>3.66</v>
+        <v>3.35</v>
       </c>
       <c r="U9" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V9" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="W9" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
         <v>1.14</v>
       </c>
       <c r="Z9" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF9" t="n">
         <v>2.25</v>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AK9" t="n">
-        <v>4.75</v>
+        <v>5.45</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.57</v>
+        <v>2.19</v>
       </c>
       <c r="O10" t="n">
-        <v>4.33</v>
+        <v>3.33</v>
       </c>
       <c r="P10" t="n">
-        <v>4.81</v>
+        <v>2.69</v>
       </c>
       <c r="Q10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R10" t="n">
         <v>2.1</v>
       </c>
-      <c r="R10" t="n">
-        <v>2.45</v>
-      </c>
       <c r="S10" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="T10" t="n">
-        <v>3.07</v>
+        <v>2.75</v>
       </c>
       <c r="U10" t="n">
-        <v>2.24</v>
+        <v>2.89</v>
       </c>
       <c r="V10" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="W10" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.6</v>
+        <v>3.05</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.54</v>
+        <v>1.86</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.27</v>
+        <v>1.85</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.18</v>
+        <v>2.84</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.56</v>
+        <v>1.37</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.35</v>
+        <v>1.47</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,65 +2156,65 @@
         </is>
       </c>
       <c r="N11" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="O11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P11" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG11" t="n">
         <v>2.25</v>
       </c>
-      <c r="O11" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AH11" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.56</v>
+        <v>2</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="O12" t="n">
-        <v>3.24</v>
+        <v>3.03</v>
       </c>
       <c r="P12" t="n">
-        <v>3.61</v>
+        <v>3.33</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.3</v>
+        <v>2.82</v>
       </c>
       <c r="R12" t="n">
-        <v>2.38</v>
+        <v>1.92</v>
       </c>
       <c r="S12" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="T12" t="n">
-        <v>3.4</v>
+        <v>2.41</v>
       </c>
       <c r="U12" t="n">
-        <v>2.39</v>
+        <v>3.16</v>
       </c>
       <c r="V12" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="W12" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.4</v>
+        <v>2.75</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.61</v>
+        <v>2.35</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.25</v>
+        <v>1.57</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.45</v>
+        <v>4.15</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.52</v>
+        <v>1.2</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="O13" t="n">
-        <v>2.95</v>
+        <v>3.24</v>
       </c>
       <c r="P13" t="n">
-        <v>3.55</v>
+        <v>3.61</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.82</v>
+        <v>2.3</v>
       </c>
       <c r="R13" t="n">
-        <v>1.92</v>
+        <v>2.38</v>
       </c>
       <c r="S13" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="T13" t="n">
-        <v>2.41</v>
+        <v>3.4</v>
       </c>
       <c r="U13" t="n">
-        <v>3.25</v>
+        <v>2.39</v>
       </c>
       <c r="V13" t="n">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.68</v>
+        <v>4.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.21</v>
+        <v>1.61</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.59</v>
+        <v>2.25</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.5</v>
+        <v>2.45</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.17</v>
+        <v>1.52</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>3.85</v>
+        <v>3.39</v>
       </c>
       <c r="O14" t="n">
         <v>3.7</v>
       </c>
       <c r="P14" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="Q14" t="n">
         <v>4</v>
@@ -2648,13 +2648,13 @@
         <v>2.36</v>
       </c>
       <c r="S14" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T14" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>2.36</v>
+        <v>2.41</v>
       </c>
       <c r="V14" t="n">
         <v>1.53</v>
@@ -2663,13 +2663,13 @@
         <v>1.1</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z14" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AA14" t="n">
         <v>1.66</v>
@@ -2681,16 +2681,16 @@
         <v>2.58</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AE14" t="n">
         <v>1.14</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U15" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="V15" t="n">
         <v>1.15</v>
       </c>
-      <c r="O15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="P15" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="Q15" t="n">
+      <c r="W15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AK15" t="n">
         <v>1.45</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>3.8</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.37</v>
+        <v>1.15</v>
       </c>
       <c r="O16" t="n">
-        <v>2.6</v>
+        <v>6.4</v>
       </c>
       <c r="P16" t="n">
-        <v>3.2</v>
+        <v>15</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.38</v>
+        <v>1.45</v>
       </c>
       <c r="R16" t="n">
-        <v>1.66</v>
+        <v>3</v>
       </c>
       <c r="S16" t="n">
-        <v>1.74</v>
+        <v>1.22</v>
       </c>
       <c r="T16" t="n">
-        <v>2.08</v>
+        <v>3.66</v>
       </c>
       <c r="U16" t="n">
-        <v>4.25</v>
+        <v>2.09</v>
       </c>
       <c r="V16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W16" t="n">
         <v>1.15</v>
       </c>
-      <c r="W16" t="n">
-        <v>1.03</v>
-      </c>
       <c r="X16" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.71</v>
+        <v>1.11</v>
       </c>
       <c r="Z16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF16" t="n">
         <v>2.1</v>
       </c>
-      <c r="AA16" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AG16" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.4</v>
+        <v>1.05</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.45</v>
+        <v>3.8</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3110,40 +3110,40 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="O17" t="n">
-        <v>3.6</v>
+        <v>3.43</v>
       </c>
       <c r="P17" t="n">
         <v>3.33</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="R17" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="S17" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T17" t="n">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="U17" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="V17" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W17" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
         <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z17" t="n">
         <v>3.55</v>
@@ -3155,19 +3155,19 @@
         <v>2</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>1.24</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3269,55 +3269,55 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.37</v>
+        <v>2.18</v>
       </c>
       <c r="O18" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="P18" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="Q18" t="n">
         <v>3.1</v>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S18" t="n">
         <v>1.47</v>
       </c>
       <c r="T18" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="U18" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="V18" t="n">
         <v>1.3</v>
       </c>
       <c r="W18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X18" t="n">
         <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AE18" t="n">
         <v>1.02</v>
@@ -3342,7 +3342,7 @@
         <v>1.27</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.25</v>
+        <v>14</v>
       </c>
       <c r="O19" t="n">
-        <v>3.5</v>
+        <v>7.2</v>
       </c>
       <c r="P19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>12</v>
+      </c>
+      <c r="R19" t="n">
         <v>3</v>
       </c>
-      <c r="Q19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R19" t="n">
-        <v>2.25</v>
-      </c>
       <c r="S19" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="T19" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="U19" t="n">
-        <v>2.45</v>
+        <v>2.01</v>
       </c>
       <c r="V19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AA19" t="n">
         <v>1.44</v>
       </c>
-      <c r="W19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AB19" t="n">
-        <v>2.07</v>
+        <v>2.44</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.8</v>
+        <v>2.13</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.57</v>
+        <v>2.55</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.23</v>
+        <v>1.45</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.28</v>
+        <v>1.09</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.54</v>
+        <v>1.08</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>19</v>
+        <v>2.25</v>
       </c>
       <c r="O20" t="n">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="P20" t="n">
-        <v>1.11</v>
+        <v>2.55</v>
       </c>
       <c r="Q20" t="n">
-        <v>14.5</v>
+        <v>2.75</v>
       </c>
       <c r="R20" t="n">
-        <v>2.95</v>
+        <v>2.25</v>
       </c>
       <c r="S20" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="T20" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="U20" t="n">
-        <v>2.01</v>
+        <v>2.55</v>
       </c>
       <c r="V20" t="n">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="W20" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.75</v>
+        <v>3.74</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.44</v>
+        <v>1.72</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.5</v>
+        <v>2.07</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.19</v>
+        <v>2.88</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.55</v>
+        <v>1.58</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.45</v>
+        <v>2.23</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.09</v>
+        <v>1.28</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.08</v>
+        <v>1.54</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,28 +4064,28 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="O23" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="P23" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="R23" t="n">
-        <v>2.12</v>
+        <v>1.88</v>
       </c>
       <c r="S23" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="T23" t="n">
-        <v>2.63</v>
+        <v>2.31</v>
       </c>
       <c r="U23" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="V23" t="n">
         <v>1.3</v>
@@ -4094,50 +4094,50 @@
         <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23" t="n">
         <v>1.34</v>
       </c>
-      <c r="Z23" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AK23" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,28 +4382,28 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="O25" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="P25" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="R25" t="n">
-        <v>1.88</v>
+        <v>2.12</v>
       </c>
       <c r="S25" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="T25" t="n">
-        <v>2.31</v>
+        <v>2.63</v>
       </c>
       <c r="U25" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="V25" t="n">
         <v>1.3</v>
@@ -4412,34 +4412,34 @@
         <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.99</v>
+        <v>1.79</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.85</v>
+        <v>2.21</v>
       </c>
       <c r="O2" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P2" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.37</v>
+        <v>2.86</v>
       </c>
       <c r="R2" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="S2" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="T2" t="n">
-        <v>2.81</v>
+        <v>2.56</v>
       </c>
       <c r="U2" t="n">
-        <v>2.75</v>
+        <v>2.86</v>
       </c>
       <c r="V2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W2" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.4</v>
+        <v>2.89</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AB2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF2" t="n">
         <v>1.83</v>
       </c>
-      <c r="AC2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AG2" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.21</v>
+        <v>3.44</v>
       </c>
       <c r="O3" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="P3" t="n">
-        <v>3.3</v>
+        <v>2.18</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.86</v>
+        <v>3.93</v>
       </c>
       <c r="R3" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="S3" t="n">
         <v>1.45</v>
       </c>
       <c r="T3" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="U3" t="n">
-        <v>2.86</v>
+        <v>3.48</v>
       </c>
       <c r="V3" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
         <v>1.05</v>
       </c>
-      <c r="X3" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y3" t="n">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.89</v>
+        <v>2.57</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AC3" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.55</v>
+        <v>1.26</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.44</v>
+        <v>1.85</v>
       </c>
       <c r="O4" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="P4" t="n">
-        <v>2.18</v>
+        <v>3.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.93</v>
+        <v>2.37</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="S4" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="T4" t="n">
-        <v>2.4</v>
+        <v>2.81</v>
       </c>
       <c r="U4" t="n">
-        <v>3.48</v>
+        <v>2.75</v>
       </c>
       <c r="V4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y4" t="n">
         <v>1.26</v>
       </c>
-      <c r="W4" t="n">
-        <v>1</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.47</v>
-      </c>
       <c r="Z4" t="n">
-        <v>2.57</v>
+        <v>3.4</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.02</v>
+        <v>1.78</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.26</v>
+        <v>1.85</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.3</v>
+        <v>2.19</v>
       </c>
       <c r="O8" t="n">
-        <v>3.62</v>
+        <v>3.33</v>
       </c>
       <c r="P8" t="n">
-        <v>1.89</v>
+        <v>2.69</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="R8" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="S8" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="T8" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="U8" t="n">
-        <v>2.46</v>
+        <v>2.89</v>
       </c>
       <c r="V8" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
         <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.96</v>
+        <v>3.05</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.65</v>
+        <v>2.84</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.21</v>
+        <v>1.47</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,65 +1838,65 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.2</v>
+        <v>1.68</v>
       </c>
       <c r="O9" t="n">
-        <v>7.5</v>
+        <v>4.2</v>
       </c>
       <c r="P9" t="n">
-        <v>13</v>
+        <v>4.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.46</v>
+        <v>2.2</v>
       </c>
       <c r="R9" t="n">
-        <v>2.98</v>
+        <v>2.48</v>
       </c>
       <c r="S9" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="T9" t="n">
-        <v>3.35</v>
+        <v>3.07</v>
       </c>
       <c r="U9" t="n">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="V9" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="W9" t="n">
         <v>1.13</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.55</v>
+        <v>2.22</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.27</v>
+        <v>2.45</v>
       </c>
       <c r="AD9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF9" t="n">
         <v>1.6</v>
       </c>
-      <c r="AE9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF9" t="n">
+      <c r="AG9" t="n">
         <v>2.25</v>
       </c>
-      <c r="AG9" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AK9" t="n">
-        <v>5.45</v>
+        <v>2</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.19</v>
+        <v>3.3</v>
       </c>
       <c r="O10" t="n">
-        <v>3.33</v>
+        <v>3.62</v>
       </c>
       <c r="P10" t="n">
-        <v>2.69</v>
+        <v>1.89</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="S10" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="T10" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="U10" t="n">
-        <v>2.89</v>
+        <v>2.46</v>
       </c>
       <c r="V10" t="n">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X10" t="n">
         <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.05</v>
+        <v>3.96</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.85</v>
+        <v>2.11</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.84</v>
+        <v>2.65</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.47</v>
+        <v>1.21</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.68</v>
+        <v>1.2</v>
       </c>
       <c r="O11" t="n">
-        <v>4.2</v>
+        <v>7.5</v>
       </c>
       <c r="P11" t="n">
-        <v>4.25</v>
+        <v>13</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.2</v>
+        <v>1.46</v>
       </c>
       <c r="R11" t="n">
-        <v>2.48</v>
+        <v>2.98</v>
       </c>
       <c r="S11" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="T11" t="n">
-        <v>3.07</v>
+        <v>3.35</v>
       </c>
       <c r="U11" t="n">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="V11" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="W11" t="n">
         <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z11" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.22</v>
+        <v>2.55</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.45</v>
+        <v>2.27</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.25</v>
+        <v>1.57</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AK11" t="n">
-        <v>2</v>
+        <v>5.45</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>3.39</v>
+        <v>2.37</v>
       </c>
       <c r="O14" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="P14" t="n">
-        <v>1.97</v>
+        <v>3.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>3.38</v>
       </c>
       <c r="R14" t="n">
-        <v>2.36</v>
+        <v>1.66</v>
       </c>
       <c r="S14" t="n">
-        <v>1.32</v>
+        <v>1.74</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>2.08</v>
       </c>
       <c r="U14" t="n">
-        <v>2.41</v>
+        <v>4.25</v>
       </c>
       <c r="V14" t="n">
-        <v>1.53</v>
+        <v>1.15</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.16</v>
+        <v>1.71</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.66</v>
+        <v>3.04</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.15</v>
+        <v>1.29</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.58</v>
+        <v>6.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.43</v>
+        <v>1.06</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.55</v>
+        <v>2.25</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.25</v>
+        <v>1.57</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.37</v>
+        <v>3.39</v>
       </c>
       <c r="O15" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="P15" t="n">
-        <v>3.2</v>
+        <v>1.97</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.38</v>
+        <v>4</v>
       </c>
       <c r="R15" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA15" t="n">
         <v>1.66</v>
       </c>
-      <c r="S15" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U15" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>3.04</v>
-      </c>
       <c r="AB15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK15" t="n">
         <v>1.29</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.45</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>14</v>
+        <v>2.25</v>
       </c>
       <c r="O19" t="n">
-        <v>7.2</v>
+        <v>3.5</v>
       </c>
       <c r="P19" t="n">
-        <v>1.09</v>
+        <v>2.55</v>
       </c>
       <c r="Q19" t="n">
-        <v>12</v>
+        <v>2.75</v>
       </c>
       <c r="R19" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="S19" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="T19" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="U19" t="n">
-        <v>2.01</v>
+        <v>2.55</v>
       </c>
       <c r="V19" t="n">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="W19" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.2</v>
+        <v>3.74</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.44</v>
+        <v>1.72</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.44</v>
+        <v>2.07</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.13</v>
+        <v>2.88</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.55</v>
+        <v>1.58</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.45</v>
+        <v>2.23</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.09</v>
+        <v>1.28</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.08</v>
+        <v>1.54</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,80 +3587,80 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.25</v>
+        <v>14</v>
       </c>
       <c r="O20" t="n">
-        <v>3.5</v>
+        <v>7.2</v>
       </c>
       <c r="P20" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>12</v>
+      </c>
+      <c r="R20" t="n">
+        <v>3</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF20" t="n">
         <v>2.55</v>
       </c>
-      <c r="Q20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="W20" t="n">
+      <c r="AG20" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK20" t="n">
         <v>1.08</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.54</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3752,58 +3752,58 @@
         <v>3.13</v>
       </c>
       <c r="P21" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
         <v>1.9</v>
       </c>
       <c r="S21" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="T21" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="U21" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="V21" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W21" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="Z21" t="n">
         <v>2.6</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.65</v>
+        <v>4.75</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>1.32</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="O23" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="P23" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="S23" t="n">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="T23" t="n">
-        <v>2.31</v>
+        <v>3.07</v>
       </c>
       <c r="U23" t="n">
-        <v>3.2</v>
+        <v>2.59</v>
       </c>
       <c r="V23" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X23" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.29</v>
+        <v>1.94</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.56</v>
+        <v>1.9</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.2</v>
+        <v>3.08</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.99</v>
+        <v>1.7</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.73</v>
+        <v>2.04</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="O24" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="P24" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="R24" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S24" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="T24" t="n">
-        <v>3.07</v>
+        <v>2.63</v>
       </c>
       <c r="U24" t="n">
-        <v>2.59</v>
+        <v>3.16</v>
       </c>
       <c r="V24" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="W24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X24" t="n">
         <v>1.04</v>
       </c>
-      <c r="X24" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y24" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.4</v>
+        <v>2.78</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.94</v>
+        <v>2.26</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.08</v>
+        <v>3.95</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.04</v>
+        <v>1.89</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,28 +4382,28 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="O25" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="P25" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="R25" t="n">
-        <v>2.12</v>
+        <v>1.88</v>
       </c>
       <c r="S25" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="T25" t="n">
-        <v>2.63</v>
+        <v>2.31</v>
       </c>
       <c r="U25" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="V25" t="n">
         <v>1.3</v>
@@ -4412,50 +4412,50 @@
         <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25" t="n">
         <v>1.34</v>
       </c>
-      <c r="Z25" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AK25" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4700,7 +4700,7 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="O27" t="n">
         <v>3.48</v>
@@ -4715,13 +4715,13 @@
         <v>2.1</v>
       </c>
       <c r="S27" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T27" t="n">
         <v>2.86</v>
       </c>
       <c r="U27" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="V27" t="n">
         <v>1.36</v>
@@ -4736,7 +4736,7 @@
         <v>1.31</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.95</v>
+        <v>3.58</v>
       </c>
       <c r="AA27" t="n">
         <v>2.02</v>
@@ -4751,13 +4751,13 @@
         <v>1.24</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF27" t="n">
         <v>1.84</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>1.25</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.19</v>
+        <v>1.16</v>
       </c>
       <c r="O8" t="n">
-        <v>3.33</v>
+        <v>7.3</v>
       </c>
       <c r="P8" t="n">
-        <v>2.69</v>
+        <v>12.35</v>
       </c>
       <c r="Q8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R8" t="n">
         <v>2.8</v>
       </c>
-      <c r="R8" t="n">
-        <v>2.1</v>
-      </c>
       <c r="S8" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="T8" t="n">
-        <v>2.75</v>
+        <v>3.88</v>
       </c>
       <c r="U8" t="n">
-        <v>2.89</v>
+        <v>2.18</v>
       </c>
       <c r="V8" t="n">
-        <v>1.36</v>
+        <v>1.64</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.05</v>
+        <v>5.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.86</v>
+        <v>1.48</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.85</v>
+        <v>2.55</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.84</v>
+        <v>2.35</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.37</v>
+        <v>1.68</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.35</v>
+        <v>1.09</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.47</v>
+        <v>5.5</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1838,46 +1838,46 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="O9" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="P9" t="n">
-        <v>4.25</v>
+        <v>3.65</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="R9" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="S9" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="T9" t="n">
-        <v>3.07</v>
+        <v>3.4</v>
       </c>
       <c r="U9" t="n">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="V9" t="n">
         <v>1.58</v>
       </c>
       <c r="W9" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
         <v>1.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="AB9" t="n">
         <v>2.22</v>
@@ -1889,13 +1889,13 @@
         <v>1.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK9" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="O10" t="n">
-        <v>3.62</v>
+        <v>3.75</v>
       </c>
       <c r="P10" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q10" t="n">
         <v>4</v>
@@ -2012,34 +2012,34 @@
         <v>2.33</v>
       </c>
       <c r="S10" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T10" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="U10" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="V10" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X10" t="n">
         <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="AA10" t="n">
         <v>1.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AC10" t="n">
         <v>2.65</v>
@@ -2051,7 +2051,7 @@
         <v>1.12</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AG10" t="n">
         <v>2.14</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.2</v>
+        <v>2.19</v>
       </c>
       <c r="O11" t="n">
-        <v>7.5</v>
+        <v>3.33</v>
       </c>
       <c r="P11" t="n">
-        <v>13</v>
+        <v>2.69</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.46</v>
+        <v>2.85</v>
       </c>
       <c r="R11" t="n">
-        <v>2.98</v>
+        <v>2.05</v>
       </c>
       <c r="S11" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="T11" t="n">
-        <v>3.35</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
-        <v>2.18</v>
+        <v>2.89</v>
       </c>
       <c r="V11" t="n">
-        <v>1.64</v>
+        <v>1.36</v>
       </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.44</v>
+        <v>2.03</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.55</v>
+        <v>1.74</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.27</v>
+        <v>3.45</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.09</v>
+        <v>1.27</v>
       </c>
       <c r="AK11" t="n">
-        <v>5.45</v>
+        <v>1.54</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="O12" t="n">
-        <v>3.03</v>
+        <v>3.24</v>
       </c>
       <c r="P12" t="n">
-        <v>3.33</v>
+        <v>3.61</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.82</v>
+        <v>2.3</v>
       </c>
       <c r="R12" t="n">
-        <v>1.92</v>
+        <v>2.38</v>
       </c>
       <c r="S12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="V12" t="n">
         <v>1.5</v>
       </c>
-      <c r="T12" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="U12" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.29</v>
-      </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.75</v>
+        <v>4.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.35</v>
+        <v>1.61</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.15</v>
+        <v>2.45</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.2</v>
+        <v>1.52</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="O13" t="n">
-        <v>3.24</v>
+        <v>2.95</v>
       </c>
       <c r="P13" t="n">
-        <v>3.61</v>
+        <v>3.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.3</v>
+        <v>2.49</v>
       </c>
       <c r="R13" t="n">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="S13" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="T13" t="n">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="U13" t="n">
-        <v>2.39</v>
+        <v>3.1</v>
       </c>
       <c r="V13" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.4</v>
+        <v>2.75</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.61</v>
+        <v>2.18</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.25</v>
+        <v>1.58</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.45</v>
+        <v>4.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.52</v>
+        <v>1.2</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.53</v>
+        <v>1.89</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.3</v>
+        <v>1.78</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>1.3</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.37</v>
+        <v>1.2</v>
       </c>
       <c r="O14" t="n">
-        <v>2.6</v>
+        <v>6.75</v>
       </c>
       <c r="P14" t="n">
-        <v>3.2</v>
+        <v>14.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.38</v>
+        <v>1.44</v>
       </c>
       <c r="R14" t="n">
-        <v>1.66</v>
+        <v>2.88</v>
       </c>
       <c r="S14" t="n">
-        <v>1.74</v>
+        <v>1.22</v>
       </c>
       <c r="T14" t="n">
-        <v>2.08</v>
+        <v>3.64</v>
       </c>
       <c r="U14" t="n">
-        <v>4.25</v>
+        <v>1.98</v>
       </c>
       <c r="V14" t="n">
-        <v>1.15</v>
+        <v>1.67</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="X14" t="n">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.71</v>
+        <v>1.11</v>
       </c>
       <c r="Z14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF14" t="n">
         <v>2.1</v>
       </c>
-      <c r="AA14" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AG14" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.4</v>
+        <v>1.05</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.45</v>
+        <v>3.8</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2792,31 +2792,31 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>3.39</v>
+        <v>3.25</v>
       </c>
       <c r="O15" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P15" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="R15" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="S15" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U15" t="n">
-        <v>2.41</v>
+        <v>2.31</v>
       </c>
       <c r="V15" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W15" t="n">
         <v>1.1</v>
@@ -2825,19 +2825,19 @@
         <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z15" t="n">
         <v>4.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="AD15" t="n">
         <v>1.43</v>
@@ -2846,10 +2846,10 @@
         <v>1.14</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,80 +2951,80 @@
         </is>
       </c>
       <c r="N16" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="P16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="V16" t="n">
         <v>1.15</v>
       </c>
-      <c r="O16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="P16" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="W16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AK16" t="n">
         <v>1.45</v>
-      </c>
-      <c r="R16" t="n">
-        <v>3</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>3.8</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="O17" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="P17" t="n">
-        <v>3.33</v>
+        <v>3.85</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="R17" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="S17" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T17" t="n">
-        <v>2.99</v>
+        <v>3.14</v>
       </c>
       <c r="U17" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="V17" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
         <v>1.23</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AB17" t="n">
         <v>2</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF17" t="n">
         <v>1.67</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3269,22 +3269,22 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="O18" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="P18" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="R18" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="S18" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="T18" t="n">
         <v>2.5</v>
@@ -3296,37 +3296,37 @@
         <v>1.3</v>
       </c>
       <c r="W18" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="AB18" t="n">
         <v>1.57</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="O19" t="n">
         <v>3.5</v>
       </c>
       <c r="P19" t="n">
-        <v>2.55</v>
+        <v>2.85</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="R19" t="n">
         <v>2.25</v>
       </c>
       <c r="S19" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T19" t="n">
         <v>3.1</v>
       </c>
       <c r="U19" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="V19" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.74</v>
+        <v>3.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AC19" t="n">
         <v>2.88</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3590,13 +3590,13 @@
         <v>14</v>
       </c>
       <c r="O20" t="n">
-        <v>7.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="R20" t="n">
         <v>3</v>
@@ -3605,13 +3605,13 @@
         <v>1.23</v>
       </c>
       <c r="T20" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="U20" t="n">
-        <v>2.01</v>
+        <v>2.09</v>
       </c>
       <c r="V20" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W20" t="n">
         <v>1.14</v>
@@ -3620,7 +3620,7 @@
         <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z20" t="n">
         <v>5.2</v>
@@ -3632,19 +3632,19 @@
         <v>2.44</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AF20" t="n">
         <v>2.55</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.09</v>
+        <v>5.8</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3908,10 +3908,10 @@
         <v>2.27</v>
       </c>
       <c r="O22" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="P22" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q22" t="n">
         <v>3.1</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,80 +4064,80 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="O23" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="P23" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="R23" t="n">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="S23" t="n">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="T23" t="n">
-        <v>3.07</v>
+        <v>2.31</v>
       </c>
       <c r="U23" t="n">
-        <v>2.59</v>
+        <v>3.2</v>
       </c>
       <c r="V23" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="W23" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.94</v>
+        <v>2.29</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.9</v>
+        <v>1.56</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.08</v>
+        <v>4.2</v>
       </c>
       <c r="AD23" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23" t="n">
         <v>1.34</v>
       </c>
-      <c r="AE23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AK23" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="O24" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="P24" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="R24" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="S24" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="T24" t="n">
-        <v>2.63</v>
+        <v>3.07</v>
       </c>
       <c r="U24" t="n">
-        <v>3.16</v>
+        <v>2.59</v>
       </c>
       <c r="V24" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="W24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X24" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AD24" t="n">
         <v>1.34</v>
       </c>
-      <c r="Z24" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AE24" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,28 +4382,28 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="O25" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="P25" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="R25" t="n">
-        <v>1.88</v>
+        <v>2.12</v>
       </c>
       <c r="S25" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="T25" t="n">
-        <v>2.31</v>
+        <v>2.63</v>
       </c>
       <c r="U25" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="V25" t="n">
         <v>1.3</v>
@@ -4412,34 +4412,34 @@
         <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.99</v>
+        <v>1.79</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,65 +725,65 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.21</v>
+        <v>3.1</v>
       </c>
       <c r="O2" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="P2" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.86</v>
+        <v>3.8</v>
       </c>
       <c r="R2" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="S2" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="T2" t="n">
-        <v>2.56</v>
+        <v>2.39</v>
       </c>
       <c r="U2" t="n">
-        <v>2.86</v>
+        <v>3.48</v>
       </c>
       <c r="V2" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="W2" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.89</v>
+        <v>2.57</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="AB2" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG2" t="n">
         <v>1.7</v>
       </c>
-      <c r="AC2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AH2" t="inlineStr">
         <is>
           <t>[]</t>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.55</v>
+        <v>1.29</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3.44</v>
+        <v>1.81</v>
       </c>
       <c r="O3" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="P3" t="n">
-        <v>2.18</v>
+        <v>3.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.93</v>
+        <v>2.37</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="S3" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="U3" t="n">
-        <v>3.48</v>
+        <v>2.65</v>
       </c>
       <c r="V3" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="X3" t="n">
         <v>1.05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.57</v>
+        <v>3.35</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.55</v>
+        <v>1.86</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.02</v>
+        <v>1.7</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.26</v>
+        <v>1.91</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,65 +1043,65 @@
         </is>
       </c>
       <c r="N4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG4" t="n">
         <v>1.85</v>
       </c>
-      <c r="O4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P4" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,31 +1838,31 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.74</v>
+        <v>3.9</v>
       </c>
       <c r="O9" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="P9" t="n">
-        <v>3.65</v>
+        <v>1.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="R9" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="S9" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="T9" t="n">
-        <v>3.4</v>
+        <v>2.98</v>
       </c>
       <c r="U9" t="n">
-        <v>2.12</v>
+        <v>2.45</v>
       </c>
       <c r="V9" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="W9" t="n">
         <v>1.11</v>
@@ -1874,44 +1874,44 @@
         <v>1.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.22</v>
+        <v>2.05</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AK9" t="n">
         <v>1.21</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>2.1</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,31 +1997,31 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>3.9</v>
+        <v>1.74</v>
       </c>
       <c r="O10" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="P10" t="n">
-        <v>1.9</v>
+        <v>3.65</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="R10" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="S10" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="T10" t="n">
-        <v>2.98</v>
+        <v>3.4</v>
       </c>
       <c r="U10" t="n">
-        <v>2.45</v>
+        <v>2.12</v>
       </c>
       <c r="V10" t="n">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="W10" t="n">
         <v>1.11</v>
@@ -2033,28 +2033,28 @@
         <v>1.17</v>
       </c>
       <c r="Z10" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.21</v>
+        <v>2.1</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="O12" t="n">
-        <v>3.24</v>
+        <v>2.95</v>
       </c>
       <c r="P12" t="n">
-        <v>3.61</v>
+        <v>3.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.3</v>
+        <v>2.49</v>
       </c>
       <c r="R12" t="n">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="S12" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="T12" t="n">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="U12" t="n">
-        <v>2.39</v>
+        <v>3.1</v>
       </c>
       <c r="V12" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="W12" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.4</v>
+        <v>2.75</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.61</v>
+        <v>2.18</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.25</v>
+        <v>1.58</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.45</v>
+        <v>4.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.52</v>
+        <v>1.2</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.53</v>
+        <v>1.89</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.3</v>
+        <v>1.78</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>1.3</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,80 +2474,80 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="O13" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="P13" t="n">
-        <v>3.5</v>
+        <v>3.61</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="R13" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="S13" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="T13" t="n">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="U13" t="n">
-        <v>3.1</v>
+        <v>2.39</v>
       </c>
       <c r="V13" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.18</v>
+        <v>1.61</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.58</v>
+        <v>2.27</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.5</v>
+        <v>2.48</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.2</v>
+        <v>1.51</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.89</v>
+        <v>1.53</v>
       </c>
       <c r="AG13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AK13" t="n">
         <v>1.78</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.6</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,80 +2633,80 @@
         </is>
       </c>
       <c r="N14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AK14" t="n">
         <v>1.2</v>
-      </c>
-      <c r="O14" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="P14" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>3.8</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q15" t="n">
         <v>3.25</v>
       </c>
-      <c r="O15" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3.8</v>
-      </c>
       <c r="R15" t="n">
-        <v>2.3</v>
+        <v>1.66</v>
       </c>
       <c r="S15" t="n">
-        <v>1.31</v>
+        <v>1.74</v>
       </c>
       <c r="T15" t="n">
-        <v>3.3</v>
+        <v>2.09</v>
       </c>
       <c r="U15" t="n">
-        <v>2.31</v>
+        <v>4.25</v>
       </c>
       <c r="V15" t="n">
-        <v>1.52</v>
+        <v>1.15</v>
       </c>
       <c r="W15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.1</v>
       </c>
-      <c r="X15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AE15" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.2</v>
+        <v>1.45</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.37</v>
+        <v>1.2</v>
       </c>
       <c r="O16" t="n">
-        <v>2.53</v>
+        <v>6.75</v>
       </c>
       <c r="P16" t="n">
-        <v>3.2</v>
+        <v>14.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.25</v>
+        <v>1.44</v>
       </c>
       <c r="R16" t="n">
-        <v>1.66</v>
+        <v>2.88</v>
       </c>
       <c r="S16" t="n">
-        <v>1.74</v>
+        <v>1.22</v>
       </c>
       <c r="T16" t="n">
-        <v>2.09</v>
+        <v>3.64</v>
       </c>
       <c r="U16" t="n">
-        <v>4.25</v>
+        <v>1.98</v>
       </c>
       <c r="V16" t="n">
-        <v>1.15</v>
+        <v>1.67</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="X16" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.7</v>
+        <v>1.11</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.05</v>
+        <v>6</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.04</v>
+        <v>1.43</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.33</v>
+        <v>2.48</v>
       </c>
       <c r="AC16" t="n">
-        <v>6.5</v>
+        <v>2.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.1</v>
+        <v>1.67</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.02</v>
+        <v>1.24</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.4</v>
+        <v>1.05</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.45</v>
+        <v>3.8</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.37</v>
+        <v>14</v>
       </c>
       <c r="O19" t="n">
-        <v>3.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="P19" t="n">
-        <v>2.85</v>
+        <v>1.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.85</v>
+        <v>15</v>
       </c>
       <c r="R19" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="T19" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="U19" t="n">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="V19" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AA19" t="n">
         <v>1.44</v>
       </c>
-      <c r="W19" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y19" t="n">
+      <c r="AB19" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AE19" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z19" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AF19" t="n">
-        <v>1.61</v>
+        <v>2.55</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.14</v>
+        <v>1.44</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.29</v>
+        <v>5.8</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.52</v>
+        <v>1.02</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>14</v>
+        <v>2.37</v>
       </c>
       <c r="O20" t="n">
-        <v>8.300000000000001</v>
+        <v>3.5</v>
       </c>
       <c r="P20" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W20" t="n">
         <v>1.1</v>
       </c>
-      <c r="Q20" t="n">
-        <v>15</v>
-      </c>
-      <c r="R20" t="n">
-        <v>3</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.14</v>
-      </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.44</v>
+        <v>1.71</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.44</v>
+        <v>2.05</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.21</v>
+        <v>2.88</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.64</v>
+        <v>1.38</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.55</v>
+        <v>1.61</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.44</v>
+        <v>2.14</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>5.8</v>
+        <v>1.29</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.02</v>
+        <v>1.52</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O21" t="n">
         <v>3.13</v>
@@ -3761,7 +3761,7 @@
         <v>1.9</v>
       </c>
       <c r="S21" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="T21" t="n">
         <v>2.36</v>
@@ -3779,10 +3779,10 @@
         <v>1.09</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="AA21" t="n">
         <v>2.3</v>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AK21" t="n">
         <v>1.52</v>
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="O22" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="P22" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q22" t="n">
         <v>3.1</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="O23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T23" t="n">
         <v>2.9</v>
       </c>
-      <c r="P23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.31</v>
-      </c>
       <c r="U23" t="n">
-        <v>3.2</v>
+        <v>2.59</v>
       </c>
       <c r="V23" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.29</v>
+        <v>1.94</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.56</v>
+        <v>1.9</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.2</v>
+        <v>3.08</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.99</v>
+        <v>1.7</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.73</v>
+        <v>2.04</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,80 +4223,80 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="O24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P24" t="n">
         <v>3.4</v>
       </c>
-      <c r="P24" t="n">
-        <v>3.55</v>
-      </c>
       <c r="Q24" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="R24" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="S24" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="T24" t="n">
-        <v>3.07</v>
+        <v>2.65</v>
       </c>
       <c r="U24" t="n">
-        <v>2.59</v>
+        <v>3.16</v>
       </c>
       <c r="V24" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="W24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X24" t="n">
         <v>1.04</v>
       </c>
-      <c r="X24" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y24" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF24" t="n">
+      <c r="AK24" t="n">
         <v>1.7</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.67</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,80 +4382,80 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="O25" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="P25" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="R25" t="n">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="S25" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="T25" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U25" t="n">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="V25" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25" t="n">
         <v>1.3</v>
       </c>
-      <c r="W25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AK25" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.22</v>
+        <v>2.41</v>
       </c>
       <c r="O28" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P28" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="O3" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P3" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.37</v>
+        <v>2.84</v>
       </c>
       <c r="R3" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA3" t="n">
         <v>2.1</v>
       </c>
-      <c r="S3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AB3" t="n">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="R4" t="n">
         <v>2.1</v>
       </c>
-      <c r="O4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.14</v>
-      </c>
       <c r="S4" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T4" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="U4" t="n">
-        <v>2.87</v>
+        <v>2.65</v>
       </c>
       <c r="V4" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE4" t="n">
         <v>1.07</v>
       </c>
-      <c r="Y4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB4" t="n">
+      <c r="AF4" t="n">
         <v>1.7</v>
       </c>
-      <c r="AC4" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AG4" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.16</v>
+        <v>3.9</v>
       </c>
       <c r="O8" t="n">
-        <v>7.3</v>
+        <v>3.75</v>
       </c>
       <c r="P8" t="n">
-        <v>12.35</v>
+        <v>1.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.48</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>2.8</v>
+        <v>2.33</v>
       </c>
       <c r="S8" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T8" t="n">
-        <v>3.88</v>
+        <v>2.98</v>
       </c>
       <c r="U8" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="V8" t="n">
-        <v>1.64</v>
+        <v>1.46</v>
       </c>
       <c r="W8" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.35</v>
+        <v>2.65</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.2</v>
+        <v>1.61</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.57</v>
+        <v>2.14</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="AK8" t="n">
-        <v>5.5</v>
+        <v>1.21</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,31 +1838,31 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>3.9</v>
+        <v>1.74</v>
       </c>
       <c r="O9" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="P9" t="n">
-        <v>1.9</v>
+        <v>3.65</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="R9" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="S9" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="T9" t="n">
-        <v>2.98</v>
+        <v>3.4</v>
       </c>
       <c r="U9" t="n">
-        <v>2.45</v>
+        <v>2.12</v>
       </c>
       <c r="V9" t="n">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="W9" t="n">
         <v>1.11</v>
@@ -1874,28 +1874,28 @@
         <v>1.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.21</v>
+        <v>2.1</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.74</v>
+        <v>1.16</v>
       </c>
       <c r="O10" t="n">
-        <v>3.65</v>
+        <v>7.3</v>
       </c>
       <c r="P10" t="n">
-        <v>3.65</v>
+        <v>12.35</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.1</v>
+        <v>1.48</v>
       </c>
       <c r="R10" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="S10" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T10" t="n">
-        <v>3.4</v>
+        <v>3.88</v>
       </c>
       <c r="U10" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="V10" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="W10" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.22</v>
+        <v>2.55</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.55</v>
+        <v>2.2</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.26</v>
+        <v>1.57</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.1</v>
+        <v>5.5</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,80 +2315,80 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="O12" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="P12" t="n">
-        <v>3.5</v>
+        <v>3.61</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="R12" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="S12" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="T12" t="n">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="U12" t="n">
-        <v>3.1</v>
+        <v>2.39</v>
       </c>
       <c r="V12" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="X12" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.18</v>
+        <v>1.61</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.58</v>
+        <v>2.27</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.5</v>
+        <v>2.48</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.2</v>
+        <v>1.51</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.89</v>
+        <v>1.53</v>
       </c>
       <c r="AG12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AK12" t="n">
         <v>1.78</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.6</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O13" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="P13" t="n">
-        <v>3.61</v>
+        <v>3.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
       <c r="R13" t="n">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="S13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V13" t="n">
         <v>1.29</v>
       </c>
-      <c r="T13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.5</v>
-      </c>
       <c r="W13" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="Z13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC13" t="n">
         <v>4.5</v>
       </c>
-      <c r="AA13" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.48</v>
-      </c>
       <c r="AD13" t="n">
-        <v>1.51</v>
+        <v>1.2</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.53</v>
+        <v>1.89</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.3</v>
+        <v>1.78</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2862,7 +2862,7 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="AK15" t="n">
         <v>1.45</v>
@@ -3944,7 +3944,7 @@
         <v>2.27</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="AB22" t="n">
         <v>1.4</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,80 +4064,80 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="O23" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P23" t="n">
         <v>3.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="R23" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="S23" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T23" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="U23" t="n">
-        <v>2.59</v>
+        <v>3.16</v>
       </c>
       <c r="V23" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z23" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF23" t="n">
+      <c r="AK23" t="n">
         <v>1.7</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1.67</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,80 +4223,80 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="O24" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="P24" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R24" t="n">
-        <v>2.09</v>
+        <v>1.93</v>
       </c>
       <c r="S24" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="T24" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="U24" t="n">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="V24" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24" t="n">
         <v>1.3</v>
       </c>
-      <c r="W24" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AK24" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.22</v>
+        <v>2.03</v>
       </c>
       <c r="O25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T25" t="n">
         <v>2.9</v>
       </c>
-      <c r="P25" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.5</v>
-      </c>
       <c r="U25" t="n">
-        <v>3.3</v>
+        <v>2.59</v>
       </c>
       <c r="V25" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="W25" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X25" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.52</v>
+        <v>3.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.36</v>
+        <v>1.94</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.54</v>
+        <v>1.9</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.2</v>
+        <v>3.08</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.01</v>
+        <v>1.7</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.72</v>
+        <v>2.04</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="O2" t="n">
-        <v>3.05</v>
+        <v>3.22</v>
       </c>
       <c r="P2" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AA2" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="U2" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2.45</v>
-      </c>
       <c r="AB2" t="n">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.5</v>
+        <v>3.44</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AF2" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="R3" t="n">
         <v>2.1</v>
       </c>
-      <c r="O3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.14</v>
-      </c>
       <c r="S3" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T3" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="U3" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="V3" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE3" t="n">
         <v>1.07</v>
       </c>
-      <c r="Y3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AF3" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,80 +1043,80 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.81</v>
+        <v>3.5</v>
       </c>
       <c r="O4" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P4" t="n">
-        <v>3.75</v>
+        <v>2.12</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.37</v>
+        <v>3.8</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="S4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y4" t="n">
         <v>1.4</v>
       </c>
-      <c r="T4" t="n">
-        <v>3</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.25</v>
-      </c>
       <c r="Z4" t="n">
-        <v>3.35</v>
+        <v>2.57</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.86</v>
+        <v>1.56</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="AD4" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK4" t="n">
         <v>1.29</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.91</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.74</v>
+        <v>1.16</v>
       </c>
       <c r="O9" t="n">
-        <v>3.65</v>
+        <v>7.3</v>
       </c>
       <c r="P9" t="n">
-        <v>3.65</v>
+        <v>12.35</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.1</v>
+        <v>1.48</v>
       </c>
       <c r="R9" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="S9" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T9" t="n">
-        <v>3.4</v>
+        <v>3.88</v>
       </c>
       <c r="U9" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="V9" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="W9" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.22</v>
+        <v>2.55</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.55</v>
+        <v>2.2</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.26</v>
+        <v>1.57</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.1</v>
+        <v>5.5</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.16</v>
+        <v>1.74</v>
       </c>
       <c r="O10" t="n">
-        <v>7.3</v>
+        <v>3.65</v>
       </c>
       <c r="P10" t="n">
-        <v>12.35</v>
+        <v>3.65</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.48</v>
+        <v>2.1</v>
       </c>
       <c r="R10" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="S10" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T10" t="n">
-        <v>3.88</v>
+        <v>3.4</v>
       </c>
       <c r="U10" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="V10" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="W10" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.55</v>
+        <v>2.22</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.2</v>
+        <v>1.55</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.57</v>
+        <v>2.26</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="AK10" t="n">
-        <v>5.5</v>
+        <v>2.1</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O12" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="P12" t="n">
-        <v>3.61</v>
+        <v>3.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
       <c r="R12" t="n">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="S12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V12" t="n">
         <v>1.29</v>
       </c>
-      <c r="T12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.5</v>
-      </c>
       <c r="W12" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="Z12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC12" t="n">
         <v>4.5</v>
       </c>
-      <c r="AA12" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.48</v>
-      </c>
       <c r="AD12" t="n">
-        <v>1.51</v>
+        <v>1.2</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.53</v>
+        <v>1.89</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.3</v>
+        <v>1.78</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="O13" t="n">
-        <v>2.95</v>
+        <v>3.55</v>
       </c>
       <c r="P13" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.49</v>
+        <v>2.39</v>
       </c>
       <c r="R13" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="S13" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="T13" t="n">
-        <v>2.63</v>
+        <v>2.98</v>
       </c>
       <c r="U13" t="n">
-        <v>3.1</v>
+        <v>2.36</v>
       </c>
       <c r="V13" t="n">
-        <v>1.29</v>
+        <v>1.51</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.75</v>
+        <v>4.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.18</v>
+        <v>1.61</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.58</v>
+        <v>2.17</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.5</v>
+        <v>2.48</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.2</v>
+        <v>1.52</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.78</v>
+        <v>2.38</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q14" t="n">
         <v>3.25</v>
       </c>
-      <c r="O14" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3.8</v>
-      </c>
       <c r="R14" t="n">
-        <v>2.3</v>
+        <v>1.66</v>
       </c>
       <c r="S14" t="n">
-        <v>1.31</v>
+        <v>1.74</v>
       </c>
       <c r="T14" t="n">
-        <v>3.3</v>
+        <v>2.09</v>
       </c>
       <c r="U14" t="n">
-        <v>2.31</v>
+        <v>4.25</v>
       </c>
       <c r="V14" t="n">
-        <v>1.52</v>
+        <v>1.15</v>
       </c>
       <c r="W14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.1</v>
       </c>
-      <c r="X14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AE14" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.67</v>
+        <v>1.23</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.2</v>
+        <v>1.45</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.37</v>
+        <v>1.2</v>
       </c>
       <c r="O15" t="n">
-        <v>2.55</v>
+        <v>6.75</v>
       </c>
       <c r="P15" t="n">
-        <v>3.2</v>
+        <v>14.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.25</v>
+        <v>1.44</v>
       </c>
       <c r="R15" t="n">
-        <v>1.66</v>
+        <v>2.88</v>
       </c>
       <c r="S15" t="n">
-        <v>1.74</v>
+        <v>1.22</v>
       </c>
       <c r="T15" t="n">
-        <v>2.09</v>
+        <v>3.64</v>
       </c>
       <c r="U15" t="n">
-        <v>4.25</v>
+        <v>1.98</v>
       </c>
       <c r="V15" t="n">
-        <v>1.15</v>
+        <v>1.67</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="X15" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.7</v>
+        <v>1.11</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.05</v>
+        <v>6</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.04</v>
+        <v>1.43</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.33</v>
+        <v>2.48</v>
       </c>
       <c r="AC15" t="n">
-        <v>6.5</v>
+        <v>2.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.1</v>
+        <v>1.67</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.02</v>
+        <v>1.24</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.23</v>
+        <v>1.05</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.45</v>
+        <v>3.8</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,80 +2951,80 @@
         </is>
       </c>
       <c r="N16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AK16" t="n">
         <v>1.2</v>
-      </c>
-      <c r="O16" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="P16" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>3.8</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>14</v>
+        <v>2.37</v>
       </c>
       <c r="O19" t="n">
-        <v>8.300000000000001</v>
+        <v>3.5</v>
       </c>
       <c r="P19" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W19" t="n">
         <v>1.1</v>
       </c>
-      <c r="Q19" t="n">
-        <v>15</v>
-      </c>
-      <c r="R19" t="n">
-        <v>3</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.14</v>
-      </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.44</v>
+        <v>1.71</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.44</v>
+        <v>2.05</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.21</v>
+        <v>2.88</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.64</v>
+        <v>1.38</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.55</v>
+        <v>1.61</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.44</v>
+        <v>2.14</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>5.8</v>
+        <v>1.29</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.02</v>
+        <v>1.52</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.37</v>
+        <v>14</v>
       </c>
       <c r="O20" t="n">
-        <v>3.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>2.85</v>
+        <v>1.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.85</v>
+        <v>15</v>
       </c>
       <c r="R20" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="S20" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="T20" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="U20" t="n">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="V20" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AA20" t="n">
         <v>1.44</v>
       </c>
-      <c r="W20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y20" t="n">
+      <c r="AB20" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AE20" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z20" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AF20" t="n">
-        <v>1.61</v>
+        <v>2.55</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.14</v>
+        <v>1.44</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.29</v>
+        <v>5.8</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.52</v>
+        <v>1.02</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,80 +4064,80 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="O23" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="P23" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R23" t="n">
-        <v>2.09</v>
+        <v>1.93</v>
       </c>
       <c r="S23" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="T23" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="U23" t="n">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="V23" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23" t="n">
         <v>1.3</v>
       </c>
-      <c r="W23" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AK23" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.22</v>
+        <v>2.03</v>
       </c>
       <c r="O24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T24" t="n">
         <v>2.9</v>
       </c>
-      <c r="P24" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.5</v>
-      </c>
       <c r="U24" t="n">
-        <v>3.3</v>
+        <v>2.59</v>
       </c>
       <c r="V24" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="W24" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.52</v>
+        <v>3.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.36</v>
+        <v>1.94</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.54</v>
+        <v>1.9</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.2</v>
+        <v>3.08</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.01</v>
+        <v>1.7</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.72</v>
+        <v>2.04</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,80 +4382,80 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="O25" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P25" t="n">
         <v>3.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="R25" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="S25" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T25" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="U25" t="n">
-        <v>2.59</v>
+        <v>3.16</v>
       </c>
       <c r="V25" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="W25" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y25" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z25" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF25" t="n">
+      <c r="AK25" t="n">
         <v>1.7</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.67</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="O2" t="n">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="P2" t="n">
-        <v>3.24</v>
+        <v>3.41</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.85</v>
+        <v>2.36</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S2" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T2" t="n">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="V2" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W2" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X2" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.99</v>
+        <v>3.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="O3" t="n">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="P3" t="n">
-        <v>3.41</v>
+        <v>3.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.36</v>
+        <v>2.85</v>
       </c>
       <c r="R3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AA3" t="n">
         <v>2.1</v>
       </c>
-      <c r="S3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.01</v>
-      </c>
       <c r="AB3" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.9</v>
+        <v>1.17</v>
       </c>
       <c r="O8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="P8" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T8" t="n">
         <v>3.75</v>
       </c>
-      <c r="P8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>4</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.98</v>
-      </c>
       <c r="U8" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="V8" t="n">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="Z8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.65</v>
+        <v>2.08</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.61</v>
+        <v>2.38</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.14</v>
+        <v>1.53</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.24</v>
+        <v>1.02</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.21</v>
+        <v>5</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.16</v>
+        <v>3.8</v>
       </c>
       <c r="O9" t="n">
-        <v>7.3</v>
+        <v>3.55</v>
       </c>
       <c r="P9" t="n">
-        <v>12.35</v>
+        <v>1.82</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.48</v>
+        <v>3.95</v>
       </c>
       <c r="R9" t="n">
-        <v>2.8</v>
+        <v>2.36</v>
       </c>
       <c r="S9" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T9" t="n">
-        <v>3.88</v>
+        <v>2.98</v>
       </c>
       <c r="U9" t="n">
-        <v>2.18</v>
+        <v>2.47</v>
       </c>
       <c r="V9" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.55</v>
+        <v>2.04</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.35</v>
+        <v>2.65</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.2</v>
+        <v>1.61</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.09</v>
+        <v>1.93</v>
       </c>
       <c r="AK9" t="n">
-        <v>5.5</v>
+        <v>1.25</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,80 +1997,80 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.74</v>
+        <v>2.3</v>
       </c>
       <c r="O10" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="P10" t="n">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="Q10" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="R10" t="n">
         <v>2.1</v>
       </c>
-      <c r="R10" t="n">
-        <v>2.5</v>
-      </c>
       <c r="S10" t="n">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="T10" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="U10" t="n">
-        <v>2.12</v>
+        <v>2.94</v>
       </c>
       <c r="V10" t="n">
-        <v>1.58</v>
+        <v>1.35</v>
       </c>
       <c r="W10" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.04</v>
       </c>
-      <c r="Y10" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AF10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK10" t="n">
         <v>1.55</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>2.1</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.19</v>
+        <v>1.65</v>
       </c>
       <c r="O11" t="n">
-        <v>3.33</v>
+        <v>4.33</v>
       </c>
       <c r="P11" t="n">
-        <v>2.69</v>
+        <v>3.95</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.85</v>
+        <v>2.15</v>
       </c>
       <c r="R11" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="S11" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="T11" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="U11" t="n">
-        <v>2.89</v>
+        <v>2.08</v>
       </c>
       <c r="V11" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
         <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.25</v>
+        <v>4.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.03</v>
+        <v>1.53</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.74</v>
+        <v>2.38</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.45</v>
+        <v>2.17</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>1.54</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.95</v>
+        <v>2.26</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.54</v>
+        <v>2.2</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="O12" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="P12" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="Q12" t="n">
         <v>2.49</v>
@@ -2336,37 +2336,37 @@
         <v>2.63</v>
       </c>
       <c r="U12" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="V12" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
         <v>1.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF12" t="n">
         <v>1.89</v>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2687,10 +2687,10 @@
         <v>1.02</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="AK14" t="n">
         <v>1.45</v>
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="O15" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="P15" t="n">
-        <v>14.6</v>
+        <v>11.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="R15" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="S15" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="T15" t="n">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="U15" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="V15" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="W15" t="n">
         <v>1.14</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z15" t="n">
-        <v>6</v>
+        <v>4.75</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.48</v>
+        <v>2.39</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF15" t="n">
         <v>2.1</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AK15" t="n">
         <v>3.8</v>
@@ -2951,37 +2951,37 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O16" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P16" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="R16" t="n">
         <v>2.3</v>
       </c>
       <c r="S16" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T16" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U16" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="V16" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
         <v>1.17</v>
@@ -2993,10 +2993,10 @@
         <v>1.63</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AD16" t="n">
         <v>1.43</v>
@@ -3005,7 +3005,7 @@
         <v>1.14</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AG16" t="n">
         <v>2.3</v>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3110,16 +3110,16 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="O17" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P17" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="R17" t="n">
         <v>2.2</v>
@@ -3128,7 +3128,7 @@
         <v>1.33</v>
       </c>
       <c r="T17" t="n">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
       <c r="U17" t="n">
         <v>2.47</v>
@@ -3140,31 +3140,31 @@
         <v>1.07</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="AA17" t="n">
         <v>1.74</v>
       </c>
       <c r="AB17" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG17" t="n">
         <v>2.1</v>
@@ -3269,7 +3269,7 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O18" t="n">
         <v>3.2</v>
@@ -3278,55 +3278,55 @@
         <v>3</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="R18" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="S18" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="T18" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="U18" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="V18" t="n">
         <v>1.3</v>
       </c>
       <c r="W18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X18" t="n">
         <v>1.03</v>
       </c>
-      <c r="X18" t="n">
-        <v>1.09</v>
-      </c>
       <c r="Y18" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Z18" t="n">
         <v>2.88</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.45</v>
+        <v>2.27</v>
       </c>
       <c r="AB18" t="n">
         <v>1.57</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.5</v>
+        <v>4.05</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AE18" t="n">
         <v>1.03</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3431,22 +3431,22 @@
         <v>2.37</v>
       </c>
       <c r="O19" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="P19" t="n">
         <v>2.85</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="R19" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S19" t="n">
         <v>1.3</v>
       </c>
       <c r="T19" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U19" t="n">
         <v>2.45</v>
@@ -3458,10 +3458,10 @@
         <v>1.1</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z19" t="n">
         <v>3.9</v>
@@ -3476,16 +3476,16 @@
         <v>2.88</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="O20" t="n">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Q20" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R20" t="n">
         <v>3</v>
       </c>
       <c r="S20" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="T20" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="U20" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="V20" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="W20" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X20" t="n">
         <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.2</v>
+        <v>4.65</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AE20" t="n">
         <v>1.25</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>5.8</v>
+        <v>1.1</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="O21" t="n">
         <v>3.13</v>
       </c>
       <c r="P21" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q21" t="n">
         <v>3</v>
@@ -3776,25 +3776,25 @@
         <v>1.02</v>
       </c>
       <c r="X21" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Y21" t="n">
         <v>1.42</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.49</v>
+        <v>2.68</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.75</v>
+        <v>6.07</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AE21" t="n">
         <v>1.05</v>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O22" t="n">
         <v>2.8</v>
@@ -3944,7 +3944,7 @@
         <v>2.27</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AB22" t="n">
         <v>1.4</v>
@@ -3953,7 +3953,7 @@
         <v>5.15</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AE22" t="n">
         <v>1.03</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="O23" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="P23" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="R23" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="S23" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="T23" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="U23" t="n">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="V23" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.52</v>
+        <v>2.78</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="AC23" t="n">
         <v>4.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="O24" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="P24" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="Q24" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="T24" t="n">
         <v>2.5</v>
       </c>
-      <c r="R24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.9</v>
-      </c>
       <c r="U24" t="n">
-        <v>2.59</v>
+        <v>3.3</v>
       </c>
       <c r="V24" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.4</v>
+        <v>2.49</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.94</v>
+        <v>2.45</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.9</v>
+        <v>1.53</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.08</v>
+        <v>4.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.7</v>
+        <v>2.02</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.04</v>
+        <v>1.71</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="O25" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P25" t="n">
         <v>3.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="R25" t="n">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="S25" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T25" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="U25" t="n">
-        <v>3.16</v>
+        <v>2.59</v>
       </c>
       <c r="V25" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="W25" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X25" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.78</v>
+        <v>3.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.26</v>
+        <v>1.94</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.95</v>
+        <v>3.08</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4700,43 +4700,43 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="O27" t="n">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="P27" t="n">
-        <v>4.36</v>
+        <v>4.07</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.39</v>
+        <v>2.47</v>
       </c>
       <c r="R27" t="n">
         <v>2.1</v>
       </c>
       <c r="S27" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T27" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="U27" t="n">
-        <v>2.9</v>
+        <v>3.07</v>
       </c>
       <c r="V27" t="n">
         <v>1.36</v>
       </c>
       <c r="W27" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X27" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
         <v>1.31</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="AA27" t="n">
         <v>2.02</v>
@@ -4748,10 +4748,10 @@
         <v>3.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AF27" t="n">
         <v>1.84</v>
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="O28" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P28" t="n">
-        <v>3.07</v>
+        <v>2.88</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU27"/>
+  <dimension ref="A1:AU28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Q2">
-        <v>2.55</v>
+        <v>2.85</v>
       </c>
       <c r="R2">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="S2">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="T2">
-        <v>2.53</v>
+        <v>2.85</v>
       </c>
       <c r="U2">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="V2">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W2">
+        <v>1.03</v>
+      </c>
+      <c r="X2">
         <v>1.02</v>
       </c>
-      <c r="X2">
+      <c r="Y2">
+        <v>1.3</v>
+      </c>
+      <c r="Z2">
+        <v>2.99</v>
+      </c>
+      <c r="AA2">
+        <v>2.05</v>
+      </c>
+      <c r="AB2">
+        <v>1.78</v>
+      </c>
+      <c r="AC2">
+        <v>3.5</v>
+      </c>
+      <c r="AD2">
+        <v>1.28</v>
+      </c>
+      <c r="AE2">
         <v>1.04</v>
       </c>
-      <c r="Y2">
-        <v>1.32</v>
-      </c>
-      <c r="Z2">
-        <v>3.1</v>
-      </c>
-      <c r="AA2">
-        <v>2.06</v>
-      </c>
-      <c r="AB2">
-        <v>1.72</v>
-      </c>
-      <c r="AC2">
-        <v>3.91</v>
-      </c>
-      <c r="AD2">
-        <v>1.26</v>
-      </c>
-      <c r="AE2">
-        <v>1.08</v>
-      </c>
       <c r="AF2">
-        <v>1.84</v>
+        <v>1.74</v>
       </c>
       <c r="AG2">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK2">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -801,61 +801,61 @@
         <v>1.91</v>
       </c>
       <c r="O3">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="P3">
-        <v>3.4</v>
+        <v>3.41</v>
       </c>
       <c r="Q3">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="R3">
         <v>2.1</v>
       </c>
       <c r="S3">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T3">
-        <v>2.73</v>
+        <v>3</v>
       </c>
       <c r="U3">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="V3">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W3">
+        <v>1.06</v>
+      </c>
+      <c r="X3">
         <v>1.05</v>
       </c>
-      <c r="X3">
-        <v>1.03</v>
-      </c>
       <c r="Y3">
+        <v>1.25</v>
+      </c>
+      <c r="Z3">
+        <v>3.4</v>
+      </c>
+      <c r="AA3">
+        <v>2.01</v>
+      </c>
+      <c r="AB3">
+        <v>1.84</v>
+      </c>
+      <c r="AC3">
+        <v>3.45</v>
+      </c>
+      <c r="AD3">
         <v>1.27</v>
       </c>
-      <c r="Z3">
-        <v>3.41</v>
-      </c>
-      <c r="AA3">
-        <v>1.95</v>
-      </c>
-      <c r="AB3">
-        <v>1.82</v>
-      </c>
-      <c r="AC3">
-        <v>3.4</v>
-      </c>
-      <c r="AD3">
-        <v>1.29</v>
-      </c>
       <c r="AE3">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF3">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG3">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK3">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -967,19 +967,19 @@
         <v>3</v>
       </c>
       <c r="P4">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="Q4">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="R4">
-        <v>2.03</v>
+        <v>1.94</v>
       </c>
       <c r="S4">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="T4">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="U4">
         <v>3.48</v>
@@ -988,28 +988,28 @@
         <v>1.26</v>
       </c>
       <c r="W4">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X4">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Z4">
-        <v>2.72</v>
+        <v>2.57</v>
       </c>
       <c r="AA4">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="AB4">
         <v>1.56</v>
       </c>
       <c r="AC4">
-        <v>4.73</v>
+        <v>4.5</v>
       </c>
       <c r="AD4">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AE4">
         <v>1.01</v>
@@ -1018,7 +1018,7 @@
         <v>2.02</v>
       </c>
       <c r="AG4">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>5.43</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1403,27 +1403,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,80 +1450,80 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="O7">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="P7">
-        <v>4.44</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q7">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="R7">
-        <v>2.46</v>
+        <v>2.25</v>
       </c>
       <c r="S7">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T7">
-        <v>3.07</v>
+        <v>2.88</v>
       </c>
       <c r="U7">
-        <v>2.26</v>
+        <v>2.55</v>
       </c>
       <c r="V7">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W7">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X7">
         <v>1.02</v>
       </c>
       <c r="Y7">
+        <v>1.22</v>
+      </c>
+      <c r="Z7">
+        <v>4.2</v>
+      </c>
+      <c r="AA7">
+        <v>1.73</v>
+      </c>
+      <c r="AB7">
+        <v>2.04</v>
+      </c>
+      <c r="AC7">
+        <v>2.78</v>
+      </c>
+      <c r="AD7">
+        <v>1.41</v>
+      </c>
+      <c r="AE7">
+        <v>1.13</v>
+      </c>
+      <c r="AF7">
+        <v>1.95</v>
+      </c>
+      <c r="AG7">
+        <v>1.74</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
         <v>1.17</v>
       </c>
-      <c r="Z7">
-        <v>4.3</v>
-      </c>
-      <c r="AA7">
-        <v>1.6</v>
-      </c>
-      <c r="AB7">
-        <v>2.2</v>
-      </c>
-      <c r="AC7">
-        <v>2.39</v>
-      </c>
-      <c r="AD7">
-        <v>1.46</v>
-      </c>
-      <c r="AE7">
-        <v>1.17</v>
-      </c>
-      <c r="AF7">
-        <v>1.61</v>
-      </c>
-      <c r="AG7">
-        <v>2.18</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7">
-        <v>1.2</v>
-      </c>
       <c r="AK7">
-        <v>2.1</v>
+        <v>2.93</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2026-07-21 13:00:00</t>
+          <t>2026-07-21 12:00:00</t>
         </is>
       </c>
     </row>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,80 +1613,80 @@
         </is>
       </c>
       <c r="N8">
-        <v>4.2</v>
+        <v>1.65</v>
       </c>
       <c r="O8">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="P8">
-        <v>1.72</v>
+        <v>3.95</v>
       </c>
       <c r="Q8">
-        <v>4.1</v>
+        <v>2.15</v>
       </c>
       <c r="R8">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="S8">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="T8">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U8">
-        <v>2.41</v>
+        <v>2.08</v>
       </c>
       <c r="V8">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="W8">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X8">
         <v>1.04</v>
       </c>
       <c r="Y8">
+        <v>1.13</v>
+      </c>
+      <c r="Z8">
+        <v>4.8</v>
+      </c>
+      <c r="AA8">
+        <v>1.53</v>
+      </c>
+      <c r="AB8">
+        <v>2.38</v>
+      </c>
+      <c r="AC8">
+        <v>2.17</v>
+      </c>
+      <c r="AD8">
+        <v>1.54</v>
+      </c>
+      <c r="AE8">
         <v>1.2</v>
       </c>
-      <c r="Z8">
-        <v>4.2</v>
-      </c>
-      <c r="AA8">
-        <v>1.69</v>
-      </c>
-      <c r="AB8">
-        <v>2.13</v>
-      </c>
-      <c r="AC8">
-        <v>2.55</v>
-      </c>
-      <c r="AD8">
-        <v>1.45</v>
-      </c>
-      <c r="AE8">
+      <c r="AF8">
+        <v>1.53</v>
+      </c>
+      <c r="AG8">
+        <v>2.26</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8">
         <v>1.17</v>
       </c>
-      <c r="AF8">
-        <v>1.59</v>
-      </c>
-      <c r="AG8">
-        <v>2.18</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8">
-        <v>1.81</v>
-      </c>
       <c r="AK8">
-        <v>1.19</v>
+        <v>2.2</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,80 +1776,80 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.11</v>
+        <v>2.3</v>
       </c>
       <c r="O9">
-        <v>7</v>
+        <v>3.3</v>
       </c>
       <c r="P9">
-        <v>14</v>
+        <v>3.05</v>
       </c>
       <c r="Q9">
-        <v>1.5</v>
+        <v>2.85</v>
       </c>
       <c r="R9">
-        <v>2.89</v>
+        <v>2.1</v>
       </c>
       <c r="S9">
+        <v>1.41</v>
+      </c>
+      <c r="T9">
+        <v>2.8</v>
+      </c>
+      <c r="U9">
+        <v>2.94</v>
+      </c>
+      <c r="V9">
+        <v>1.35</v>
+      </c>
+      <c r="W9">
+        <v>1.03</v>
+      </c>
+      <c r="X9">
+        <v>1.05</v>
+      </c>
+      <c r="Y9">
+        <v>1.31</v>
+      </c>
+      <c r="Z9">
+        <v>3.27</v>
+      </c>
+      <c r="AA9">
+        <v>2.08</v>
+      </c>
+      <c r="AB9">
+        <v>1.68</v>
+      </c>
+      <c r="AC9">
+        <v>3.45</v>
+      </c>
+      <c r="AD9">
+        <v>1.29</v>
+      </c>
+      <c r="AE9">
+        <v>1.04</v>
+      </c>
+      <c r="AF9">
+        <v>1.75</v>
+      </c>
+      <c r="AG9">
+        <v>1.95</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9">
         <v>1.25</v>
       </c>
-      <c r="T9">
-        <v>4</v>
-      </c>
-      <c r="U9">
-        <v>2.18</v>
-      </c>
-      <c r="V9">
-        <v>1.65</v>
-      </c>
-      <c r="W9">
-        <v>1.15</v>
-      </c>
-      <c r="X9">
-        <v>1.02</v>
-      </c>
-      <c r="Y9">
-        <v>1.11</v>
-      </c>
-      <c r="Z9">
-        <v>5.15</v>
-      </c>
-      <c r="AA9">
-        <v>1.47</v>
-      </c>
-      <c r="AB9">
-        <v>2.44</v>
-      </c>
-      <c r="AC9">
-        <v>2.08</v>
-      </c>
-      <c r="AD9">
-        <v>1.68</v>
-      </c>
-      <c r="AE9">
-        <v>1.2</v>
-      </c>
-      <c r="AF9">
-        <v>2.15</v>
-      </c>
-      <c r="AG9">
-        <v>1.63</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9">
-        <v>1.08</v>
-      </c>
       <c r="AK9">
-        <v>4.85</v>
+        <v>1.55</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.33</v>
+        <v>1.17</v>
       </c>
       <c r="O10">
-        <v>3.34</v>
+        <v>5.9</v>
       </c>
       <c r="P10">
-        <v>2.95</v>
+        <v>20</v>
       </c>
       <c r="Q10">
-        <v>2.9</v>
+        <v>1.44</v>
       </c>
       <c r="R10">
-        <v>2.09</v>
+        <v>3.1</v>
       </c>
       <c r="S10">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T10">
-        <v>2.73</v>
+        <v>3.75</v>
       </c>
       <c r="U10">
-        <v>2.73</v>
+        <v>2.05</v>
       </c>
       <c r="V10">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="W10">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="Z10">
-        <v>3.44</v>
+        <v>5</v>
       </c>
       <c r="AA10">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="AB10">
-        <v>1.89</v>
+        <v>2.5</v>
       </c>
       <c r="AC10">
-        <v>3.12</v>
+        <v>2.08</v>
       </c>
       <c r="AD10">
-        <v>1.28</v>
+        <v>1.68</v>
       </c>
       <c r="AE10">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AF10">
-        <v>1.67</v>
+        <v>2.38</v>
       </c>
       <c r="AG10">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.4</v>
+        <v>1.02</v>
       </c>
       <c r="AK10">
-        <v>1.57</v>
+        <v>5</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="O11">
-        <v>2.95</v>
+        <v>3.55</v>
       </c>
       <c r="P11">
-        <v>3.5</v>
+        <v>1.82</v>
       </c>
       <c r="Q11">
-        <v>2.7</v>
+        <v>3.95</v>
       </c>
       <c r="R11">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="S11">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="T11">
-        <v>2.63</v>
+        <v>2.98</v>
       </c>
       <c r="U11">
-        <v>3.05</v>
+        <v>2.47</v>
       </c>
       <c r="V11">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="W11">
+        <v>1.08</v>
+      </c>
+      <c r="X11">
         <v>1.01</v>
       </c>
-      <c r="X11">
-        <v>1.05</v>
-      </c>
       <c r="Y11">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="Z11">
-        <v>2.54</v>
+        <v>4.1</v>
       </c>
       <c r="AA11">
-        <v>2.24</v>
+        <v>1.67</v>
       </c>
       <c r="AB11">
-        <v>1.56</v>
+        <v>2.04</v>
       </c>
       <c r="AC11">
-        <v>4.6</v>
+        <v>2.65</v>
       </c>
       <c r="AD11">
-        <v>1.15</v>
+        <v>1.4</v>
       </c>
       <c r="AE11">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AF11">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="AG11">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.2</v>
+        <v>1.93</v>
       </c>
       <c r="AK11">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-07-21 14:00:00</t>
+          <t>2026-07-21 13:00:00</t>
         </is>
       </c>
     </row>
@@ -2223,22 +2223,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="O12">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="P12">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AA12">
-        <v>1.61</v>
+        <v>2.15</v>
       </c>
       <c r="AB12">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2381,27 +2381,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.25</v>
+        <v>1.98</v>
       </c>
       <c r="O13">
-        <v>5.7</v>
+        <v>2.88</v>
       </c>
       <c r="P13">
-        <v>11</v>
+        <v>3.2</v>
       </c>
       <c r="Q13">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="R13">
-        <v>2.78</v>
+        <v>2.3</v>
       </c>
       <c r="S13">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T13">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="U13">
-        <v>2.21</v>
+        <v>2.36</v>
       </c>
       <c r="V13">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="W13">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X13">
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z13">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="AA13">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AB13">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AC13">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="AD13">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="AE13">
         <v>1.18</v>
       </c>
       <c r="AF13">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="AG13">
-        <v>1.8</v>
+        <v>2.38</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AK13">
-        <v>3.8</v>
+        <v>1.75</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-07-21 15:00:00</t>
+          <t>2026-07-21 14:00:00</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,80 +2591,80 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.05</v>
+        <v>1.14</v>
       </c>
       <c r="O14">
-        <v>3.7</v>
+        <v>7</v>
       </c>
       <c r="P14">
-        <v>1.96</v>
+        <v>11.5</v>
       </c>
       <c r="Q14">
-        <v>3.9</v>
+        <v>1.57</v>
       </c>
       <c r="R14">
-        <v>2.28</v>
+        <v>2.75</v>
       </c>
       <c r="S14">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="T14">
         <v>3.4</v>
       </c>
       <c r="U14">
-        <v>2.34</v>
+        <v>2.05</v>
       </c>
       <c r="V14">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="W14">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X14">
+        <v>1</v>
+      </c>
+      <c r="Y14">
+        <v>1.12</v>
+      </c>
+      <c r="Z14">
+        <v>4.75</v>
+      </c>
+      <c r="AA14">
+        <v>1.46</v>
+      </c>
+      <c r="AB14">
+        <v>2.39</v>
+      </c>
+      <c r="AC14">
+        <v>2.26</v>
+      </c>
+      <c r="AD14">
+        <v>1.65</v>
+      </c>
+      <c r="AE14">
+        <v>1.25</v>
+      </c>
+      <c r="AF14">
+        <v>2.1</v>
+      </c>
+      <c r="AG14">
+        <v>1.62</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14">
         <v>1.04</v>
       </c>
-      <c r="Y14">
-        <v>1.16</v>
-      </c>
-      <c r="Z14">
-        <v>4.1</v>
-      </c>
-      <c r="AA14">
-        <v>1.65</v>
-      </c>
-      <c r="AB14">
-        <v>2.19</v>
-      </c>
-      <c r="AC14">
-        <v>2.48</v>
-      </c>
-      <c r="AD14">
-        <v>1.43</v>
-      </c>
-      <c r="AE14">
-        <v>1.14</v>
-      </c>
-      <c r="AF14">
-        <v>1.55</v>
-      </c>
-      <c r="AG14">
-        <v>2.3</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14">
-        <v>1.73</v>
-      </c>
       <c r="AK14">
-        <v>1.25</v>
+        <v>3.8</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2712,22 +2712,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.35</v>
+        <v>3.2</v>
       </c>
       <c r="O15">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="P15">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="Q15">
-        <v>3.38</v>
+        <v>3.75</v>
       </c>
       <c r="R15">
-        <v>1.66</v>
+        <v>2.3</v>
       </c>
       <c r="S15">
-        <v>1.74</v>
+        <v>1.25</v>
       </c>
       <c r="T15">
-        <v>2.08</v>
+        <v>3.25</v>
       </c>
       <c r="U15">
-        <v>4.25</v>
+        <v>2.36</v>
       </c>
       <c r="V15">
-        <v>1.15</v>
+        <v>1.5</v>
       </c>
       <c r="W15">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X15">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.71</v>
+        <v>1.17</v>
       </c>
       <c r="Z15">
-        <v>2.1</v>
+        <v>4.1</v>
       </c>
       <c r="AA15">
-        <v>3.04</v>
+        <v>1.63</v>
       </c>
       <c r="AB15">
-        <v>1.36</v>
+        <v>2.19</v>
       </c>
       <c r="AC15">
-        <v>6.5</v>
+        <v>2.7</v>
       </c>
       <c r="AD15">
-        <v>1.06</v>
+        <v>1.43</v>
       </c>
       <c r="AE15">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="AF15">
-        <v>2.4</v>
+        <v>1.57</v>
       </c>
       <c r="AG15">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.4</v>
+        <v>1.87</v>
       </c>
       <c r="AK15">
-        <v>1.45</v>
+        <v>1.21</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2870,27 +2870,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,81 +2917,81 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.91</v>
+        <v>2.37</v>
       </c>
       <c r="O16">
-        <v>3.6</v>
+        <v>2.55</v>
       </c>
       <c r="P16">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="Q16">
-        <v>2.41</v>
+        <v>3.25</v>
       </c>
       <c r="R16">
-        <v>2.16</v>
+        <v>1.66</v>
       </c>
       <c r="S16">
-        <v>1.35</v>
+        <v>1.74</v>
       </c>
       <c r="T16">
-        <v>2.94</v>
+        <v>2.09</v>
       </c>
       <c r="U16">
-        <v>2.6</v>
+        <v>4.25</v>
       </c>
       <c r="V16">
+        <v>1.15</v>
+      </c>
+      <c r="W16">
+        <v>1.03</v>
+      </c>
+      <c r="X16">
+        <v>1.13</v>
+      </c>
+      <c r="Y16">
+        <v>1.7</v>
+      </c>
+      <c r="Z16">
+        <v>2.05</v>
+      </c>
+      <c r="AA16">
+        <v>3.04</v>
+      </c>
+      <c r="AB16">
+        <v>1.33</v>
+      </c>
+      <c r="AC16">
+        <v>6.5</v>
+      </c>
+      <c r="AD16">
+        <v>1.1</v>
+      </c>
+      <c r="AE16">
+        <v>1.02</v>
+      </c>
+      <c r="AF16">
+        <v>2.4</v>
+      </c>
+      <c r="AG16">
+        <v>1.48</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16">
+        <v>1.4</v>
+      </c>
+      <c r="AK16">
         <v>1.45</v>
       </c>
-      <c r="W16">
-        <v>1.11</v>
-      </c>
-      <c r="X16">
-        <v>1.01</v>
-      </c>
-      <c r="Y16">
-        <v>1.22</v>
-      </c>
-      <c r="Z16">
-        <v>3.54</v>
-      </c>
-      <c r="AA16">
-        <v>1.8</v>
-      </c>
-      <c r="AB16">
-        <v>2.22</v>
-      </c>
-      <c r="AC16">
-        <v>2.7</v>
-      </c>
-      <c r="AD16">
-        <v>1.43</v>
-      </c>
-      <c r="AE16">
-        <v>1.17</v>
-      </c>
-      <c r="AF16">
-        <v>1.67</v>
-      </c>
-      <c r="AG16">
-        <v>2.05</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16">
-        <v>1.27</v>
-      </c>
-      <c r="AK16">
-        <v>1.85</v>
-      </c>
       <c r="AL16">
         <v>0</v>
       </c>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-07-21 15:30:00</t>
+          <t>2026-07-21 15:00:00</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.17</v>
+        <v>1.8</v>
       </c>
       <c r="O17">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="P17">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="Q17">
-        <v>3.1</v>
+        <v>2.31</v>
       </c>
       <c r="R17">
-        <v>1.96</v>
+        <v>2.2</v>
       </c>
       <c r="S17">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="T17">
-        <v>2.34</v>
+        <v>3.16</v>
       </c>
       <c r="U17">
-        <v>3.13</v>
+        <v>2.47</v>
       </c>
       <c r="V17">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="W17">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X17">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="Z17">
-        <v>2.48</v>
+        <v>3.9</v>
       </c>
       <c r="AA17">
-        <v>2.46</v>
+        <v>1.74</v>
       </c>
       <c r="AB17">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="AC17">
-        <v>4.8</v>
+        <v>2.85</v>
       </c>
       <c r="AD17">
-        <v>1.15</v>
+        <v>1.42</v>
       </c>
       <c r="AE17">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AF17">
-        <v>2.02</v>
+        <v>1.65</v>
       </c>
       <c r="AG17">
-        <v>1.69</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK17">
-        <v>1.55</v>
+        <v>1.92</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2026-07-21 15:45:00</t>
+          <t>2026-07-21 15:30:00</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>16</v>
+        <v>2.4</v>
       </c>
       <c r="O18">
-        <v>7.45</v>
+        <v>3.2</v>
       </c>
       <c r="P18">
-        <v>1.11</v>
+        <v>3</v>
       </c>
       <c r="Q18">
-        <v>13</v>
+        <v>3.1</v>
       </c>
       <c r="R18">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="S18">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="T18">
-        <v>3.7</v>
+        <v>2.56</v>
       </c>
       <c r="U18">
-        <v>2.18</v>
+        <v>3.1</v>
       </c>
       <c r="V18">
-        <v>1.64</v>
+        <v>1.3</v>
       </c>
       <c r="W18">
-        <v>1.17</v>
+        <v>1.02</v>
       </c>
       <c r="X18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y18">
-        <v>1.11</v>
+        <v>1.44</v>
       </c>
       <c r="Z18">
-        <v>4.95</v>
+        <v>2.88</v>
       </c>
       <c r="AA18">
-        <v>1.44</v>
+        <v>2.27</v>
       </c>
       <c r="AB18">
-        <v>2.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC18">
-        <v>2.17</v>
+        <v>4.05</v>
       </c>
       <c r="AD18">
-        <v>1.61</v>
+        <v>1.18</v>
       </c>
       <c r="AE18">
-        <v>1.22</v>
+        <v>1.03</v>
       </c>
       <c r="AF18">
-        <v>2.51</v>
+        <v>1.88</v>
       </c>
       <c r="AG18">
-        <v>1.46</v>
+        <v>1.78</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>5.7</v>
+        <v>1.33</v>
       </c>
       <c r="AK18">
-        <v>1.02</v>
+        <v>1.53</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2026-07-21 16:00:00</t>
+          <t>2026-07-21 15:45:00</t>
         </is>
       </c>
     </row>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.3</v>
+        <v>16.5</v>
       </c>
       <c r="O19">
+        <v>8</v>
+      </c>
+      <c r="P19">
+        <v>1.14</v>
+      </c>
+      <c r="Q19">
+        <v>13</v>
+      </c>
+      <c r="R19">
+        <v>3</v>
+      </c>
+      <c r="S19">
+        <v>1.24</v>
+      </c>
+      <c r="T19">
         <v>3.5</v>
       </c>
-      <c r="P19">
-        <v>3</v>
-      </c>
-      <c r="Q19">
-        <v>2.8</v>
-      </c>
-      <c r="R19">
-        <v>2.2</v>
-      </c>
-      <c r="S19">
-        <v>1.3</v>
-      </c>
-      <c r="T19">
-        <v>3.2</v>
-      </c>
       <c r="U19">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="V19">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="W19">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X19">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="Z19">
-        <v>4</v>
+        <v>4.65</v>
       </c>
       <c r="AA19">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AB19">
-        <v>2.06</v>
+        <v>2.55</v>
       </c>
       <c r="AC19">
-        <v>2.66</v>
+        <v>2.23</v>
       </c>
       <c r="AD19">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="AE19">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AF19">
-        <v>1.57</v>
+        <v>2.43</v>
       </c>
       <c r="AG19">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="AK19">
-        <v>1.57</v>
+        <v>1.03</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3522,27 +3522,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.55</v>
+        <v>2.37</v>
       </c>
       <c r="O20">
-        <v>3.05</v>
+        <v>3.48</v>
       </c>
       <c r="P20">
+        <v>2.85</v>
+      </c>
+      <c r="Q20">
         <v>2.8</v>
       </c>
-      <c r="Q20">
-        <v>0</v>
-      </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2026-07-21 18:30:00</t>
+          <t>2026-07-21 16:00:00</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G21">
@@ -3735,61 +3735,61 @@
         <v>2.3</v>
       </c>
       <c r="O21">
-        <v>2.75</v>
+        <v>3.13</v>
       </c>
       <c r="P21">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q21">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R21">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="S21">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="T21">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="U21">
-        <v>3.74</v>
+        <v>3.25</v>
       </c>
       <c r="V21">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="W21">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X21">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Y21">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="Z21">
-        <v>2.25</v>
+        <v>2.68</v>
       </c>
       <c r="AA21">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="AB21">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AC21">
-        <v>5.75</v>
+        <v>6.07</v>
       </c>
       <c r="AD21">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AE21">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF21">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AG21">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AK21">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00:00</t>
+          <t>2026-07-21 18:30:00</t>
         </is>
       </c>
     </row>
@@ -3848,12 +3848,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="O22">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="P22">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="Q22">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="R22">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="S22">
-        <v>1.42</v>
+        <v>1.61</v>
       </c>
       <c r="T22">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="U22">
+        <v>3.72</v>
+      </c>
+      <c r="V22">
+        <v>1.2</v>
+      </c>
+      <c r="W22">
+        <v>1.03</v>
+      </c>
+      <c r="X22">
+        <v>1.09</v>
+      </c>
+      <c r="Y22">
+        <v>1.58</v>
+      </c>
+      <c r="Z22">
+        <v>2.27</v>
+      </c>
+      <c r="AA22">
         <v>2.62</v>
       </c>
-      <c r="V22">
-        <v>1.39</v>
-      </c>
-      <c r="W22">
-        <v>1.04</v>
-      </c>
-      <c r="X22">
-        <v>1.02</v>
-      </c>
-      <c r="Y22">
-        <v>1.32</v>
-      </c>
-      <c r="Z22">
-        <v>3.38</v>
-      </c>
-      <c r="AA22">
-        <v>1.94</v>
-      </c>
       <c r="AB22">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="AC22">
-        <v>3.75</v>
+        <v>5.15</v>
       </c>
       <c r="AD22">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AE22">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AF22">
-        <v>1.7</v>
+        <v>2.17</v>
       </c>
       <c r="AG22">
-        <v>2.04</v>
+        <v>1.6</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AK22">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2026-07-21 19:30:00</t>
+          <t>2026-07-21 19:00:00</t>
         </is>
       </c>
     </row>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="O23">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="P23">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="Q23">
+        <v>2.5</v>
+      </c>
+      <c r="R23">
+        <v>2.2</v>
+      </c>
+      <c r="S23">
+        <v>1.38</v>
+      </c>
+      <c r="T23">
         <v>2.8</v>
       </c>
-      <c r="R23">
-        <v>1.96</v>
-      </c>
-      <c r="S23">
-        <v>1.42</v>
-      </c>
-      <c r="T23">
-        <v>2.65</v>
-      </c>
       <c r="U23">
-        <v>3.16</v>
+        <v>2.59</v>
       </c>
       <c r="V23">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="W23">
+        <v>1.09</v>
+      </c>
+      <c r="X23">
         <v>1.01</v>
       </c>
-      <c r="X23">
-        <v>1.08</v>
-      </c>
       <c r="Y23">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="Z23">
-        <v>2.78</v>
+        <v>3.38</v>
       </c>
       <c r="AA23">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="AB23">
-        <v>1.61</v>
+        <v>1.92</v>
       </c>
       <c r="AC23">
-        <v>4.2</v>
+        <v>3.08</v>
       </c>
       <c r="AD23">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE23">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AF23">
-        <v>1.91</v>
+        <v>1.69</v>
       </c>
       <c r="AG23">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK23">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="O24">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="P24">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="Q24">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="R24">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="S24">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="T24">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="U24">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="V24">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X24">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y24">
         <v>1.42</v>
       </c>
       <c r="Z24">
-        <v>2.49</v>
+        <v>2.78</v>
       </c>
       <c r="AA24">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AB24">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AC24">
         <v>4.2</v>
       </c>
       <c r="AD24">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AE24">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF24">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AG24">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK24">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4337,12 +4337,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.51</v>
+        <v>2.15</v>
       </c>
       <c r="O25">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="P25">
-        <v>4.7</v>
+        <v>3.45</v>
       </c>
       <c r="Q25">
-        <v>2</v>
+        <v>2.88</v>
       </c>
       <c r="R25">
-        <v>2.29</v>
+        <v>1.88</v>
       </c>
       <c r="S25">
+        <v>1.48</v>
+      </c>
+      <c r="T25">
+        <v>2.5</v>
+      </c>
+      <c r="U25">
+        <v>3.3</v>
+      </c>
+      <c r="V25">
         <v>1.27</v>
       </c>
-      <c r="T25">
-        <v>3.25</v>
-      </c>
-      <c r="U25">
-        <v>2.25</v>
-      </c>
-      <c r="V25">
-        <v>1.57</v>
-      </c>
       <c r="W25">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="X25">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y25">
-        <v>1.12</v>
+        <v>1.42</v>
       </c>
       <c r="Z25">
-        <v>4.65</v>
+        <v>2.49</v>
       </c>
       <c r="AA25">
-        <v>1.55</v>
+        <v>2.45</v>
       </c>
       <c r="AB25">
-        <v>2.29</v>
+        <v>1.53</v>
       </c>
       <c r="AC25">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
       <c r="AD25">
-        <v>1.48</v>
+        <v>1.14</v>
       </c>
       <c r="AE25">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="AF25">
-        <v>1.59</v>
+        <v>2.02</v>
       </c>
       <c r="AG25">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AK25">
-        <v>2.3</v>
+        <v>1.64</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>2026-07-21 20:00:00</t>
+          <t>2026-07-21 19:30:00</t>
         </is>
       </c>
     </row>
@@ -4500,12 +4500,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.32</v>
+        <v>1.51</v>
       </c>
       <c r="O26">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="P26">
-        <v>2.95</v>
+        <v>4.7</v>
       </c>
       <c r="Q26">
-        <v>2.95</v>
+        <v>2</v>
       </c>
       <c r="R26">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="S26">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="T26">
-        <v>2.63</v>
+        <v>3.25</v>
       </c>
       <c r="U26">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="V26">
-        <v>1.34</v>
+        <v>1.57</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.35</v>
+        <v>1.12</v>
       </c>
       <c r="Z26">
-        <v>2.88</v>
+        <v>4.65</v>
       </c>
       <c r="AA26">
-        <v>2.07</v>
+        <v>1.55</v>
       </c>
       <c r="AB26">
-        <v>1.65</v>
+        <v>2.29</v>
       </c>
       <c r="AC26">
-        <v>3.65</v>
+        <v>2.3</v>
       </c>
       <c r="AD26">
-        <v>1.23</v>
+        <v>1.48</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF26">
-        <v>1.82</v>
+        <v>1.59</v>
       </c>
       <c r="AG26">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AK26">
-        <v>1.52</v>
+        <v>2.3</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>2026-07-21 21:00:00</t>
+          <t>2026-07-21 20:00:00</t>
         </is>
       </c>
     </row>
@@ -4663,156 +4663,319 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>CD Universidad Católica</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N27">
+        <v>1.87</v>
+      </c>
+      <c r="O27">
+        <v>3.42</v>
+      </c>
+      <c r="P27">
+        <v>4.07</v>
+      </c>
+      <c r="Q27">
+        <v>2.47</v>
+      </c>
+      <c r="R27">
+        <v>2.1</v>
+      </c>
+      <c r="S27">
+        <v>1.38</v>
+      </c>
+      <c r="T27">
+        <v>2.84</v>
+      </c>
+      <c r="U27">
+        <v>3.07</v>
+      </c>
+      <c r="V27">
+        <v>1.36</v>
+      </c>
+      <c r="W27">
+        <v>1.06</v>
+      </c>
+      <c r="X27">
+        <v>1.01</v>
+      </c>
+      <c r="Y27">
+        <v>1.31</v>
+      </c>
+      <c r="Z27">
+        <v>3.54</v>
+      </c>
+      <c r="AA27">
+        <v>2.02</v>
+      </c>
+      <c r="AB27">
+        <v>1.67</v>
+      </c>
+      <c r="AC27">
+        <v>3.5</v>
+      </c>
+      <c r="AD27">
+        <v>1.27</v>
+      </c>
+      <c r="AE27">
+        <v>1.09</v>
+      </c>
+      <c r="AF27">
+        <v>1.84</v>
+      </c>
+      <c r="AG27">
+        <v>1.85</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
+        <v>1.25</v>
+      </c>
+      <c r="AK27">
+        <v>1.76</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>-1</v>
+      </c>
+      <c r="AN27">
+        <v>-1</v>
+      </c>
+      <c r="AO27">
+        <v>-1</v>
+      </c>
+      <c r="AP27">
+        <v>-1</v>
+      </c>
+      <c r="AQ27">
+        <v>0</v>
+      </c>
+      <c r="AR27">
+        <v>0</v>
+      </c>
+      <c r="AS27">
+        <v>0</v>
+      </c>
+      <c r="AT27">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>2026-07-21 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>21:35</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Vila Nova</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>Fortaleza</t>
         </is>
       </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-      <c r="H27">
-        <v>0</v>
-      </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27">
-        <v>0</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27" t="inlineStr">
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N27">
+      <c r="N28">
         <v>2.35</v>
       </c>
-      <c r="O27">
+      <c r="O28">
         <v>3.1</v>
       </c>
-      <c r="P27">
+      <c r="P28">
         <v>2.88</v>
       </c>
-      <c r="Q27">
-        <v>0</v>
-      </c>
-      <c r="R27">
-        <v>0</v>
-      </c>
-      <c r="S27">
-        <v>0</v>
-      </c>
-      <c r="T27">
-        <v>0</v>
-      </c>
-      <c r="U27">
-        <v>0</v>
-      </c>
-      <c r="V27">
-        <v>0</v>
-      </c>
-      <c r="W27">
-        <v>0</v>
-      </c>
-      <c r="X27">
-        <v>0</v>
-      </c>
-      <c r="Y27">
-        <v>0</v>
-      </c>
-      <c r="Z27">
-        <v>0</v>
-      </c>
-      <c r="AA27">
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+      <c r="Y28">
+        <v>0</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+      <c r="AA28">
         <v>2.2</v>
       </c>
-      <c r="AB27">
+      <c r="AB28">
         <v>1.65</v>
       </c>
-      <c r="AC27">
-        <v>0</v>
-      </c>
-      <c r="AD27">
-        <v>0</v>
-      </c>
-      <c r="AE27">
-        <v>0</v>
-      </c>
-      <c r="AF27">
-        <v>0</v>
-      </c>
-      <c r="AG27">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>0</v>
-      </c>
-      <c r="AK27">
-        <v>0</v>
-      </c>
-      <c r="AL27">
-        <v>0</v>
-      </c>
-      <c r="AM27">
-        <v>-1</v>
-      </c>
-      <c r="AN27">
-        <v>-1</v>
-      </c>
-      <c r="AO27">
-        <v>-1</v>
-      </c>
-      <c r="AP27">
-        <v>-1</v>
-      </c>
-      <c r="AQ27">
-        <v>0</v>
-      </c>
-      <c r="AR27">
-        <v>0</v>
-      </c>
-      <c r="AS27">
-        <v>0</v>
-      </c>
-      <c r="AT27">
-        <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
+      <c r="AC28">
+        <v>0</v>
+      </c>
+      <c r="AD28">
+        <v>0</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>0</v>
+      </c>
+      <c r="AG28">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
+        <v>0</v>
+      </c>
+      <c r="AK28">
+        <v>0</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>-1</v>
+      </c>
+      <c r="AN28">
+        <v>-1</v>
+      </c>
+      <c r="AO28">
+        <v>-1</v>
+      </c>
+      <c r="AP28">
+        <v>-1</v>
+      </c>
+      <c r="AQ28">
+        <v>0</v>
+      </c>
+      <c r="AR28">
+        <v>0</v>
+      </c>
+      <c r="AS28">
+        <v>0</v>
+      </c>
+      <c r="AT28">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
         <is>
           <t>2026-07-21 21:35:00</t>
         </is>

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G2">
@@ -635,80 +635,80 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.15</v>
+        <v>3.2</v>
       </c>
       <c r="O2">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="P2">
-        <v>3.22</v>
+        <v>2.17</v>
       </c>
       <c r="Q2">
-        <v>2.85</v>
+        <v>3.8</v>
       </c>
       <c r="R2">
-        <v>2.19</v>
+        <v>1.94</v>
       </c>
       <c r="S2">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="T2">
-        <v>2.85</v>
+        <v>2.39</v>
       </c>
       <c r="U2">
-        <v>2.99</v>
+        <v>3.48</v>
       </c>
       <c r="V2">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="W2">
+        <v>1</v>
+      </c>
+      <c r="X2">
         <v>1.03</v>
       </c>
-      <c r="X2">
-        <v>1.02</v>
-      </c>
       <c r="Y2">
+        <v>1.4</v>
+      </c>
+      <c r="Z2">
+        <v>2.57</v>
+      </c>
+      <c r="AA2">
+        <v>2.45</v>
+      </c>
+      <c r="AB2">
+        <v>1.56</v>
+      </c>
+      <c r="AC2">
+        <v>4.5</v>
+      </c>
+      <c r="AD2">
+        <v>1.13</v>
+      </c>
+      <c r="AE2">
+        <v>1.01</v>
+      </c>
+      <c r="AF2">
+        <v>2.02</v>
+      </c>
+      <c r="AG2">
+        <v>1.69</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ2">
         <v>1.3</v>
       </c>
-      <c r="Z2">
-        <v>2.99</v>
-      </c>
-      <c r="AA2">
-        <v>2.05</v>
-      </c>
-      <c r="AB2">
-        <v>1.78</v>
-      </c>
-      <c r="AC2">
-        <v>3.5</v>
-      </c>
-      <c r="AD2">
-        <v>1.28</v>
-      </c>
-      <c r="AE2">
-        <v>1.04</v>
-      </c>
-      <c r="AF2">
-        <v>1.74</v>
-      </c>
-      <c r="AG2">
-        <v>1.85</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ2">
+      <c r="AK2">
         <v>1.29</v>
-      </c>
-      <c r="AK2">
-        <v>1.57</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="O3">
-        <v>3.34</v>
+        <v>3.24</v>
       </c>
       <c r="P3">
-        <v>3.41</v>
+        <v>3.22</v>
       </c>
       <c r="Q3">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="R3">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="S3">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="T3">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="U3">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="V3">
         <v>1.36</v>
       </c>
       <c r="W3">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X3">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z3">
-        <v>3.4</v>
+        <v>2.99</v>
       </c>
       <c r="AA3">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AB3">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="AC3">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AD3">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE3">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AF3">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AG3">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK3">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.2</v>
+        <v>1.91</v>
       </c>
       <c r="O4">
+        <v>3.34</v>
+      </c>
+      <c r="P4">
+        <v>3.41</v>
+      </c>
+      <c r="Q4">
+        <v>2.5</v>
+      </c>
+      <c r="R4">
+        <v>2.1</v>
+      </c>
+      <c r="S4">
+        <v>1.39</v>
+      </c>
+      <c r="T4">
         <v>3</v>
       </c>
-      <c r="P4">
-        <v>2.17</v>
-      </c>
-      <c r="Q4">
-        <v>3.8</v>
-      </c>
-      <c r="R4">
-        <v>1.94</v>
-      </c>
-      <c r="S4">
-        <v>1.48</v>
-      </c>
-      <c r="T4">
-        <v>2.39</v>
-      </c>
       <c r="U4">
-        <v>3.48</v>
+        <v>2.88</v>
       </c>
       <c r="V4">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="W4">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="X4">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y4">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="Z4">
-        <v>2.57</v>
+        <v>3.4</v>
       </c>
       <c r="AA4">
-        <v>2.45</v>
+        <v>2.01</v>
       </c>
       <c r="AB4">
-        <v>1.56</v>
+        <v>1.84</v>
       </c>
       <c r="AC4">
-        <v>4.5</v>
+        <v>3.45</v>
       </c>
       <c r="AD4">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="AE4">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AF4">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="AG4">
-        <v>1.69</v>
+        <v>1.93</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK4">
-        <v>1.29</v>
+        <v>1.8</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,80 +1939,80 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.17</v>
+        <v>3.8</v>
       </c>
       <c r="O10">
-        <v>5.9</v>
+        <v>3.55</v>
       </c>
       <c r="P10">
-        <v>20</v>
+        <v>1.82</v>
       </c>
       <c r="Q10">
-        <v>1.44</v>
+        <v>3.95</v>
       </c>
       <c r="R10">
-        <v>3.1</v>
+        <v>2.36</v>
       </c>
       <c r="S10">
+        <v>1.3</v>
+      </c>
+      <c r="T10">
+        <v>2.98</v>
+      </c>
+      <c r="U10">
+        <v>2.47</v>
+      </c>
+      <c r="V10">
+        <v>1.5</v>
+      </c>
+      <c r="W10">
+        <v>1.08</v>
+      </c>
+      <c r="X10">
+        <v>1.01</v>
+      </c>
+      <c r="Y10">
+        <v>1.2</v>
+      </c>
+      <c r="Z10">
+        <v>4.1</v>
+      </c>
+      <c r="AA10">
+        <v>1.67</v>
+      </c>
+      <c r="AB10">
+        <v>2.04</v>
+      </c>
+      <c r="AC10">
+        <v>2.65</v>
+      </c>
+      <c r="AD10">
+        <v>1.4</v>
+      </c>
+      <c r="AE10">
+        <v>1.12</v>
+      </c>
+      <c r="AF10">
+        <v>1.61</v>
+      </c>
+      <c r="AG10">
+        <v>2.15</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10">
+        <v>1.93</v>
+      </c>
+      <c r="AK10">
         <v>1.25</v>
-      </c>
-      <c r="T10">
-        <v>3.75</v>
-      </c>
-      <c r="U10">
-        <v>2.05</v>
-      </c>
-      <c r="V10">
-        <v>1.6</v>
-      </c>
-      <c r="W10">
-        <v>1.13</v>
-      </c>
-      <c r="X10">
-        <v>1.02</v>
-      </c>
-      <c r="Y10">
-        <v>1.12</v>
-      </c>
-      <c r="Z10">
-        <v>5</v>
-      </c>
-      <c r="AA10">
-        <v>1.5</v>
-      </c>
-      <c r="AB10">
-        <v>2.5</v>
-      </c>
-      <c r="AC10">
-        <v>2.08</v>
-      </c>
-      <c r="AD10">
-        <v>1.68</v>
-      </c>
-      <c r="AE10">
-        <v>1.18</v>
-      </c>
-      <c r="AF10">
-        <v>2.38</v>
-      </c>
-      <c r="AG10">
-        <v>1.53</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10">
-        <v>1.02</v>
-      </c>
-      <c r="AK10">
-        <v>5</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>3.8</v>
+        <v>1.17</v>
       </c>
       <c r="O11">
-        <v>3.55</v>
+        <v>5.9</v>
       </c>
       <c r="P11">
-        <v>1.82</v>
+        <v>20</v>
       </c>
       <c r="Q11">
-        <v>3.95</v>
+        <v>1.44</v>
       </c>
       <c r="R11">
-        <v>2.36</v>
+        <v>3.1</v>
       </c>
       <c r="S11">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T11">
-        <v>2.98</v>
+        <v>3.75</v>
       </c>
       <c r="U11">
-        <v>2.47</v>
+        <v>2.05</v>
       </c>
       <c r="V11">
+        <v>1.6</v>
+      </c>
+      <c r="W11">
+        <v>1.13</v>
+      </c>
+      <c r="X11">
+        <v>1.02</v>
+      </c>
+      <c r="Y11">
+        <v>1.12</v>
+      </c>
+      <c r="Z11">
+        <v>5</v>
+      </c>
+      <c r="AA11">
         <v>1.5</v>
       </c>
-      <c r="W11">
-        <v>1.08</v>
-      </c>
-      <c r="X11">
-        <v>1.01</v>
-      </c>
-      <c r="Y11">
-        <v>1.2</v>
-      </c>
-      <c r="Z11">
-        <v>4.1</v>
-      </c>
-      <c r="AA11">
-        <v>1.67</v>
-      </c>
       <c r="AB11">
-        <v>2.04</v>
+        <v>2.5</v>
       </c>
       <c r="AC11">
-        <v>2.65</v>
+        <v>2.08</v>
       </c>
       <c r="AD11">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="AE11">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF11">
-        <v>1.61</v>
+        <v>2.38</v>
       </c>
       <c r="AG11">
-        <v>2.15</v>
+        <v>1.53</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.93</v>
+        <v>1.02</v>
       </c>
       <c r="AK11">
-        <v>1.25</v>
+        <v>5</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -3735,31 +3735,31 @@
         <v>2.3</v>
       </c>
       <c r="O21">
-        <v>3.13</v>
+        <v>2.91</v>
       </c>
       <c r="P21">
-        <v>3.1</v>
+        <v>2.77</v>
       </c>
       <c r="Q21">
         <v>3</v>
       </c>
       <c r="R21">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="S21">
         <v>1.44</v>
       </c>
       <c r="T21">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="U21">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="V21">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W21">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X21">
         <v>1.05</v>
@@ -3768,16 +3768,16 @@
         <v>1.42</v>
       </c>
       <c r="Z21">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="AA21">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AB21">
         <v>1.53</v>
       </c>
       <c r="AC21">
-        <v>6.07</v>
+        <v>4.55</v>
       </c>
       <c r="AD21">
         <v>1.14</v>
@@ -3789,7 +3789,7 @@
         <v>2</v>
       </c>
       <c r="AG21">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -4713,10 +4713,10 @@
         <v>1.87</v>
       </c>
       <c r="O27">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="P27">
-        <v>4.07</v>
+        <v>3.7</v>
       </c>
       <c r="Q27">
         <v>2.47</v>
@@ -4749,10 +4749,10 @@
         <v>3.54</v>
       </c>
       <c r="AA27">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AB27">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AC27">
         <v>3.5</v>

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.2</v>
+        <v>2.15</v>
       </c>
       <c r="O2">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="P2">
-        <v>2.17</v>
+        <v>3.22</v>
       </c>
       <c r="Q2">
-        <v>3.8</v>
+        <v>2.85</v>
       </c>
       <c r="R2">
-        <v>1.94</v>
+        <v>2.19</v>
       </c>
       <c r="S2">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="T2">
-        <v>2.39</v>
+        <v>2.85</v>
       </c>
       <c r="U2">
-        <v>3.48</v>
+        <v>2.99</v>
       </c>
       <c r="V2">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="W2">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X2">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="Z2">
-        <v>2.57</v>
+        <v>2.99</v>
       </c>
       <c r="AA2">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="AB2">
-        <v>1.56</v>
+        <v>1.78</v>
       </c>
       <c r="AC2">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="AD2">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="AE2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF2">
-        <v>2.02</v>
+        <v>1.74</v>
       </c>
       <c r="AG2">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK2">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G3">
@@ -798,80 +798,80 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.15</v>
+        <v>3.2</v>
       </c>
       <c r="O3">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="P3">
-        <v>3.22</v>
+        <v>2.17</v>
       </c>
       <c r="Q3">
-        <v>2.85</v>
+        <v>3.8</v>
       </c>
       <c r="R3">
-        <v>2.19</v>
+        <v>1.94</v>
       </c>
       <c r="S3">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="T3">
-        <v>2.85</v>
+        <v>2.39</v>
       </c>
       <c r="U3">
-        <v>2.99</v>
+        <v>3.48</v>
       </c>
       <c r="V3">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="W3">
+        <v>1</v>
+      </c>
+      <c r="X3">
         <v>1.03</v>
       </c>
-      <c r="X3">
-        <v>1.02</v>
-      </c>
       <c r="Y3">
+        <v>1.4</v>
+      </c>
+      <c r="Z3">
+        <v>2.57</v>
+      </c>
+      <c r="AA3">
+        <v>2.45</v>
+      </c>
+      <c r="AB3">
+        <v>1.56</v>
+      </c>
+      <c r="AC3">
+        <v>4.5</v>
+      </c>
+      <c r="AD3">
+        <v>1.13</v>
+      </c>
+      <c r="AE3">
+        <v>1.01</v>
+      </c>
+      <c r="AF3">
+        <v>2.02</v>
+      </c>
+      <c r="AG3">
+        <v>1.69</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3">
         <v>1.3</v>
       </c>
-      <c r="Z3">
-        <v>2.99</v>
-      </c>
-      <c r="AA3">
-        <v>2.05</v>
-      </c>
-      <c r="AB3">
-        <v>1.78</v>
-      </c>
-      <c r="AC3">
-        <v>3.5</v>
-      </c>
-      <c r="AD3">
-        <v>1.28</v>
-      </c>
-      <c r="AE3">
-        <v>1.04</v>
-      </c>
-      <c r="AF3">
-        <v>1.74</v>
-      </c>
-      <c r="AG3">
-        <v>1.85</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3">
+      <c r="AK3">
         <v>1.29</v>
-      </c>
-      <c r="AK3">
-        <v>1.57</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -2920,7 +2920,7 @@
         <v>2.37</v>
       </c>
       <c r="O16">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="P16">
         <v>3.2</v>
@@ -2929,7 +2929,7 @@
         <v>3.25</v>
       </c>
       <c r="R16">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="S16">
         <v>1.74</v>
@@ -2947,7 +2947,7 @@
         <v>1.03</v>
       </c>
       <c r="X16">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Y16">
         <v>1.7</v>
@@ -2965,7 +2965,7 @@
         <v>6.5</v>
       </c>
       <c r="AD16">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AE16">
         <v>1.02</v>
@@ -2974,7 +2974,7 @@
         <v>2.4</v>
       </c>
       <c r="AG16">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3738,13 +3738,13 @@
         <v>2.91</v>
       </c>
       <c r="P21">
-        <v>2.77</v>
+        <v>3.1</v>
       </c>
       <c r="Q21">
         <v>3</v>
       </c>
       <c r="R21">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="S21">
         <v>1.44</v>
@@ -3762,13 +3762,13 @@
         <v>1.04</v>
       </c>
       <c r="X21">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y21">
         <v>1.42</v>
       </c>
       <c r="Z21">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="AA21">
         <v>2.4</v>
@@ -3780,7 +3780,7 @@
         <v>4.55</v>
       </c>
       <c r="AD21">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AE21">
         <v>1.05</v>
@@ -3805,7 +3805,7 @@
         <v>1.3</v>
       </c>
       <c r="AK21">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3931,7 +3931,7 @@
         <v>1.58</v>
       </c>
       <c r="Z22">
-        <v>2.27</v>
+        <v>2.32</v>
       </c>
       <c r="AA22">
         <v>2.62</v>
@@ -3943,7 +3943,7 @@
         <v>5.15</v>
       </c>
       <c r="AD22">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AE22">
         <v>1.03</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="O26">
-        <v>3.9</v>
+        <v>3.78</v>
       </c>
       <c r="P26">
         <v>4.7</v>
       </c>
       <c r="Q26">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="R26">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="S26">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T26">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="U26">
+        <v>2.21</v>
+      </c>
+      <c r="V26">
+        <v>1.5</v>
+      </c>
+      <c r="W26">
+        <v>1.09</v>
+      </c>
+      <c r="X26">
+        <v>1.01</v>
+      </c>
+      <c r="Y26">
+        <v>1.15</v>
+      </c>
+      <c r="Z26">
+        <v>4.8</v>
+      </c>
+      <c r="AA26">
+        <v>1.6</v>
+      </c>
+      <c r="AB26">
         <v>2.25</v>
       </c>
-      <c r="V26">
-        <v>1.57</v>
-      </c>
-      <c r="W26">
-        <v>1.15</v>
-      </c>
-      <c r="X26">
-        <v>1.02</v>
-      </c>
-      <c r="Y26">
-        <v>1.12</v>
-      </c>
-      <c r="Z26">
-        <v>4.65</v>
-      </c>
-      <c r="AA26">
-        <v>1.55</v>
-      </c>
-      <c r="AB26">
-        <v>2.29</v>
-      </c>
       <c r="AC26">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="AD26">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AE26">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF26">
         <v>1.59</v>
       </c>
       <c r="AG26">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK26">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4716,22 +4716,22 @@
         <v>3.4</v>
       </c>
       <c r="P27">
-        <v>3.7</v>
+        <v>3.48</v>
       </c>
       <c r="Q27">
         <v>2.47</v>
       </c>
       <c r="R27">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="S27">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="T27">
         <v>2.84</v>
       </c>
       <c r="U27">
-        <v>3.07</v>
+        <v>2.33</v>
       </c>
       <c r="V27">
         <v>1.36</v>
@@ -4746,7 +4746,7 @@
         <v>1.31</v>
       </c>
       <c r="Z27">
-        <v>3.54</v>
+        <v>2.5</v>
       </c>
       <c r="AA27">
         <v>2.04</v>
@@ -4758,7 +4758,7 @@
         <v>3.5</v>
       </c>
       <c r="AD27">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AE27">
         <v>1.09</v>
@@ -4783,7 +4783,7 @@
         <v>1.25</v>
       </c>
       <c r="AK27">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="AL27">
         <v>0</v>

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>3.8</v>
+        <v>1.17</v>
       </c>
       <c r="O10">
-        <v>3.55</v>
+        <v>5.9</v>
       </c>
       <c r="P10">
-        <v>1.82</v>
+        <v>20</v>
       </c>
       <c r="Q10">
-        <v>3.95</v>
+        <v>1.44</v>
       </c>
       <c r="R10">
-        <v>2.36</v>
+        <v>3.1</v>
       </c>
       <c r="S10">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T10">
-        <v>2.98</v>
+        <v>3.75</v>
       </c>
       <c r="U10">
-        <v>2.47</v>
+        <v>2.05</v>
       </c>
       <c r="V10">
+        <v>1.6</v>
+      </c>
+      <c r="W10">
+        <v>1.13</v>
+      </c>
+      <c r="X10">
+        <v>1.02</v>
+      </c>
+      <c r="Y10">
+        <v>1.12</v>
+      </c>
+      <c r="Z10">
+        <v>5</v>
+      </c>
+      <c r="AA10">
         <v>1.5</v>
       </c>
-      <c r="W10">
-        <v>1.08</v>
-      </c>
-      <c r="X10">
-        <v>1.01</v>
-      </c>
-      <c r="Y10">
-        <v>1.2</v>
-      </c>
-      <c r="Z10">
-        <v>4.1</v>
-      </c>
-      <c r="AA10">
-        <v>1.67</v>
-      </c>
       <c r="AB10">
-        <v>2.04</v>
+        <v>2.5</v>
       </c>
       <c r="AC10">
-        <v>2.65</v>
+        <v>2.08</v>
       </c>
       <c r="AD10">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="AE10">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF10">
-        <v>1.61</v>
+        <v>2.38</v>
       </c>
       <c r="AG10">
-        <v>2.15</v>
+        <v>1.53</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.93</v>
+        <v>1.02</v>
       </c>
       <c r="AK10">
-        <v>1.25</v>
+        <v>5</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,80 +2102,80 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.17</v>
+        <v>3.8</v>
       </c>
       <c r="O11">
-        <v>5.9</v>
+        <v>3.55</v>
       </c>
       <c r="P11">
-        <v>20</v>
+        <v>1.82</v>
       </c>
       <c r="Q11">
-        <v>1.44</v>
+        <v>3.95</v>
       </c>
       <c r="R11">
-        <v>3.1</v>
+        <v>2.36</v>
       </c>
       <c r="S11">
+        <v>1.3</v>
+      </c>
+      <c r="T11">
+        <v>2.98</v>
+      </c>
+      <c r="U11">
+        <v>2.47</v>
+      </c>
+      <c r="V11">
+        <v>1.5</v>
+      </c>
+      <c r="W11">
+        <v>1.08</v>
+      </c>
+      <c r="X11">
+        <v>1.01</v>
+      </c>
+      <c r="Y11">
+        <v>1.2</v>
+      </c>
+      <c r="Z11">
+        <v>4.1</v>
+      </c>
+      <c r="AA11">
+        <v>1.67</v>
+      </c>
+      <c r="AB11">
+        <v>2.04</v>
+      </c>
+      <c r="AC11">
+        <v>2.65</v>
+      </c>
+      <c r="AD11">
+        <v>1.4</v>
+      </c>
+      <c r="AE11">
+        <v>1.12</v>
+      </c>
+      <c r="AF11">
+        <v>1.61</v>
+      </c>
+      <c r="AG11">
+        <v>2.15</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11">
+        <v>1.93</v>
+      </c>
+      <c r="AK11">
         <v>1.25</v>
-      </c>
-      <c r="T11">
-        <v>3.75</v>
-      </c>
-      <c r="U11">
-        <v>2.05</v>
-      </c>
-      <c r="V11">
-        <v>1.6</v>
-      </c>
-      <c r="W11">
-        <v>1.13</v>
-      </c>
-      <c r="X11">
-        <v>1.02</v>
-      </c>
-      <c r="Y11">
-        <v>1.12</v>
-      </c>
-      <c r="Z11">
-        <v>5</v>
-      </c>
-      <c r="AA11">
-        <v>1.5</v>
-      </c>
-      <c r="AB11">
-        <v>2.5</v>
-      </c>
-      <c r="AC11">
-        <v>2.08</v>
-      </c>
-      <c r="AD11">
-        <v>1.68</v>
-      </c>
-      <c r="AE11">
-        <v>1.18</v>
-      </c>
-      <c r="AF11">
-        <v>2.38</v>
-      </c>
-      <c r="AG11">
-        <v>1.53</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11">
-        <v>1.02</v>
-      </c>
-      <c r="AK11">
-        <v>5</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N16">
@@ -4550,16 +4550,16 @@
         <v>1.57</v>
       </c>
       <c r="O26">
-        <v>3.78</v>
+        <v>3.68</v>
       </c>
       <c r="P26">
         <v>4.7</v>
       </c>
       <c r="Q26">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R26">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S26">
         <v>1.25</v>
@@ -4568,7 +4568,7 @@
         <v>3.45</v>
       </c>
       <c r="U26">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="V26">
         <v>1.5</v>
@@ -4592,13 +4592,13 @@
         <v>2.25</v>
       </c>
       <c r="AC26">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="AD26">
         <v>1.44</v>
       </c>
       <c r="AE26">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF26">
         <v>1.59</v>
@@ -4620,7 +4620,7 @@
         <v>1.2</v>
       </c>
       <c r="AK26">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AL26">
         <v>0</v>

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="O2">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="P2">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="Q2">
-        <v>2.85</v>
+        <v>2.91</v>
       </c>
       <c r="R2">
-        <v>2.19</v>
+        <v>1.99</v>
       </c>
       <c r="S2">
         <v>1.42</v>
       </c>
       <c r="T2">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="U2">
         <v>2.99</v>
       </c>
       <c r="V2">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W2">
         <v>1.03</v>
       </c>
       <c r="X2">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y2">
         <v>1.3</v>
@@ -674,16 +674,16 @@
         <v>2.99</v>
       </c>
       <c r="AA2">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AB2">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AC2">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AD2">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AE2">
         <v>1.04</v>
@@ -692,7 +692,7 @@
         <v>1.74</v>
       </c>
       <c r="AG2">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK2">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>3.2</v>
+        <v>1.98</v>
       </c>
       <c r="O3">
+        <v>3.34</v>
+      </c>
+      <c r="P3">
+        <v>3.12</v>
+      </c>
+      <c r="Q3">
+        <v>2.58</v>
+      </c>
+      <c r="R3">
+        <v>2.1</v>
+      </c>
+      <c r="S3">
+        <v>1.4</v>
+      </c>
+      <c r="T3">
         <v>3</v>
       </c>
-      <c r="P3">
-        <v>2.17</v>
-      </c>
-      <c r="Q3">
-        <v>3.8</v>
-      </c>
-      <c r="R3">
-        <v>1.94</v>
-      </c>
-      <c r="S3">
-        <v>1.48</v>
-      </c>
-      <c r="T3">
-        <v>2.39</v>
-      </c>
       <c r="U3">
-        <v>3.48</v>
+        <v>2.81</v>
       </c>
       <c r="V3">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="W3">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="X3">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y3">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="Z3">
-        <v>2.57</v>
+        <v>3.4</v>
       </c>
       <c r="AA3">
-        <v>2.45</v>
+        <v>1.9</v>
       </c>
       <c r="AB3">
-        <v>1.56</v>
+        <v>1.82</v>
       </c>
       <c r="AC3">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="AD3">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AE3">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AF3">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="AG3">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK3">
-        <v>1.29</v>
+        <v>1.8</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G4">
@@ -961,80 +961,80 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.91</v>
+        <v>3.13</v>
       </c>
       <c r="O4">
-        <v>3.34</v>
+        <v>2.95</v>
       </c>
       <c r="P4">
-        <v>3.41</v>
+        <v>2.15</v>
       </c>
       <c r="Q4">
+        <v>3.8</v>
+      </c>
+      <c r="R4">
+        <v>1.92</v>
+      </c>
+      <c r="S4">
+        <v>1.5</v>
+      </c>
+      <c r="T4">
+        <v>2.41</v>
+      </c>
+      <c r="U4">
+        <v>3.2</v>
+      </c>
+      <c r="V4">
+        <v>1.3</v>
+      </c>
+      <c r="W4">
+        <v>1</v>
+      </c>
+      <c r="X4">
+        <v>1.03</v>
+      </c>
+      <c r="Y4">
+        <v>1.4</v>
+      </c>
+      <c r="Z4">
+        <v>2.57</v>
+      </c>
+      <c r="AA4">
         <v>2.5</v>
       </c>
-      <c r="R4">
-        <v>2.1</v>
-      </c>
-      <c r="S4">
-        <v>1.39</v>
-      </c>
-      <c r="T4">
-        <v>3</v>
-      </c>
-      <c r="U4">
-        <v>2.88</v>
-      </c>
-      <c r="V4">
+      <c r="AB4">
+        <v>1.57</v>
+      </c>
+      <c r="AC4">
+        <v>4.5</v>
+      </c>
+      <c r="AD4">
+        <v>1.14</v>
+      </c>
+      <c r="AE4">
+        <v>1.01</v>
+      </c>
+      <c r="AF4">
+        <v>2</v>
+      </c>
+      <c r="AG4">
+        <v>1.69</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4">
         <v>1.36</v>
       </c>
-      <c r="W4">
-        <v>1.06</v>
-      </c>
-      <c r="X4">
-        <v>1.05</v>
-      </c>
-      <c r="Y4">
+      <c r="AK4">
         <v>1.25</v>
-      </c>
-      <c r="Z4">
-        <v>3.4</v>
-      </c>
-      <c r="AA4">
-        <v>2.01</v>
-      </c>
-      <c r="AB4">
-        <v>1.84</v>
-      </c>
-      <c r="AC4">
-        <v>3.45</v>
-      </c>
-      <c r="AD4">
-        <v>1.27</v>
-      </c>
-      <c r="AE4">
-        <v>1.1</v>
-      </c>
-      <c r="AF4">
-        <v>1.8</v>
-      </c>
-      <c r="AG4">
-        <v>1.93</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4">
-        <v>1.25</v>
-      </c>
-      <c r="AK4">
-        <v>1.8</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1127,25 +1127,25 @@
         <v>5.43</v>
       </c>
       <c r="O5">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P5">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="Q5">
-        <v>6.1</v>
+        <v>6.25</v>
       </c>
       <c r="R5">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="S5">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T5">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="U5">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="V5">
         <v>1.4</v>
@@ -1154,34 +1154,34 @@
         <v>1.08</v>
       </c>
       <c r="X5">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z5">
-        <v>3.77</v>
+        <v>3.88</v>
       </c>
       <c r="AA5">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AB5">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AC5">
-        <v>3.5</v>
+        <v>3.39</v>
       </c>
       <c r="AD5">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE5">
         <v>1.1</v>
       </c>
       <c r="AF5">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG5">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>2.39</v>
+        <v>1.21</v>
       </c>
       <c r="AK5">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,43 +1287,43 @@
         </is>
       </c>
       <c r="N6">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="O6">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="P6">
-        <v>3.68</v>
+        <v>3.4</v>
       </c>
       <c r="Q6">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="R6">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="S6">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="T6">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="U6">
-        <v>3.08</v>
+        <v>3.13</v>
       </c>
       <c r="V6">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W6">
         <v>1.07</v>
       </c>
       <c r="X6">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z6">
-        <v>2.97</v>
+        <v>2.81</v>
       </c>
       <c r="AA6">
         <v>2.1</v>
@@ -1332,19 +1332,19 @@
         <v>1.7</v>
       </c>
       <c r="AC6">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="AD6">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AE6">
         <v>1.03</v>
       </c>
       <c r="AF6">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AG6">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK6">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1456,31 +1456,31 @@
         <v>4.4</v>
       </c>
       <c r="P7">
-        <v>8.550000000000001</v>
+        <v>6.5</v>
       </c>
       <c r="Q7">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="R7">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="S7">
         <v>1.33</v>
       </c>
       <c r="T7">
-        <v>2.88</v>
+        <v>3.13</v>
       </c>
       <c r="U7">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="V7">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="W7">
         <v>1.1</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y7">
         <v>1.22</v>
@@ -1489,25 +1489,25 @@
         <v>4.2</v>
       </c>
       <c r="AA7">
+        <v>1.75</v>
+      </c>
+      <c r="AB7">
+        <v>2.05</v>
+      </c>
+      <c r="AC7">
+        <v>2.83</v>
+      </c>
+      <c r="AD7">
+        <v>1.4</v>
+      </c>
+      <c r="AE7">
+        <v>1.12</v>
+      </c>
+      <c r="AF7">
+        <v>1.96</v>
+      </c>
+      <c r="AG7">
         <v>1.73</v>
-      </c>
-      <c r="AB7">
-        <v>2.04</v>
-      </c>
-      <c r="AC7">
-        <v>2.78</v>
-      </c>
-      <c r="AD7">
-        <v>1.41</v>
-      </c>
-      <c r="AE7">
-        <v>1.13</v>
-      </c>
-      <c r="AF7">
-        <v>1.95</v>
-      </c>
-      <c r="AG7">
-        <v>1.74</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>1.17</v>
       </c>
       <c r="AK7">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="O8">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="P8">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="Q8">
         <v>2.15</v>
       </c>
       <c r="R8">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="S8">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="T8">
         <v>3.4</v>
       </c>
       <c r="U8">
-        <v>2.08</v>
+        <v>2.34</v>
       </c>
       <c r="V8">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="W8">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X8">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="Z8">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="AA8">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AB8">
-        <v>2.38</v>
+        <v>2.13</v>
       </c>
       <c r="AC8">
-        <v>2.17</v>
+        <v>2.59</v>
       </c>
       <c r="AD8">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AE8">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AF8">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AG8">
-        <v>2.26</v>
+        <v>2.06</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK8">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1779,28 +1779,28 @@
         <v>2.3</v>
       </c>
       <c r="O9">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P9">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="Q9">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="R9">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="S9">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T9">
+        <v>2.75</v>
+      </c>
+      <c r="U9">
         <v>2.8</v>
       </c>
-      <c r="U9">
-        <v>2.94</v>
-      </c>
       <c r="V9">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W9">
         <v>1.03</v>
@@ -1809,31 +1809,31 @@
         <v>1.05</v>
       </c>
       <c r="Y9">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z9">
-        <v>3.27</v>
+        <v>3</v>
       </c>
       <c r="AA9">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="AB9">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AC9">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AD9">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE9">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF9">
         <v>1.75</v>
       </c>
       <c r="AG9">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>1.25</v>
       </c>
       <c r="AK9">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,80 +1939,80 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.17</v>
+        <v>3.5</v>
       </c>
       <c r="O10">
-        <v>5.9</v>
+        <v>3.53</v>
       </c>
       <c r="P10">
-        <v>20</v>
+        <v>1.99</v>
       </c>
       <c r="Q10">
-        <v>1.44</v>
+        <v>3.65</v>
       </c>
       <c r="R10">
-        <v>3.1</v>
+        <v>2.33</v>
       </c>
       <c r="S10">
         <v>1.25</v>
       </c>
       <c r="T10">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U10">
-        <v>2.05</v>
+        <v>2.32</v>
       </c>
       <c r="V10">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="W10">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X10">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z10">
-        <v>5</v>
+        <v>4.35</v>
       </c>
       <c r="AA10">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AB10">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="AC10">
-        <v>2.08</v>
+        <v>2.27</v>
       </c>
       <c r="AD10">
-        <v>1.68</v>
+        <v>1.45</v>
       </c>
       <c r="AE10">
+        <v>1.2</v>
+      </c>
+      <c r="AF10">
+        <v>1.52</v>
+      </c>
+      <c r="AG10">
+        <v>2.3</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10">
         <v>1.18</v>
       </c>
-      <c r="AF10">
-        <v>2.38</v>
-      </c>
-      <c r="AG10">
-        <v>1.53</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10">
-        <v>1.02</v>
-      </c>
       <c r="AK10">
-        <v>5</v>
+        <v>1.25</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>3.8</v>
+        <v>1.12</v>
       </c>
       <c r="O11">
-        <v>3.55</v>
+        <v>7.75</v>
       </c>
       <c r="P11">
-        <v>1.82</v>
+        <v>14</v>
       </c>
       <c r="Q11">
-        <v>3.95</v>
+        <v>1.44</v>
       </c>
       <c r="R11">
-        <v>2.36</v>
+        <v>3.1</v>
       </c>
       <c r="S11">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="T11">
-        <v>2.98</v>
+        <v>3.5</v>
       </c>
       <c r="U11">
-        <v>2.47</v>
+        <v>2.09</v>
       </c>
       <c r="V11">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="W11">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="Z11">
-        <v>4.1</v>
+        <v>5.25</v>
       </c>
       <c r="AA11">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AB11">
-        <v>2.04</v>
+        <v>2.67</v>
       </c>
       <c r="AC11">
-        <v>2.65</v>
+        <v>2.13</v>
       </c>
       <c r="AD11">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="AE11">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AF11">
-        <v>1.61</v>
+        <v>2.38</v>
       </c>
       <c r="AG11">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.93</v>
+        <v>1.05</v>
       </c>
       <c r="AK11">
-        <v>1.25</v>
+        <v>5</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="O12">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P12">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="Q12">
-        <v>2.49</v>
+        <v>2.6</v>
       </c>
       <c r="R12">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="S12">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T12">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U12">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="V12">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W12">
         <v>1.02</v>
       </c>
       <c r="X12">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y12">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="Z12">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AA12">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AB12">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC12">
         <v>4.4</v>
       </c>
       <c r="AD12">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE12">
         <v>1.02</v>
       </c>
       <c r="AF12">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AG12">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK12">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,34 +2428,34 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="O13">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="P13">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q13">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="R13">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S13">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T13">
-        <v>2.98</v>
+        <v>3.6</v>
       </c>
       <c r="U13">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="V13">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W13">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X13">
         <v>1.01</v>
@@ -2464,19 +2464,19 @@
         <v>1.18</v>
       </c>
       <c r="Z13">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA13">
         <v>1.61</v>
       </c>
       <c r="AB13">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AC13">
-        <v>2.39</v>
+        <v>2.63</v>
       </c>
       <c r="AD13">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="AE13">
         <v>1.18</v>
@@ -2485,7 +2485,7 @@
         <v>1.5</v>
       </c>
       <c r="AG13">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK13">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2594,31 +2594,31 @@
         <v>1.14</v>
       </c>
       <c r="O14">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="P14">
         <v>11.5</v>
       </c>
       <c r="Q14">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="R14">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="S14">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="T14">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="U14">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="V14">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W14">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X14">
         <v>1</v>
@@ -2627,28 +2627,28 @@
         <v>1.12</v>
       </c>
       <c r="Z14">
-        <v>4.75</v>
+        <v>5.1</v>
       </c>
       <c r="AA14">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AB14">
-        <v>2.39</v>
+        <v>2.57</v>
       </c>
       <c r="AC14">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="AD14">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AE14">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AF14">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AG14">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AK14">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.2</v>
+        <v>3.51</v>
       </c>
       <c r="O15">
-        <v>3.6</v>
+        <v>3.66</v>
       </c>
       <c r="P15">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="Q15">
-        <v>3.75</v>
+        <v>4.03</v>
       </c>
       <c r="R15">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S15">
         <v>1.25</v>
@@ -2778,28 +2778,28 @@
         <v>2.36</v>
       </c>
       <c r="V15">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W15">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y15">
         <v>1.17</v>
       </c>
       <c r="Z15">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA15">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AB15">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="AC15">
-        <v>2.7</v>
+        <v>2.47</v>
       </c>
       <c r="AD15">
         <v>1.43</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AK15">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="O16">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="P16">
-        <v>3.2</v>
+        <v>2.91</v>
       </c>
       <c r="Q16">
         <v>3.25</v>
@@ -2947,7 +2947,7 @@
         <v>1.03</v>
       </c>
       <c r="X16">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="Y16">
         <v>1.7</v>
@@ -2974,7 +2974,7 @@
         <v>2.4</v>
       </c>
       <c r="AG16">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3083,16 +3083,16 @@
         <v>1.8</v>
       </c>
       <c r="O17">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P17">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="Q17">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="R17">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="S17">
         <v>1.33</v>
@@ -3101,40 +3101,40 @@
         <v>3.16</v>
       </c>
       <c r="U17">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="V17">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W17">
         <v>1.07</v>
       </c>
       <c r="X17">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y17">
         <v>1.22</v>
       </c>
       <c r="Z17">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AA17">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AB17">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC17">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="AD17">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE17">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF17">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AG17">
         <v>2.1</v>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AK17">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="O18">
+        <v>3.05</v>
+      </c>
+      <c r="P18">
         <v>3.2</v>
       </c>
-      <c r="P18">
-        <v>3</v>
-      </c>
       <c r="Q18">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="R18">
         <v>1.95</v>
       </c>
       <c r="S18">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="T18">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="U18">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="V18">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="W18">
         <v>1.02</v>
       </c>
       <c r="X18">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y18">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="Z18">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AA18">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="AB18">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AC18">
-        <v>4.05</v>
+        <v>4.15</v>
       </c>
       <c r="AD18">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AE18">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF18">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AG18">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>1.33</v>
       </c>
       <c r="AK18">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,61 +3406,61 @@
         </is>
       </c>
       <c r="N19">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="O19">
-        <v>8</v>
+        <v>6.95</v>
       </c>
       <c r="P19">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Q19">
-        <v>13</v>
+        <v>12.3</v>
       </c>
       <c r="R19">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="S19">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T19">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U19">
         <v>2.25</v>
       </c>
       <c r="V19">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="W19">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
         <v>1.12</v>
       </c>
       <c r="Z19">
-        <v>4.65</v>
+        <v>5.25</v>
       </c>
       <c r="AA19">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AB19">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AC19">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AD19">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AE19">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AF19">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="AG19">
         <v>1.5</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AK19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,16 +3569,16 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.37</v>
+        <v>2.44</v>
       </c>
       <c r="O20">
         <v>3.48</v>
       </c>
       <c r="P20">
-        <v>2.85</v>
+        <v>2.52</v>
       </c>
       <c r="Q20">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="R20">
         <v>2.2</v>
@@ -3599,34 +3599,34 @@
         <v>1.1</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y20">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z20">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AA20">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AB20">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC20">
-        <v>2.88</v>
+        <v>2.57</v>
       </c>
       <c r="AD20">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE20">
         <v>1.12</v>
       </c>
       <c r="AF20">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AG20">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AK20">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,16 +3732,16 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="O21">
         <v>2.91</v>
       </c>
       <c r="P21">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q21">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="R21">
         <v>1.9</v>
@@ -3759,16 +3759,16 @@
         <v>1.25</v>
       </c>
       <c r="W21">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X21">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y21">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="Z21">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="AA21">
         <v>2.4</v>
@@ -3780,7 +3780,7 @@
         <v>4.55</v>
       </c>
       <c r="AD21">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE21">
         <v>1.05</v>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK21">
         <v>1.5</v>
@@ -3895,19 +3895,19 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="O22">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="P22">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="Q22">
         <v>3.1</v>
       </c>
       <c r="R22">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="S22">
         <v>1.61</v>
@@ -3916,10 +3916,10 @@
         <v>2.25</v>
       </c>
       <c r="U22">
-        <v>3.72</v>
+        <v>3.8</v>
       </c>
       <c r="V22">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W22">
         <v>1.03</v>
@@ -3931,13 +3931,13 @@
         <v>1.58</v>
       </c>
       <c r="Z22">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="AA22">
         <v>2.62</v>
       </c>
       <c r="AB22">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AC22">
         <v>5.15</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="O23">
         <v>3.4</v>
       </c>
       <c r="P23">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="Q23">
         <v>2.5</v>
@@ -4073,10 +4073,10 @@
         <v>2.2</v>
       </c>
       <c r="S23">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T23">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="U23">
         <v>2.59</v>
@@ -4085,28 +4085,28 @@
         <v>1.4</v>
       </c>
       <c r="W23">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X23">
         <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z23">
         <v>3.38</v>
       </c>
       <c r="AA23">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AB23">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AC23">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="AD23">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AE23">
         <v>1.11</v>
@@ -4221,28 +4221,28 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.14</v>
+        <v>2.01</v>
       </c>
       <c r="O24">
-        <v>3.15</v>
+        <v>3.02</v>
       </c>
       <c r="P24">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="Q24">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="R24">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="S24">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T24">
         <v>2.65</v>
       </c>
       <c r="U24">
-        <v>3.16</v>
+        <v>2.95</v>
       </c>
       <c r="V24">
         <v>1.3</v>
@@ -4254,28 +4254,28 @@
         <v>1.08</v>
       </c>
       <c r="Y24">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="Z24">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="AA24">
         <v>2.25</v>
       </c>
       <c r="AB24">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AC24">
-        <v>4.2</v>
+        <v>4.21</v>
       </c>
       <c r="AD24">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE24">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF24">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG24">
         <v>1.83</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK24">
         <v>1.7</v>
@@ -4384,31 +4384,31 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="O25">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="P25">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="Q25">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="R25">
         <v>1.88</v>
       </c>
       <c r="S25">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="T25">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="U25">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="V25">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W25">
         <v>1.03</v>
@@ -4429,7 +4429,7 @@
         <v>1.53</v>
       </c>
       <c r="AC25">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AD25">
         <v>1.14</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AK25">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,10 +4547,10 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="O26">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="P26">
         <v>4.7</v>
@@ -4571,7 +4571,7 @@
         <v>2.25</v>
       </c>
       <c r="V26">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W26">
         <v>1.09</v>
@@ -4583,16 +4583,16 @@
         <v>1.15</v>
       </c>
       <c r="Z26">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="AA26">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB26">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AC26">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="AD26">
         <v>1.44</v>
@@ -4713,7 +4713,7 @@
         <v>1.87</v>
       </c>
       <c r="O27">
-        <v>3.4</v>
+        <v>3.11</v>
       </c>
       <c r="P27">
         <v>3.48</v>
@@ -4728,10 +4728,10 @@
         <v>1.41</v>
       </c>
       <c r="T27">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="U27">
-        <v>2.33</v>
+        <v>3.08</v>
       </c>
       <c r="V27">
         <v>1.36</v>
@@ -4743,10 +4743,10 @@
         <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z27">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="AA27">
         <v>2.04</v>
@@ -4783,7 +4783,7 @@
         <v>1.25</v>
       </c>
       <c r="AK27">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.35</v>
+        <v>2.17</v>
       </c>
       <c r="O28">
-        <v>3.1</v>
+        <v>3.03</v>
       </c>
       <c r="P28">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="Q28">
         <v>0</v>

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="O2">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="P2">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="Q2">
-        <v>2.91</v>
+        <v>2.58</v>
       </c>
       <c r="R2">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="S2">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T2">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U2">
-        <v>2.99</v>
+        <v>2.81</v>
       </c>
       <c r="V2">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W2">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X2">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y2">
+        <v>1.29</v>
+      </c>
+      <c r="Z2">
+        <v>3.4</v>
+      </c>
+      <c r="AA2">
+        <v>1.9</v>
+      </c>
+      <c r="AB2">
+        <v>1.82</v>
+      </c>
+      <c r="AC2">
+        <v>3.4</v>
+      </c>
+      <c r="AD2">
         <v>1.3</v>
       </c>
-      <c r="Z2">
-        <v>2.99</v>
-      </c>
-      <c r="AA2">
-        <v>2.12</v>
-      </c>
-      <c r="AB2">
-        <v>1.75</v>
-      </c>
-      <c r="AC2">
-        <v>3.8</v>
-      </c>
-      <c r="AD2">
-        <v>1.22</v>
-      </c>
       <c r="AE2">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF2">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AG2">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK2">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.98</v>
+        <v>3.13</v>
       </c>
       <c r="O3">
-        <v>3.34</v>
+        <v>2.95</v>
       </c>
       <c r="P3">
-        <v>3.12</v>
+        <v>2.15</v>
       </c>
       <c r="Q3">
-        <v>2.58</v>
+        <v>3.8</v>
       </c>
       <c r="R3">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="S3">
+        <v>1.5</v>
+      </c>
+      <c r="T3">
+        <v>2.41</v>
+      </c>
+      <c r="U3">
+        <v>3.2</v>
+      </c>
+      <c r="V3">
+        <v>1.3</v>
+      </c>
+      <c r="W3">
+        <v>1</v>
+      </c>
+      <c r="X3">
+        <v>1.03</v>
+      </c>
+      <c r="Y3">
         <v>1.4</v>
       </c>
-      <c r="T3">
-        <v>3</v>
-      </c>
-      <c r="U3">
-        <v>2.81</v>
-      </c>
-      <c r="V3">
-        <v>1.38</v>
-      </c>
-      <c r="W3">
-        <v>1.06</v>
-      </c>
-      <c r="X3">
-        <v>1.04</v>
-      </c>
-      <c r="Y3">
-        <v>1.29</v>
-      </c>
       <c r="Z3">
-        <v>3.4</v>
+        <v>2.57</v>
       </c>
       <c r="AA3">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="AB3">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="AC3">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="AD3">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AE3">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="AF3">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AG3">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
+        <v>1.36</v>
+      </c>
+      <c r="AK3">
         <v>1.25</v>
-      </c>
-      <c r="AK3">
-        <v>1.8</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G4">
@@ -961,80 +961,80 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.13</v>
+        <v>2.12</v>
       </c>
       <c r="O4">
-        <v>2.95</v>
+        <v>3.22</v>
       </c>
       <c r="P4">
-        <v>2.15</v>
+        <v>3.3</v>
       </c>
       <c r="Q4">
+        <v>2.91</v>
+      </c>
+      <c r="R4">
+        <v>1.99</v>
+      </c>
+      <c r="S4">
+        <v>1.42</v>
+      </c>
+      <c r="T4">
+        <v>2.88</v>
+      </c>
+      <c r="U4">
+        <v>2.99</v>
+      </c>
+      <c r="V4">
+        <v>1.37</v>
+      </c>
+      <c r="W4">
+        <v>1.03</v>
+      </c>
+      <c r="X4">
+        <v>1.05</v>
+      </c>
+      <c r="Y4">
+        <v>1.3</v>
+      </c>
+      <c r="Z4">
+        <v>2.99</v>
+      </c>
+      <c r="AA4">
+        <v>2.12</v>
+      </c>
+      <c r="AB4">
+        <v>1.75</v>
+      </c>
+      <c r="AC4">
         <v>3.8</v>
       </c>
-      <c r="R4">
-        <v>1.92</v>
-      </c>
-      <c r="S4">
-        <v>1.5</v>
-      </c>
-      <c r="T4">
-        <v>2.41</v>
-      </c>
-      <c r="U4">
-        <v>3.2</v>
-      </c>
-      <c r="V4">
+      <c r="AD4">
+        <v>1.22</v>
+      </c>
+      <c r="AE4">
+        <v>1.04</v>
+      </c>
+      <c r="AF4">
+        <v>1.74</v>
+      </c>
+      <c r="AG4">
+        <v>1.9</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4">
         <v>1.3</v>
       </c>
-      <c r="W4">
-        <v>1</v>
-      </c>
-      <c r="X4">
-        <v>1.03</v>
-      </c>
-      <c r="Y4">
-        <v>1.4</v>
-      </c>
-      <c r="Z4">
-        <v>2.57</v>
-      </c>
-      <c r="AA4">
-        <v>2.5</v>
-      </c>
-      <c r="AB4">
-        <v>1.57</v>
-      </c>
-      <c r="AC4">
-        <v>4.5</v>
-      </c>
-      <c r="AD4">
-        <v>1.14</v>
-      </c>
-      <c r="AE4">
-        <v>1.01</v>
-      </c>
-      <c r="AF4">
-        <v>2</v>
-      </c>
-      <c r="AG4">
-        <v>1.69</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4">
-        <v>1.36</v>
-      </c>
       <c r="AK4">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.91</v>
+        <v>1.35</v>
       </c>
       <c r="O6">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="P6">
-        <v>3.4</v>
+        <v>6.5</v>
       </c>
       <c r="Q6">
-        <v>2.46</v>
+        <v>1.82</v>
       </c>
       <c r="R6">
-        <v>1.97</v>
+        <v>2.27</v>
       </c>
       <c r="S6">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="T6">
-        <v>2.6</v>
+        <v>3.13</v>
       </c>
       <c r="U6">
-        <v>3.13</v>
+        <v>2.53</v>
       </c>
       <c r="V6">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="W6">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X6">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="Z6">
-        <v>2.81</v>
+        <v>4.2</v>
       </c>
       <c r="AA6">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AB6">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AC6">
-        <v>3.84</v>
+        <v>2.83</v>
       </c>
       <c r="AD6">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="AE6">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AF6">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="AG6">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AK6">
-        <v>1.77</v>
+        <v>2.88</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.35</v>
+        <v>1.91</v>
       </c>
       <c r="O7">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="P7">
-        <v>6.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q7">
-        <v>1.82</v>
+        <v>2.46</v>
       </c>
       <c r="R7">
-        <v>2.27</v>
+        <v>1.97</v>
       </c>
       <c r="S7">
+        <v>1.45</v>
+      </c>
+      <c r="T7">
+        <v>2.6</v>
+      </c>
+      <c r="U7">
+        <v>3.13</v>
+      </c>
+      <c r="V7">
+        <v>1.32</v>
+      </c>
+      <c r="W7">
+        <v>1.07</v>
+      </c>
+      <c r="X7">
+        <v>1.03</v>
+      </c>
+      <c r="Y7">
         <v>1.33</v>
       </c>
-      <c r="T7">
-        <v>3.13</v>
-      </c>
-      <c r="U7">
-        <v>2.53</v>
-      </c>
-      <c r="V7">
-        <v>1.42</v>
-      </c>
-      <c r="W7">
-        <v>1.1</v>
-      </c>
-      <c r="X7">
-        <v>1</v>
-      </c>
-      <c r="Y7">
-        <v>1.22</v>
-      </c>
       <c r="Z7">
-        <v>4.2</v>
+        <v>2.81</v>
       </c>
       <c r="AA7">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AB7">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AC7">
-        <v>2.83</v>
+        <v>3.84</v>
       </c>
       <c r="AD7">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="AE7">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AF7">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="AG7">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AK7">
-        <v>2.88</v>
+        <v>1.77</v>
       </c>
       <c r="AL7">
         <v>0</v>

--- a/jogos_2026-07-21.xlsx
+++ b/jogos_2026-07-21.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.35</v>
+        <v>1.91</v>
       </c>
       <c r="O6">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="P6">
-        <v>6.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q6">
-        <v>1.82</v>
+        <v>2.46</v>
       </c>
       <c r="R6">
-        <v>2.27</v>
+        <v>1.97</v>
       </c>
       <c r="S6">
+        <v>1.45</v>
+      </c>
+      <c r="T6">
+        <v>2.6</v>
+      </c>
+      <c r="U6">
+        <v>3.13</v>
+      </c>
+      <c r="V6">
+        <v>1.32</v>
+      </c>
+      <c r="W6">
+        <v>1.07</v>
+      </c>
+      <c r="X6">
+        <v>1.03</v>
+      </c>
+      <c r="Y6">
         <v>1.33</v>
       </c>
-      <c r="T6">
-        <v>3.13</v>
-      </c>
-      <c r="U6">
-        <v>2.53</v>
-      </c>
-      <c r="V6">
-        <v>1.42</v>
-      </c>
-      <c r="W6">
-        <v>1.1</v>
-      </c>
-      <c r="X6">
-        <v>1</v>
-      </c>
-      <c r="Y6">
-        <v>1.22</v>
-      </c>
       <c r="Z6">
-        <v>4.2</v>
+        <v>2.81</v>
       </c>
       <c r="AA6">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AB6">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AC6">
-        <v>2.83</v>
+        <v>3.84</v>
       </c>
       <c r="AD6">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="AE6">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AF6">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="AG6">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AK6">
-        <v>2.88</v>
+        <v>1.77</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.91</v>
+        <v>1.35</v>
       </c>
       <c r="O7">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="P7">
-        <v>3.4</v>
+        <v>6.5</v>
       </c>
       <c r="Q7">
-        <v>2.46</v>
+        <v>1.82</v>
       </c>
       <c r="R7">
-        <v>1.97</v>
+        <v>2.27</v>
       </c>
       <c r="S7">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="T7">
-        <v>2.6</v>
+        <v>3.13</v>
       </c>
       <c r="U7">
-        <v>3.13</v>
+        <v>2.53</v>
       </c>
       <c r="V7">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="W7">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X7">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="Z7">
-        <v>2.81</v>
+        <v>4.2</v>
       </c>
       <c r="AA7">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AB7">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AC7">
-        <v>3.84</v>
+        <v>2.83</v>
       </c>
       <c r="AD7">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="AE7">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AF7">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="AG7">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AK7">
-        <v>1.77</v>
+        <v>2.88</v>
       </c>
       <c r="AL7">
         <v>0</v>
